--- a/data/networking_cybersecurity_data.xlsx
+++ b/data/networking_cybersecurity_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\text_mining_project -V2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1011FC8A-A913-48B1-B769-60A81623E395}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56778B50-4D46-43CF-84FE-FC01D803CBCF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{66267932-DE90-47D8-BCE7-1B1BF65AE624}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1204" uniqueCount="869">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1206" uniqueCount="869">
   <si>
     <t>No</t>
   </si>
@@ -1947,252 +1947,726 @@
     <t>Due to the increasing presence of networked devices in everyday life, not only cybersecurity specialists but also end users benefit from security applications such as firewalls, vulnerability scanners, and intrusion detection systems. Recent approaches use large language models (LLMs) to rewrite brief, technical security alerts into intuitive language and suggest actionable measures, helping everyday users understand and respond appropriately to security risks. However, it remains an open question how well such alerts are explained to users. LLM outputs can also be hallucinated, inconsistent, or misleading. In this work, we introduce the Human-Centered Security Alert Evaluation Framework (HCSAEF). HCSAEF assesses LLM-generated cybersecurity notifications to support researchers who want to compare notifications generated for everyday users, improve them, or analyze the capabilities of different LLMs in explaining cybersecurity issues. We demonstrate HCSAEF through three use cases, which allow us to quantify the impact of prompt design, model selection, and output consistency. Our findings indicate that HCSAEF effectively differentiates generated notifications along dimensions such as intuitiveness, urgency, and correctness.</t>
   </si>
   <si>
+    <t>Penetration Testing for System Security: Methods and Practical Approaches</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Penetration testing refers to the process of simulating hacker attacks to evaluate the security of information systems . This study aims not only to clarify the theoretical foundations of penetration testing but also to explain and demonstrate the complete testing process, including how network system administrators may simulate attacks using various penetration testing methods. Methodologically, the paper outlines the five basic stages of a typical penetration test: intelligence gathering, vulnerability scanning, vulnerability exploitation, privilege escalation, and post-exploitation activities. In each phase, specific tools and techniques are examined in detail, along with practical guidance on their use. To enhance the practical relevance of the study, the paper also presents a real-life case study, illustrating how a complete penetration test is conducted in a real-world environment. Through this case, readers can gain insights into the detailed procedures and applied techniques, thereby deepening their understanding of the practical value of penetration testing. Finally, the paper summarizes the importance and necessity of penetration testing in securing information systems and maintaining network integrity, and it explores future trends and development directions for the field. Overall, the findings of this paper offer valuable references for both researchers and practitioners, contributing meaningfully to the improvement of penetration testing practices and the advancement of cybersecurity as a whole. </t>
+  </si>
+  <si>
+    <t>Vehicular Intrusion Detection System for Controller Area Network: A Comprehensive Survey and Evaluation</t>
+  </si>
+  <si>
+    <t>The progress of automotive technologies has made cybersecurity a crucial focus, leading to various cyber attacks. These attacks primarily target the Controller Area Network (CAN) and specialized Electronic Control Units (ECUs). In order to mitigate these attacks and bolster the security of vehicular systems, numerous defense solutions have been proposed.These solutions aim to detect diverse forms of vehicular attacks. However, the practical implementation of these solutions still presents certain limitations and challenges. In light of these circumstances, this paper undertakes a thorough examination of existing vehicular attacks and defense strategies employed against the CAN and ECUs. The objective is to provide valuable insights and inform the future design of Vehicular Intrusion Detection Systems (VIDS). The findings of our investigation reveal that the examined VIDS primarily concentrate on particular categories of attacks, neglecting the broader spectrum of potential threats. Moreover, we provide a comprehensive overview of the significant challenges encountered in implementing a robust and feasible VIDS. Additionally, we put forth several defense recommendations based on our study findings, aiming to inform and guide the future design of VIDS in the context of vehicular security.</t>
+  </si>
+  <si>
+    <t>Neuromorphic Mimicry Attacks Exploiting Brain-Inspired Computing for Covert Cyber Intrusions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Neuromorphic computing, inspired by the human brain's neural architecture, is revolutionizing artificial intelligence and edge computing with its low-power, adaptive, and event-driven designs. However, these unique characteristics introduce novel cybersecurity risks. This paper proposes Neuromorphic Mimicry Attacks (NMAs), a groundbreaking class of threats that exploit the probabilistic and non-deterministic nature of neuromorphic chips to execute covert intrusions. By mimicking legitimate neural activity through techniques such as synaptic weight tampering and sensory input poisoning, NMAs evade traditional intrusion detection systems, posing risks to applications such as autonomous vehicles, smart medical implants, and IoT networks. This research develops a theoretical framework for NMAs, evaluates their impact using a simulated neuromorphic chip dataset, and proposes countermeasures, including neural-specific anomaly detection and secure synaptic learning protocols. The findings underscore the critical need for tailored cybersecurity measures to protect brain-inspired computing, offering a pioneering exploration of this emerging threat landscape. </t>
+  </si>
+  <si>
+    <t>A Non-Zero-Sum Game Model for Optimal Cyber Defense Strategies</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In the contemporary digital landscape, cybersecurity has become a critical issue due to the increasing frequency and sophistication of cyber attacks. This study utilizes a non-zero-sum game theoretical framework to model the strategic interactions between cyber attackers and defenders, with the objective of identifying optimal strategies for both. By defining precise payoff functions that incorporate the probabilities and costs associated with various exploits, as well as the values of network nodes and the costs of deploying honeypots, we derive Nash equilibria that inform strategic decisions. The proposed model is validated through extensive simulations, demonstrating its effectiveness in enhancing network security. Our results indicate that high-probability, low-cost exploits like Phishing and Social Engineering are more likely to be used by attackers, necessitating prioritized defense mechanisms. Our findings also show that increasing the number of network nodes dilutes the attacker's efforts, thereby improving the defender's payoff. This study provides valuable insights into optimizing resource allocation for cybersecurity and highlights the scalability and practical applicability of the game-theoretic approach. △</t>
+  </si>
+  <si>
+    <t>Adaptive Pruning of Deep Neural Networks for Resource-Aware Embedded Intrusion Detection on the Edge</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Artificial neural network pruning is a method in which artificial neural network sizes can be reduced while attempting to preserve the predicting capabilities of the network. This is done to make the model smaller or faster during inference time. In this work we analyze the ability of a selection of artificial neural network pruning methods to generalize to a new cybersecurity dataset utilizing a simpler network type than was designed for. We analyze each method using a variety of pruning degrees to best understand how each algorithm responds to the new environment. This has allowed us to determine the most well fit pruning method of those we searched for the task. Unexpectedly, we have found that many of them do not generalize to the problem well, leaving only a few algorithms working to an acceptable degree. </t>
+  </si>
+  <si>
+    <t>A Survey of Learning-Based Intrusion Detection Systems for In-Vehicle Network</t>
+  </si>
+  <si>
+    <t>Connected and Autonomous Vehicles (CAVs) enhance mobility but face cybersecurity threats, particularly through the insecure Controller Area Network (CAN) bus. Cyberattacks can have devastating consequences in connected vehicles, including the loss of control over critical systems, necessitating robust security solutions. In-vehicle Intrusion Detection Systems (IDSs) offer a promising approach by detecting malicious activities in real time. This survey provides a comprehensive review of state-of-the-art research on learning-based in-vehicle IDSs, focusing on Machine Learning (ML), Deep Learning (DL), and Federated Learning (FL) approaches. Based on the reviewed studies, we critically examine existing IDS approaches, categorising them by the types of attacks they detect - known, unknown, and combined known-unknown attacks - while identifying their limitations. We also review the evaluation metrics used in research, emphasising the need to consider multiple criteria to meet the requirements of safety-critical systems. Additionally, we analyse FL-based IDSs and highlight their limitations. By doing so, this survey helps identify effective security measures, address existing limitations, and guide future research toward more resilient and adaptive protection mechanisms, ensuring the safety and reliability of CAVs.</t>
+  </si>
+  <si>
+    <t>Modeling Interdependent Cybersecurity Threats Using Bayesian Networks: A Case Study on In-Vehicle Infotainment Systems</t>
+  </si>
+  <si>
+    <t>Cybersecurity threats are increasingly marked by interdependence, uncertainty, and evolving complexity challenges that traditional assessment methods such as CVSS, STRIDE, and attack trees fail to adequately capture. This paper reviews the application of Bayesian Networks (BNs) in cybersecurity risk modeling, highlighting their capacity to represent probabilistic dependencies, integrate diverse threat indicators, and support reasoning under uncertainty. A structured case study is presented in which a STRIDE-based attack tree for an automotive In-Vehicle Infotainment (IVI) system is transformed into a Bayesian Network. Logical relationships are encoded using Conditional Probability Tables (CPTs), and threat likelihoods are derived from normalized DREAD scores. The model enables not only probabilistic inference of system compromise likelihood but also supports causal analysis using do-calculus and local sensitivity analysis to identify high-impact vulnerabilities. These analyses provide insight into the most influential nodes within the threat propagation chain, informing targeted mitigation strategies. While demonstrating the potential of BNs for dynamic and context-aware risk assessment, the study also outlines limitations related to scalability, reliance on expert input, static structure assumptions, and limited temporal modeling. The paper concludes by advocating for future enhancements through Dynamic Bayesian Networks, structure learning, and adaptive inference to better support real-time cybersecurity decision-making in complex environments.</t>
+  </si>
+  <si>
+    <t>The Geography of Transportation Cybersecurity: Visitor Flows, Industry Clusters, and Spatial Dynamics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rapid evolution of the transportation cybersecurity ecosystem, encompassing cybersecurity, automotive, and transportation and logistics sectors, will lead to the formation of distinct spatial clusters and visitor flow patterns across the US. This study examines the spatiotemporal dynamics of visitor flows, analyzing how socioeconomic factors shape industry clustering and workforce distribution within these evolving sectors. To model and predict visitor flow patterns, we develop a BiTransGCN framework, integrating an attention-based Transformer architecture with a Graph Convolutional Network backbone. By integrating AI-enabled forecasting techniques with spatial analysis, this study improves our ability to track, interpret, and anticipate changes in industry clustering and mobility trends, thereby supporting strategic planning for a secure and resilient transportation network. It offers a data-driven foundation for economic planning, workforce development, and targeted investments in the transportation cybersecurity ecosystem. </t>
+  </si>
+  <si>
+    <t>Building a global quantum internet using a satellite constellation with inter-satellite links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The quantum internet is a global network to distribute entanglement and communicate quantum information with applications in cybersecurity, quantum computing, and quantum sensing. Here, we propose building a quantum internet using a constellation of low-Earth-orbit satellites equipped with inter-satellite laser links. Our proposal is based on the downlink model of photon transmission, where satellites carry entangled photon sources and/or have a mirror relay system to redirect the photon path in space. We show that few MHz entanglement distribution rates are possible between the US, Europe, and Asia, with a multiplexed entangled-photon source generating pairs at 10 GHz. Our proposal demonstrates the importance of passive optics in realizing a satellite-based quantum internet, which reduces dependency on quantum memory and repeater technologies. </t>
+  </si>
+  <si>
+    <t>Security through the Eyes of AI: How Visualization is Shaping Malware Detection</t>
+  </si>
+  <si>
+    <t>Malware, a persistent cybersecurity threat, increasingly targets interconnected digital systems such as desktop, mobile, and IoT platforms through sophisticated attack vectors. By exploiting these vulnerabilities, attackers compromise the integrity and resilience of modern digital ecosystems. To address this risk, security experts actively employ Machine Learning or Deep Learning-based strategies, integrating static, dynamic, or hybrid approaches to categorize malware instances. Despite their advantages, these methods have inherent drawbacks and malware variants persistently evolve with increased sophistication, necessitating advancements in detection strategies. Visualization-based techniques are emerging as scalable and interpretable solutions for detecting and understanding malicious behaviors across diverse platforms including desktop, mobile, IoT, and distributed systems as well as through analysis of network packet capture files. In this comprehensive survey of more than 100 high-quality research articles, we evaluate existing visualization-based approaches applied to malware detection and classification. As a first contribution, we propose a new all-encompassing framework to study the landscape of visualization-based malware detection techniques. Within this framework, we systematically analyze state-of-the-art approaches across the critical stages of the malware detection pipeline. By analyzing not only the single techniques but also how they are combined to produce the final solution, we shed light on the main challenges in visualization-based approaches and provide insights into the advancements and potential future directions in this critical field.</t>
+  </si>
+  <si>
+    <t>Open Challenges in Multi-Agent Security: Towards Secure Systems of Interacting AI Agents</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Decentralized AI agents will soon interact across internet platforms, creating security challenges beyond traditional cybersecurity and AI safety frameworks. Free-form protocols are essential for AI's task generalization but enable new threats like secret collusion and coordinated swarm attacks. Network effects can rapidly spread privacy breaches, disinformation, jailbreaks, and data poisoning, while multi-agent dispersion and stealth optimization help adversaries evade oversightcreating novel persistent threats at a systemic level. Despite their critical importance, these security challenges remain understudied, with research fragmented across disparate fields including AI security, multi-agent learning, complex systems, cybersecurity, game theory, distributed systems, and technical AI governance. We introduce \textbf{multi-agent security}, a new field dedicated to securing networks of decentralized AI agents against threats that emerge or amplify through their interactionswhether direct or indirect via shared environmentswith each other, humans, and institutions, and characterize fundamental security-performance trade-offs. Our preliminary work (1) taxonomizes the threat landscape arising from interacting AI agents, (2) surveys security-performance tradeoffs in decentralized AI systems, and (3) proposes a unified research agenda addressing open challenges in designing secure agent systems and interaction environments. By identifying these gaps, we aim to guide research in this critical area to unlock the socioeconomic potential of large-scale agent deployment on the internet, foster public trust, and mitigate national security risks in critical infrastructure and defense contexts.</t>
+  </si>
+  <si>
+    <t>From Texts to Shields: Convergence of Large Language Models and Cybersecurity</t>
+  </si>
+  <si>
+    <t>This report explores the convergence of large language models (LLMs) and cybersecurity, synthesizing interdisciplinary insights from network security, artificial intelligence, formal methods, and human-centered design. It examines emerging applications of LLMs in software and network security, 5G vulnerability analysis, and generative security engineering. The report highlights the role of agentic LLMs in automating complex tasks, improving operational efficiency, and enabling reasoning-driven security analytics. Socio-technical challenges associated with the deployment of LLMs -- including trust, transparency, and ethical considerations -- can be addressed through strategies such as human-in-the-loop systems, role-specific training, and proactive robustness testing. The report further outlines critical research challenges in ensuring interpretability, safety, and fairness in LLM-based systems, particularly in high-stakes domains. By integrating technical advances with organizational and societal considerations, this report presents a forward-looking research agenda for the secure and effective adoption of LLMs in cybersecurity.</t>
+  </si>
+  <si>
+    <t>PICO: Secure Transformers via Robust Prompt Isolation and Cybersecurity Oversight</t>
+  </si>
+  <si>
+    <t>We propose a robust transformer architecture designed to prevent prompt injection attacks and ensure secure, reliable response generation. Our PICO (Prompt Isolation and Cybersecurity Oversight) framework structurally separates trusted system instructions from untrusted user inputs through dual channels that are processed independently and merged only by a controlled, gated fusion mechanism. In addition, we integrate a specialized Security Expert Agent within a Mixture-of-Experts (MoE) framework and incorporate a Cybersecurity Knowledge Graph (CKG) to supply domain-specific reasoning. Our training design further ensures that the system prompt branch remains immutable while the rest of the network learns to handle adversarial inputs safely. This PICO framework is presented via a general mathematical formulation, then elaborated in terms of the specifics of transformer architecture, and fleshed out via hypothetical case studies including Policy Puppetry attacks. While the most effective implementation may involve training transformers in a PICO-based way from scratch, we also present a cost-effective fine-tuning approach.</t>
+  </si>
+  <si>
+    <t>The Dark Side of Digital Twins: Adversarial Attacks on AI-Driven Water Forecasting</t>
+  </si>
+  <si>
+    <t>Digital twins (DTs) are improving water distribution systems by using real-time data, analytics, and prediction models to optimize operations. This paper presents a DT platform designed for a Spanish water supply network, utilizing Long Short-Term Memory (LSTM) networks to predict water consumption. However, machine learning models are vulnerable to adversarial attacks, such as the Fast Gradient Sign Method (FGSM) and Projected Gradient Descent (PGD). These attacks manipulate critical model parameters, injecting subtle distortions that degrade forecasting accuracy. To further exploit these vulnerabilities, we introduce a Learning Automata (LA) and Random LA-based approach that dynamically adjusts perturbations, making adversarial attacks more difficult to detect. Experimental results show that this approach significantly impacts prediction reliability, causing the Mean Absolute Percentage Error (MAPE) to rise from 26% to over 35%. Moreover, adaptive attack strategies amplify this effect, highlighting cybersecurity risks in AI-driven DTs. These findings emphasize the urgent need for robust defenses, including adversarial training, anomaly detection, and secure data pipelines.</t>
+  </si>
+  <si>
+    <t>A Virtual Cybersecurity Department for Securing Digital Twins in Water Distribution Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Digital twins (DTs) help improve real-time monitoring and decision-making in water distribution systems. However, their connectivity makes them easy targets for cyberattacks such as scanning, denial-of-service (DoS), and unauthorized access. Small and medium-sized enterprises (SMEs) that manage these systems often do not have enough budget or staff to build strong cybersecurity teams. To solve this problem, we present a Virtual Cybersecurity Department (VCD), an affordable and automated framework designed for SMEs. The VCD uses open-source tools like Zabbix for real-time monitoring, Suricata for network intrusion detection, Fail2Ban to block repeated login attempts, and simple firewall settings. To improve threat detection, we also add a machine-learning-based IDS trained on the OD-IDS2022 dataset using an improved ensemble model. This model detects cyber threats such as brute-force attacks, remote code execution (RCE), and network flooding, with 92\% accuracy and fewer false alarms. Our solution gives SMEs a practical and efficient way to secure water systems using low-cost and easy-to-manage tools. </t>
+  </si>
+  <si>
+    <t>Cybersecurity for Autonomous Vehicles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The increasing adoption of autonomous vehicles is bringing a major shift in the automotive industry. However, as these vehicles become more connected, cybersecurity threats have emerged as a serious concern. Protecting the security and integrity of autonomous systems is essential to prevent malicious activities that can harm passengers, other road users, and the overall transportation network. This paper focuses on addressing the cybersecurity issues in autonomous vehicles by examining the challenges and risks involved, which are important for building a secure future. Since autonomous vehicles depend on the communication between sensors, artificial intelligence, external infrastructure, and other systems, they are exposed to different types of cyber threats. A cybersecurity breach in an autonomous vehicle can cause serious problems, including a loss of public trust and safety. Therefore, it is very important to develop and apply strong cybersecurity measures to support the growth and acceptance of self-driving cars. This paper discusses major cybersecurity challenges like vulnerabilities in software and hardware, risks from wireless communication, and threats through external interfaces. It also reviews existing solutions such as secure software development, intrusion detection systems, cryptographic protocols, and anomaly detection methods. Additionally, the paper highlights the role of regulatory bodies, industry collaborations, and cybersecurity standards in creating a secure environment for autonomous vehicles. Setting clear rules and best practices is necessary for consistent protection across manufacturers and regions. By analyzing the current cybersecurity landscape and suggesting practical countermeasures, this paper aims to contribute to the safe development and public trust of autonomous vehicle technology. </t>
+  </si>
+  <si>
+    <t>Feature Selection via GANs (GANFS): Enhancing Machine Learning Models for DDoS Mitigation</t>
+  </si>
+  <si>
+    <t>Distributed Denial of Service (DDoS) attacks represent a persistent and evolving threat to modern networked systems, capable of causing large-scale service disruptions. The complexity of such attacks, often hidden within high-dimensional and redundant network traffic data, necessitates robust and intelligent feature selection techniques for effective detection. Traditional methods such as filter-based, wrapper-based, and embedded approaches, each offer strengths but struggle with scalability or adaptability in complex attack environments. In this study, we explore these existing techniques through a detailed comparative analysis and highlight their limitations when applied to large-scale DDoS detection tasks. Building upon these insights, we introduce a novel Generative Adversarial Network-based Feature Selection (GANFS) method that leverages adversarial learning dynamics to identify the most informative features. By training a GAN exclusively on attack traffic and employing a perturbation-based sensitivity analysis on the Discriminator, GANFS effectively ranks feature importance without relying on full supervision. Experimental evaluations using the CIC-DDoS2019 dataset demonstrate that GANFS not only improves the accuracy of downstream classifiers but also enhances computational efficiency by significantly reducing feature dimensionality. These results point to the potential of integrating generative learning models into cybersecurity pipelines to build more adaptive and scalable detection systems.</t>
+  </si>
+  <si>
+    <t>Cluster-Aware Attacks on Graph Watermarks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data from domains such as social networks, healthcare, finance, and cybersecurity can be represented as graph-structured information. Given the sensitive nature of this data and their frequent distribution among collaborators, ensuring secure and attributable sharing is essential. Graph watermarking enables attribution by embedding user-specific signatures into graph-structured data. While prior work has addressed random perturbation attacks, the threat posed by adversaries leveraging structural properties through community detection remains unexplored. In this work, we introduce a cluster-aware threat model in which adversaries apply community-guided modifications to evade detection. We propose two novel attack strategies and evaluate them on real-world social network graphs. Our results show that cluster-aware attacks can reduce attribution accuracy by up to 80% more than random baselines under equivalent perturbation budgets on sparse graphs. To mitigate this threat, we propose a lightweight embedding enhancement that distributes watermark nodes across graph communities. This approach improves attribution accuracy by up to 60% under attack on dense graphs, without increasing runtime or structural distortion. Our findings underscore the importance of cluster-topological awareness in both watermarking design and adversarial modeling. </t>
+  </si>
+  <si>
+    <t>Structural Resilience Analysis of an Internet Fragment Against Targeted and Random Attacks -- A Case Study Based on iThena Project Data</t>
+  </si>
+  <si>
+    <t>This article presents an analysis of the structural resilience of a fragment of Internet topology against both targeted and random attacks, based on empirical data obtained from the iThena project. Using a processed visualization of the network, a graph representing node connections was generated and subsequently subjected to detailed analysis using centrality metrics and community detection algorithms. Two attack scenarios were carried out: removal of nodes with the highest betweenness centrality and random removal of an equivalent number of nodes. The results indicate that targeted attacks have a significantly more destructive impact on the cohesion and functionality of the network than random disruptions. The article highlights the importance of identifying critical nodes and developing monitoring and protection mechanisms for Internet infrastructure in the context of cybersecurity.</t>
+  </si>
+  <si>
+    <t>Integrating Graph Theoretical Approaches in Cybersecurity Education CSCI-RTED</t>
+  </si>
+  <si>
+    <t>As cybersecurity threats continue to evolve, the need for advanced tools to analyze and understand complex cyber environments has become increasingly critical. Graph theory offers a powerful framework for modeling relationships within cyber ecosystems, making it highly applicable to cybersecurity. This paper focuses on the development of an enriched version of the widely recognized NSL-KDD dataset, incorporating graph-theoretical concepts to enhance its practical value. The enriched dataset provides a resource for students and professionals to engage in hands-on analysis, enabling them to explore graph-based methodologies for identifying network behavior and vulnerabilities. To validate the effectiveness of this dataset, we employed IBM Auto AI, demonstrating its capability in real-world applications such as classification and threat prediction. By addressing the need for graph-theoretical datasets, this study provides a practical tool for equipping future cybersecurity professionals with the skills necessary to confront complex cyber challenges.</t>
+  </si>
+  <si>
+    <t>Cyber Value At Risk Model for IoT Ecosystems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The Internet of Things (IoT) presents unique cybersecurity challenges due to its interconnected nature and diverse application domains. This paper explores the application of Cyber Value-at-Risk (Cy-VaR) models to assess and mitigate cybersecurity risks in IoT environments. Cy-VaR, rooted in Value at Risk principles, provides a framework to quantify the potential financial impacts of cybersecurity incidents. Initially developed to evaluate overall risk exposure across scenarios, our approach extends Cy-VaR to consider specific IoT layers: perception, network, and application. Each layer encompasses distinct functionalities and vulnerabilities, from sensor data acquisition (perception layer) to secure data transmission (network layer) and application-specific services (application layer). By calculating Cy- VaR for each layer and scenario, organizations can prioritize security investments effectively. This paper discusses methodologies and models, including scenario-based Cy-VaR and layer-specific risk assessments, emphasizing their application in enhancing IoT cybersecurity resilience. </t>
+  </si>
+  <si>
+    <t>Towards Explainable and Lightweight AI for Real-Time Cyber Threat Hunting in Edge Networks</t>
+  </si>
+  <si>
+    <t>As cyber threats continue to evolve, securing edge networks has become increasingly challenging due to their distributed nature and resource limitations. Many AI-driven threat detection systems rely on complex deep learning models, which, despite their high accuracy, suffer from two major drawbacks: lack of interpretability and high computational cost. Black-box AI models make it difficult for security analysts to understand the reasoning behind their predictions, limiting their practical deployment. Moreover, conventional deep learning techniques demand significant computational resources, rendering them unsuitable for edge devices with limited processing power. To address these issues, this study introduces an Explainable and Lightweight AI (ELAI) framework designed for real-time cyber threat detection in edge networks. Our approach integrates interpretable machine learning algorithms with optimized lightweight deep learning techniques, ensuring both transparency and computational efficiency. The proposed system leverages decision trees, attention-based deep learning, and federated learning to enhance detection accuracy while maintaining explainability. We evaluate ELAI using benchmark cybersecurity datasets, such as CICIDS and UNSW-NB15, assessing its performance across diverse cyberattack scenarios. Experimental results demonstrate that the proposed framework achieves high detection rates with minimal false positives, all while significantly reducing computational demands compared to traditional deep learning methods. The key contributions of this work include: (1) a novel interpretable AI-based cybersecurity model tailored for edge computing environments, (2) an optimized lightweight deep learning approach for real-time cyber threat detection, and (3) a comprehensive analysis of explainability techniques in AI-driven cybersecurity applications.</t>
+  </si>
+  <si>
+    <t>Exploring the Role of Large Language Models in Cybersecurity: A Systematic Survey</t>
+  </si>
+  <si>
+    <t>With the rapid development of technology and the acceleration of digitalisation, the frequency and complexity of cyber security threats are increasing. Traditional cybersecurity approaches, often based on static rules and predefined scenarios, are struggling to adapt to the rapidly evolving nature of modern cyberattacks. There is an urgent need for more adaptive and intelligent defence strategies. The emergence of Large Language Model (LLM) provides an innovative solution to cope with the increasingly severe cyber threats, and its potential in analysing complex attack patterns, predicting threats and assisting real-time response has attracted a lot of attention in the field of cybersecurity, and exploring how to effectively use LLM to defend against cyberattacks has become a hot topic in the current research field. This survey examines the applications of LLM from the perspective of the cyber attack lifecycle, focusing on the three phases of defense reconnaissance, foothold establishment, and lateral movement, and it analyzes the potential of LLMs in Cyber Threat Intelligence (CTI) tasks. Meanwhile, we investigate how LLM-based security solutions are deployed and applied in different network scenarios. It also summarizes the internal and external risk issues faced by LLM during its application. Finally, this survey also points out the facing risk issues and possible future research directions in this domain.</t>
+  </si>
+  <si>
+    <t>Rethinking trust in the digital age: An investigation of zero trust architecture's social consequences on organizational culture, collaboration, and knowledge sharing</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As cyber threats escalate, Zero Trust Architecture (ZTA) replaces outdated perimeter security with strict never trust, always verify protocols. However, ZTA's dual nature as both technical infrastructure and social intervention creates an unresolved tension: its very mechanisms for security may systematically erode the trust foundations enabling effective collaboration. This integrative research combines case study analysis, employee surveys, and social network mapping reveals how ZTA disrupts knowledge-sharing, disproportionately hindering low-altruism employees, while surveillance erodes collective psychological ownership. Networked organizations, reliant on fluid trust, face fragmentation risks. Mitigation strategies include adaptive authorization frameworks using behavioral analytics and transparent communication reframing security as shared responsibility. Interdepartmental collaboration in security design preserves organizational trust structures identified through sociometric mapping. This research provides a framework balancing technical rigor with cultural sensitivity, proving cybersecurity can coexist with innovation by aligning verification with organizational psychology. The findings pioneer a paradigm where security and trust evolve synergistically critical for digital resilience in hybrid work environments. Future security must harmonize protocols with trust cultivation, ensuring defenses adapt to social dynamics driving modern enterprises.</t>
+  </si>
+  <si>
+    <t>Designing a reliable lateral movement detector using a graph foundation model</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Foundation models have recently emerged as a new paradigm in machine learning (ML). These models are pre-trained on large and diverse datasets and can subsequently be applied to various downstream tasks with little or no retraining. This allows people without advanced ML expertise to build ML applications, accelerating innovation across many fields. However, the adoption of foundation models in cybersecurity is hindered by their inability to efficiently process data such as network traffic captures or binary executables. The recent introduction of graph foundation models (GFMs) could make a significant difference, as graphs are well-suited to representing these types of data. We study the usability of GFMs in cybersecurity through the lens of one specific use case, namely lateral movement detection. Using a pre-trained GFM, we build a detector that reaches state-of-the-art performance without requiring any training on domain-specific data. This case study thus provides compelling evidence of the potential of GFMs for cybersecurity. </t>
+  </si>
+  <si>
+    <t>Investigating cybersecurity incidents using large language models in latest-generation wireless networks</t>
+  </si>
+  <si>
+    <t>The purpose of research: Detection of cybersecurity incidents and analysis of decision support and assessment of the effectiveness of measures to counter information security threats based on modern generative models. The methods of research: Emulation of signal propagation data in MIMO systems, synthesis of adversarial examples, execution of adversarial attacks on machine learning models, fine tuning of large language models for detecting adversarial attacks, explainability of decisions on detecting cybersecurity incidents based on the prompts technique. Scientific novelty: A binary classification of data poisoning attacks was performed using large language models, and the possibility of using large language models for investigating cybersecurity incidents in the latest generation wireless networks was investigated. The result of research: Fine-tuning of large language models was performed on the prepared data of the emulated wireless network segment. Six large language models were compared for detecting adversarial attacks, and the capabilities of explaining decisions made by a large language model were investigated. The Gemma-7b model showed the best results according to the metrics Precision = 0.89, Recall = 0.89 and F1-Score = 0.89. Based on various explainability prompts, the Gemma-7b model notes inconsistencies in the compromised data under study, performs feature importance analysis and provides various recommendations for mitigating the consequences of adversarial attacks. Large language models integrated with binary classifiers of network threats have significant potential for practical application in the field of cybersecurity incident investigation, decision support and assessing the effectiveness of measures to counter information security threats</t>
+  </si>
+  <si>
+    <t>The Evolution of Zero Trust Architecture (ZTA) from Concept to Implementation</t>
+  </si>
+  <si>
+    <t>Zero Trust Architecture (ZTA) is one of the paradigm changes in cybersecurity, from the traditional perimeter-based model to perimeterless. This article studies the core concepts of ZTA, its beginning, a few use cases and future trends. Emphasising the always verify and least privilege access, some key tenets of ZTA have grown to be integration technologies like Identity Management, Multi-Factor Authentication (MFA) and real-time analytics. ZTA is expected to strengthen cloud environments, education, work environments (including from home) while controlling other risks like lateral movement and insider threats. Despite ZTA's benefits, it comes with challenges in the form of complexity, performance overhead and vulnerabilities in the control plane. These require phased implementation and continuous refinement to keep up with evolving organisational needs and threat landscapes. Emerging technologies, such as Artificial Intelligence (AI) and Machine Learning (ML) will further automate policy enforcement and threat detection in keeping up with dynamic cyber threats.</t>
+  </si>
+  <si>
+    <t>Intelligent DoS and DDoS Detection: A Hybrid GRU-NTM Approach to Network Security</t>
+  </si>
+  <si>
+    <t>Detecting Denial of Service (DoS) and Distributed Denial of Service (DDoS) attacks remains a critical challenge in cybersecurity. This research introduces a hybrid deep learning model combining Gated Recurrent Units (GRUs) and a Neural Turing Machine (NTM) for enhanced intrusion detection. Trained on the UNSW-NB15 and BoT-IoT datasets, the model employs GRU layers for sequential data processing and an NTM for long-term pattern recognition. The proposed approach achieves 99% accuracy in distinguishing between normal, DoS, and DDoS traffic. These findings offer promising advancements in real-time threat detection and contribute to improved network security across various domains.</t>
+  </si>
+  <si>
+    <t>WeiDetect: Weibull Distribution-Based Defense against Poisoning Attacks in Federated Learning for Network Intrusion Detection Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In the era of data expansion, ensuring data privacy has become increasingly critical, posing significant challenges to traditional AI-based applications. In addition, the increasing adoption of IoT devices has introduced significant cybersecurity challenges, making traditional Network Intrusion Detection Systems (NIDS) less effective against evolving threats, and privacy concerns and regulatory restrictions limit their deployment. Federated Learning (FL) has emerged as a promising solution, allowing decentralized model training while maintaining data privacy to solve these issues. However, despite implementing privacy-preserving technologies, FL systems remain vulnerable to adversarial attacks. Furthermore, data distribution among clients is not heterogeneous in the FL scenario. We propose WeiDetect, a two-phase, server-side defense mechanism for FL-based NIDS that detects malicious participants to address these challenges. In the first phase, local models are evaluated using a validation dataset to generate validation scores. These scores are then analyzed using a Weibull distribution, identifying and removing malicious models. We conducted experiments to evaluate the effectiveness of our approach in diverse attack settings. Our evaluation included two popular datasets, CIC-Darknet2020 and CSE-CIC-IDS2018, tested under non-IID data distributions. Our findings highlight that WeiDetect outperforms state-of-the-art defense approaches, improving higher target class recall up to 70% and enhancing the global model's F1 score by 1% to 14%. </t>
+  </si>
+  <si>
+    <t>Hierarchical Local-Global Feature Learning for Few-shot Malicious Traffic Detection</t>
+  </si>
+  <si>
+    <t>With the rapid growth of internet traffic, malicious network attacks have become increasingly frequent and sophisticated, posing significant threats to global cybersecurity. Traditional detection methods, including rule-based and machine learning-based approaches, struggle to accurately identify emerging threats, particularly in scenarios with limited samples. While recent advances in few-shot learning have partially addressed the data scarcity issue, existing methods still exhibit high false positive rates and lack the capability to effectively capture crucial local traffic patterns. In this paper, we propose HLoG, a novel hierarchical few-shot malicious traffic detection framework that leverages both local and global features extracted from network sessions. HLoG employs a sliding-window approach to segment sessions into phases, capturing fine-grained local interaction patterns through hierarchical bidirectional GRU encoding, while simultaneously modeling global contextual dependencies. We further design a session similarity assessment module that integrates local similarity with global self-attention-enhanced representations, achieving accurate and robust few-shot traffic classification. Comprehensive experiments on three meticulously reconstructed datasets demonstrate that HLoG significantly outperforms existing state-of-the-art methods. Particularly, HLoG achieves superior recall rates while substantially reducing false positives, highlighting its effectiveness and practical value in real-world cybersecurity applications.</t>
+  </si>
+  <si>
+    <t>Accelerating IoV Intrusion Detection: Benchmarking GPU-Accelerated vs CPU-Based ML Libraries</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The Internet of Vehicles (IoV) may face challenging cybersecurity attacks that may require sophisticated intrusion detection systems, necessitating a rapid development and response system. This research investigates the performance advantages of GPU-accelerated libraries (cuML) compared to traditional CPU-based implementations (scikit-learn), focusing on the speed and efficiency required for machine learning models used in IoV threat detection environments. The comprehensive evaluations conducted employ four machine learning approaches (Random Forest, KNN, Logistic Regression, XGBoost) across three distinct IoV security datasets (OTIDS, GIDS, CICIoV2024). Our findings demonstrate that GPU-accelerated implementations dramatically improved computational efficiency, with training times reduced by a factor of up to 159 and prediction speeds accelerated by up to 95 times compared to traditional CPU processing, all while preserving detection accuracy. This remarkable performance breakthrough empowers researchers and security specialists to harness GPU acceleration for creating faster, more effective threat detection systems that meet the urgent real-time security demands of today's connected vehicle networks.</t>
+  </si>
+  <si>
+    <t>Adaptive Federated Learning with Functional Encryption: A Comparison of Classical and Quantum-safe Options</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federated Learning (FL) is a collaborative method for training machine learning models while preserving the confidentiality of the participants' training data. Nevertheless, FL is vulnerable to reconstruction attacks that exploit shared parameters to reveal private training data. In this paper, we address this issue in the cybersecurity domain by applying Multi-Input Functional Encryption (MIFE) to a recent FL implementation for training ML-based network intrusion detection systems. We assess both classical and post-quantum solutions in terms of memory cost and computational overhead in the FL process, highlighting their impact on convergence time. </t>
+  </si>
+  <si>
+    <t>Methodology for Detecting Energy Anomalies due to Multi-Replay Attacks on Electric Vehicle Charging Infrastructure</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The increasing deployment of Electric Vehicle Charging Infrastructures (EVCIs) introduces cybersecurity challenges, particularly due to inherent vulnerabilities, making them susceptible to cyberattacks. The vulnerable points in EVCI are charging ports, which serve as the links between the EVs and the EVCI as they transfer the data along with the power. Data spoofing attacks targeting these ports can compromise security, reliability, and overall system performance by introducing anomalies in operational data. An efficient method for identifying the charging port current magnitude variations is presented in this research. The MATLAB/SIMULINK environment simulates an EVCI system for various data generating scenarios. A Temporal Convolution Network - Autoencoder (TCN-AE) model is used in training the multivariate time series data of EVCI and reconstructing it. The abnormalities in data are that various charging port current magnitudes are replaced with their respective data of different durations, thus enabling the replay attack scenarios. To detect anomalies, the error between the original and reconstructed data is computed, and these error values are used for detecting the anomalies. With the help of the mean vector and covariance matrices of the errors, the anomaly score is computed in the form of Mahalanobis distance. The threshold is obtained from the short sub-sequence of the errors and optimized for the whole time series data. The obtained optimal threshold is compared with the anomaly score to detect the anomaly. The model demonstrates robust performance in data reconstruction by identifying anomalies with an accuracy of 99.64%, to enhance the reliability and security in operations of EVCI. </t>
+  </si>
+  <si>
+    <t>Training Large Language Models for Advanced Typosquatting Detection</t>
+  </si>
+  <si>
+    <t>Typosquatting is a long-standing cyber threat that exploits human error in typing URLs to deceive users, distribute malware, and conduct phishing attacks. With the proliferation of domain names and new Top-Level Domains (TLDs), typosquatting techniques have grown more sophisticated, posing significant risks to individuals, businesses, and national cybersecurity infrastructure. Traditional detection methods primarily focus on well-known impersonation patterns, leaving gaps in identifying more complex attacks. This study introduces a novel approach leveraging large language models (LLMs) to enhance typosquatting detection. By training an LLM on character-level transformations and pattern-based heuristics rather than domain-specific data, a more adaptable and resilient detection mechanism develops. Experimental results indicate that the Phi-4 14B model outperformed other tested models when properly fine tuned achieving a 98% accuracy rate with only a few thousand training samples. This research highlights the potential of LLMs in cybersecurity applications, specifically in mitigating domain-based deception tactics, and provides insights into optimizing machine learning strategies for threat detection.</t>
+  </si>
+  <si>
+    <t>Redefining Network Topology in Complex Systems: Merging Centrality Metrics, Spectral Theory, and Diffusion Dynamics</t>
+  </si>
+  <si>
+    <t>This paper introduces a novel framework that combines traditional centrality measures with eigenvalue spectra and diffusion processes for a more comprehensive analysis of complex networks. While centrality measures such as degree, closeness, and betweenness have been commonly used to assess nodal importance, they provide limited insight into dynamic network behaviors. By incorporating eigenvalue analysis, which evaluates network robustness and connectivity through spectral properties, and diffusion processes that model information flow, this framework offers a deeper understanding of how networks function under dynamic conditions. Applied to synthetic networks, the approach identifies key nodes not only by centrality but also by their role in diffusion dynamics and vulnerability points, offering a multi-dimensional view that traditional methods alone cannot. This integrated analysis enables a more precise identification of critical nodes and potential weaknesses, with implications for improving network resilience in fields ranging from epidemiology to cybersecurity. Keywords: Centrality measures, eigenvalue spectra, diffusion processes, network analysis, network robustness, information flow, synthetic networks.</t>
+  </si>
+  <si>
+    <t>Advancing CAN Network Security through RBM-Based Synthetic Attack Data Generation for Intrusion Detection Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rapid development of network technologies and industrial intelligence has augmented the connectivity and intelligence within the automotive industry. Notably, in the Internet of Vehicles (IoV), the Controller Area Network (CAN), which is crucial for the communication of electronic control units but lacks inbuilt security measures, has become extremely vulnerable to severe cybersecurity threats. Meanwhile, the efficacy of Intrusion Detection Systems (IDS) is hampered by the scarcity of sufficient attack data for robust model training. To overcome this limitation, we introduce a novel methodology leveraging the Restricted Boltzmann Machine (RBM) to generate synthetic CAN attack data, thereby producing training datasets with a more balanced sample distribution. Specifically, we design a CAN Data Processing Module for transforming raw CAN data into an RBM-trainable format, and a Negative Sample Generation Module to generate data reflecting the distribution of CAN data frames denoting network intrusions. Experimental results show the generated data significantly improves IDS performance, with CANet accuracy rising from 0.6477 to 0.9725 and EfficientNet from 0.1067 to 0.1555. Code is available at https://github.com/wangkai-tech23/CANDataSynthetic. </t>
+  </si>
+  <si>
+    <t>Power Networks SCADA Communication Cybersecurity, A Qiskit Implementation</t>
+  </si>
+  <si>
+    <t>The cyber-physical system of electricity power networks utilizes supervisory control and data acquisition systems (SCADA), which are inherently vulnerable to cyber threats if usually connected with the internet technology (IT). Power system operations are conducted through communication systems that are mapped to standards, protocols, ports, and addresses. Real-time situational awareness is a standard term with implications and applications in both power systems and cybersecurity. In the plausible quantum world (Q-world), conventional approaches will likely face new challenges. The unique art of transmitting a quantum state from one place, Alice, to another, Bob, is known as quantum communication. Quantum communication for SCADA communication in a plausible quantum era thus obviously entails wired communication through optical fiber networks complying with the typical cybersecurity criteria of confidentiality, integrity, and availability for classical internet technology unless a quantum internet (qinternet) transpires practically. When combined with the reverse order of AIC for operational technology, the cybersecurity criteria for power networks' critical infrastructure drill down to more specific sub-areas. Unlike other communication modes, such as information technology (IT) in broadband internet connections, SCADA for power networks, one of the critical infrastructures, is intricately intertwined with operations technology (OT), which significantly increases complexity. Though it is desirable to have a barrier called a demilitarized zone (DMZ), some overlap is inevitable. This paper highlights the opportunities and challenges in securing SCADA communication in the plausible quantum computing and communication regime, along with a corresponding integrated Qiskit implementation for possible future framework development.</t>
+  </si>
+  <si>
+    <t>EVSOAR: Security Orchestration, Automation and Response via EV Charging Stations</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Vehicle cybersecurity has emerged as a critical concern, driven by the innovation in the automotive industry, e.g., automomous, electric, or connnected vehicles. Current efforts to address these challenges are constrained by the limited computational resources of vehicles and the reliance on connected infrastructures. This motivated the foundation of Vehicle Security Operations Centers (VSOCs) that extend IT-based Security Operations Centers (SOCs) to cover the entire automotive ecosystem, both the in-vehicle and off-vehicle scopes. Security Orchestration, Automation, and Response (SOAR) tools are considered key for impelementing an effective cybersecurity solution. However, existing state-of-the-art solutions depend on infrastructure networks such as 4G, 5G, and WiFi, which often face scalability and congestion issues. To address these limitations, we propose a novel SOAR architecture EVSOAR that leverages the EV charging stations for connectivity and computing to enhance vehicle cybersecurity. Our EV-specific SOAR architecture enables real-time analysis and automated responses to cybersecurity threats closer to the EV, reducing the cellular latency, bandwidth, and interference limitations. Our experimental results demonstrate a significant improvement in latency, stability, and scalability through the infrastructure and the capacity to deploy computationally intensive applications, that are otherwise infeasible within the resource constraints of individual vehicles. </t>
+  </si>
+  <si>
+    <t>Assessment of Cyberattack Detection-Isolation Algorithm for CAV Platoons Using SUMO</t>
+  </si>
+  <si>
+    <t>A Connected Autonomous Vehicle (CAV) platoon in an evolving real-world driving environment relies strongly on accurate vehicle-to-vehicle (V2V) and vehicle-to-infrastructure (V2I) communication for its safe and efficient operation. However, a cyberattack on this communication network can corrupt the appropriate control actions, tamper with system measurement, and drive the platoon to unsafe or undesired conditions. As a first step toward practicable resilience against such V2V-V2I attacks, in this paper, we implemented a unified V2V-V2I cyberattack detection scheme and a V2I isolation scheme for a CAV platoon under changing driving conditions in Simulation of Urban MObility (SUMO). The implemented algorithm utilizes vehicle-specific residual generators that are designed based on analytical disturbance-to-state stability, robustness, and sensitivity performance constraints. Our case studies include two driving scenarios where highway driving is simulated using the Next-Generation Simulation (NGSIM) data and urban driving follows the benchmark EPA Urban Dynamometer Driving Schedule (UDDS). The results validate the applicability of the algorithm to ensure CAV cybersecurity and demonstrate the promising potential for practical test-bed implementation in the future.</t>
+  </si>
+  <si>
+    <t>Quantum Computing and Cybersecurity Education: A Novel Curriculum for Enhancing Graduate STEM Learning</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Quantum computing is an emerging paradigm with the potential to transform numerous application areas by addressing problems considered intractable in the classical domain. However, its integration into cyberspace introduces significant security and privacy challenges. The exponential rise in cyber attacks, further complicated by quantum capabilities, poses serious risks to financial systems and national security. The scope of quantum threats extends beyond traditional software, operating system, and network vulnerabilities, necessitating a shift in cybersecurity education. Traditional cybersecurity education, often reliant on didactic methods, lacks hands on, student centered learning experiences necessary to prepare students for these evolving challenges. There is an urgent need for curricula that address both classical and quantum security threats through experiential learning. In this work, we present the design and evaluation of EE 597: Introduction to Hardware Security, a graduate level course integrating hands-on quantum security learning with classical security concepts through simulations and cloud-based quantum hardware. Unlike conventional courses focused on quantum threats to cryptographic systems, EE 597 explores security challenges specific to quantum computing itself. We employ a mixed-methods evaluation using pre and post surveys to assess student learning outcomes and engagement. Results indicate significant improvements in students' understanding of quantum and hardware security, with strong positive feedback on course structure and remote instruction (mean scores: 3.33 to 3.83 on a 4 point scale). </t>
+  </si>
+  <si>
+    <t>Domination in Graph Theory: A Bibliometric Analysis of Research Trends, Collaboration and Citation Networks</t>
+  </si>
+  <si>
+    <t>This study conducts a comprehensive bibliometric analysis of research on domination in graph theory from 1961 to 2024, based on Scopus-indexed publications retrieved using the query (dominating OR domination) AND graph. The analysis examines publication trends, key contributors, collaboration patterns, citation impact, and emerging research themes. Results indicate a significant and sustained increase in research output, particularly in recent decades. Henning, M.A., Hedetniemi, S.T., and Haynes, T.W. are identified as the most highly cited researchers, underscoring their foundational contributions to the field. Co-authorship network analysis reveals strong international collaborations, with Sheikhholeslami, S.M. exhibiting the highest total link strength, while the United States emerges as the leading hub for global research partnerships. Keyword co-occurrence analysis identifies four major research clusters: graph algorithms, graph-theoretic foundations, domination variants, and binary graph operations. Notably, recent studies increasingly focus on how domination properties evolve under different graph operations. Citation network analysis confirms the enduring influence of foundational studies while highlighting a shift towards computational and applied methodologies. These findings highlight the transition from theoretical to applied research, emphasizing the role of advanced algorithms, interdisciplinary approaches, and large-scale computational techniques. Future research directions should explore machine learning-based optimization, domination in evolving networks, and applications in cybersecurity, bioinformatics, and large-scale social networks.</t>
+  </si>
+  <si>
+    <t>PacketCLIP: Multi-Modal Embedding of Network Traffic and Language for Cybersecurity Reasoning</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Traffic classification is vital for cybersecurity, yet encrypted traffic poses significant challenges. We present PacketCLIP, a multi-modal framework combining packet data with natural language semantics through contrastive pretraining and hierarchical Graph Neural Network (GNN) reasoning. PacketCLIP integrates semantic reasoning with efficient classification, enabling robust detection of anomalies in encrypted network flows. By aligning textual descriptions with packet behaviors, it offers enhanced interpretability, scalability, and practical applicability across diverse security scenarios. PacketCLIP achieves a 95% mean AUC, outperforms baselines by 11.6%, and reduces model size by 92%, making it ideal for real-time anomaly detection. By bridging advanced machine learning techniques and practical cybersecurity needs, PacketCLIP provides a foundation for scalable, efficient, and interpretable solutions to tackle encrypted traffic classification and network intrusion detection challenges in resource-constrained environments.</t>
+  </si>
+  <si>
+    <t>Network Anomaly Detection for IoT Using Hyperdimensional Computing on NSL-KDD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">With the rapid growth of IoT devices, ensuring robust network security has become a critical challenge. Traditional intrusion detection systems (IDSs) often face limitations in detecting sophisticated attacks within high-dimensional and complex data environments. This paper presents a novel approach to network anomaly detection using hyperdimensional computing (HDC) techniques, specifically applied to the NSL-KDD dataset. The proposed method leverages the efficiency of HDC in processing large-scale data to identify both known and unknown attack patterns. The model achieved an accuracy of 91.55% on the KDDTrain+ subset, outperforming traditional approaches. These comparative evaluations underscore the model's superior performance, highlighting its potential in advancing anomaly detection for IoT networks and contributing to more secure and intelligent cybersecurity solutions. </t>
+  </si>
+  <si>
+    <t>A Kolmogorov-Arnold Network for Explainable Detection of Cyberattacks on EV Chargers</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The increasing adoption of Electric Vehicles (EVs) and the expansion of charging infrastructure and their reliance on communication expose Electric Vehicle Supply Equipment (EVSE) to cyberattacks. This paper presents a novel Kolmogorov-Arnold Network (KAN)-based framework for detecting cyberattacks on EV chargers using only power consumption measurements. Leveraging the KAN's capability to model nonlinear, high-dimensional functions and its inherently interpretable architecture, the framework effectively differentiates between normal and malicious charging scenarios. The model is trained offline on a comprehensive dataset containing over 100,000 cyberattack cases generated through an experimental setup. Once trained, the KAN model can be deployed within individual chargers for real-time detection of abnormal charging behaviors indicative of cyberattacks. Our results demonstrate that the proposed KAN-based approach can accurately detect cyberattacks on EV chargers with Precision and F1-score of 99% and 92%, respectively, outperforming existing detection methods. Additionally, the proposed KANs's enable the extraction of mathematical formulas representing KAN's detection decisions, addressing interpretability, a key challenge in deep learning-based cybersecurity frameworks. This work marks a significant step toward building secure and explainable EV charging infrastructure.</t>
+  </si>
+  <si>
+    <t>The Road Less Traveled: Investigating Robustness and Explainability in CNN Malware Detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Machine learning has become a key tool in cybersecurity, improving both attack strategies and defense mechanisms. Deep learning models, particularly Convolutional Neural Networks (CNNs), have demonstrated high accuracy in detecting malware images generated from binary data. However, the decision-making process of these black-box models remains difficult to interpret. This study addresses this challenge by integrating quantitative analysis with explainability tools such as Occlusion Maps, HiResCAM, and SHAP to better understand CNN behavior in malware classification. We further demonstrate that obfuscation techniques can reduce model accuracy by up to 50%, and propose a mitigation strategy to enhance robustness. Additionally, we analyze heatmaps from multiple tests and outline a methodology for identification of artifacts, aiding researchers in conducting detailed manual investigations. This work contributes to improving the interpretability and resilience of deep learning-based intrusion detection systems </t>
+  </si>
+  <si>
+    <t>CAGN-GAT Fusion: A Hybrid Contrastive Attentive Graph Neural Network for Network Intrusion Detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cybersecurity threats are growing, making network intrusion detection essential. Traditional machine learning models remain effective in resource-limited environments due to their efficiency, requiring fewer parameters and less computational time. However, handling short and highly imbalanced datasets remains challenging. In this study, we propose the fusion of a Contrastive Attentive Graph Network and Graph Attention Network (CAGN-GAT Fusion) and benchmark it against 15 other models, including both Graph Neural Networks (GNNs) and traditional ML models. Our evaluation is conducted on four benchmark datasets (KDD-CUP-1999, NSL-KDD, UNSW-NB15, and CICIDS2017) using a short and proportionally imbalanced dataset with a constant size of 5000 samples to ensure fairness in comparison. Results show that CAGN-GAT Fusion demonstrates stable and competitive accuracy, recall, and F1-score, even though it does not achieve the highest performance in every dataset. Our analysis also highlights the impact of adaptive graph construction techniques, including small changes in connections (edge perturbation) and selective hiding of features (feature masking), improving detection performance. The findings confirm that GNNs, particularly CAGN-GAT Fusion, are robust and computationally efficient, making them well-suited for resource-constrained environments. Future work will explore GraphSAGE layers and multiview graph construction techniques to further enhance adaptability and detection accuracy.</t>
+  </si>
+  <si>
+    <t>Towards Zero Touch Networks: Cross-Layer Automated Security Solutions for 6G Wireless Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The transition from 5G to 6G mobile networks necessitates network automation to meet the escalating demands for high data rates, ultra-low latency, and integrated technology. Recently, Zero-Touch Networks (ZTNs), driven by Artificial Intelligence (AI) and Machine Learning (ML), are designed to automate the entire lifecycle of network operations with minimal human intervention, presenting a promising solution for enhancing automation in 5G/6G networks. However, the implementation of ZTNs brings forth the need for autonomous and robust cybersecurity solutions, as ZTNs rely heavily on automation. AI/ML algorithms are widely used to develop cybersecurity mechanisms, but require substantial specialized expertise and encounter model drift issues, posing significant challenges in developing autonomous cybersecurity measures. Therefore, this paper proposes an automated security framework targeting Physical Layer Authentication (PLA) and Cross-Layer Intrusion Detection Systems (CLIDS) to address security concerns at multiple Internet protocol layers. The proposed framework employs drift-adaptive online learning techniques and a novel enhanced Successive Halving (SH)-based Automated ML (AutoML) method to automatically generate optimized ML models for dynamic networking environments. Experimental results illustrate that the proposed framework achieves high performance on the public Radio Frequency (RF) fingerprinting and the Canadian Institute for CICIDS2017 datasets, showcasing its effectiveness in addressing PLA and CLIDS tasks within dynamic and complex networking environments. Furthermore, the paper explores open challenges and research directions in the 5G/6G cybersecurity domain. This framework represents a significant advancement towards fully autonomous and secure 6G networks, paving the way for future innovations in network automation and cybersecurity.</t>
+  </si>
+  <si>
+    <t>SSD: A State-based Stealthy Backdoor Attack For Navigation System in UAV Route Planning</t>
+  </si>
+  <si>
+    <t>Unmanned aerial vehicles (UAVs) are increasingly employed to perform high-risk tasks that require minimal human intervention. However, UAVs face escalating cybersecurity threats, particularly from GNSS spoofing attacks. While previous studies have extensively investigated the impacts of GNSS spoofing on UAVs, few have focused on its effects on specific tasks. Moreover, the influence of UAV motion states on the assessment of network security risks is often overlooked. To address these gaps, we first provide a detailed evaluation of how motion states affect the effectiveness of network attacks. We demonstrate that nonlinear motion states not only enhance the effectiveness of position spoofing in GNSS spoofing attacks but also reduce the probability of speed-related attack detection. Building upon this, we propose a state-triggered backdoor attack method (SSD) to deceive GNSS systems and assess its risk to trajectory planning tasks. Extensive validation of SSD's effectiveness and stealthiness is conducted. Experimental results show that, with appropriately tuned hyperparameters, SSD significantly increases positioning errors and the risk of task failure, while maintaining 100% stealth across three state-of-the-art detectors</t>
+  </si>
+  <si>
+    <t>Rebalancing the Scales: A Systematic Mapping Study of Generative Adversarial Networks (GANs) in Addressing Data Imbalance</t>
+  </si>
+  <si>
+    <t>Machine learning algorithms are used in diverse domains, many of which face significant challenges due to data imbalance. Studies have explored various approaches to address the issue, like data preprocessing, cost-sensitive learning, and ensemble methods. Generative Adversarial Networks (GANs) showed immense potential as a data preprocessing technique that generates good quality synthetic data. This study employs a systematic mapping methodology to analyze 3041 papers on GAN-based sampling techniques for imbalanced data sourced from four digital libraries. A filtering process identified 100 key studies spanning domains such as healthcare, finance, and cybersecurity. Through comprehensive quantitative analysis, this research introduces three categorization mappings as application domains, GAN techniques, and GAN variants used to handle the imbalanced nature of the data. GAN-based over-sampling emerges as an effective preprocessing method. Advanced architectures and tailored frameworks helped GANs to improve further in the case of data imbalance. GAN variants like vanilla GAN, CTGAN, and CGAN show great adaptability in structured imbalanced data cases. Interest in GANs for imbalanced data has grown tremendously, touching a peak in recent years, with journals and conferences playing crucial roles in transmitting foundational theories and practical applications. While with these advances, none of the reviewed studies explicitly explore hybridized GAN frameworks with diffusion models or reinforcement learning techniques. This gap leads to a future research idea develop innovative approaches for effectively handling data imbalance.</t>
+  </si>
+  <si>
+    <t>Cyber security of OT networks: A tutorial and overview</t>
+  </si>
+  <si>
+    <t>This manuscript explores the cybersecurity challenges of Operational Technology (OT) networks, focusing on their critical role in industrial environments such as manufacturing, energy, and utilities. As OT systems increasingly integrate with Information Technology (IT) systems due to Industry 4.0 initiatives, they become more vulnerable to cyberattacks, which pose risks not only to data but also to physical infrastructure. The study examines key components of OT systems, such as SCADA (Supervisory Control and Data Acquisition), PLCs (Programmable Logic Controllers), and RTUs (Remote Terminal Units), and analyzes recent cyberattacks targeting OT environments. Furthermore, it highlights the security concerns arising from the convergence of IT and OT systems, examining attack vectors and the growing threats posed by malware, ransomware, and nation-state actors. Finally, the paper discusses modern approaches and tools used to secure these environments, providing insights into improving the cybersecurity posture of OT networks.</t>
+  </si>
+  <si>
+    <t>Hybrid Machine Learning Models for Intrusion Detection in IoT: Leveraging a Real-World IoT Dataset</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rapid growth of the Internet of Things (IoT) has revolutionized industries, enabling unprecedented connectivity and functionality. However, this expansion also increases vulnerabilities, exposing IoT networks to increasingly sophisticated cyberattacks. Intrusion Detection Systems (IDS) are crucial for mitigating these threats, and recent advancements in Machine Learning (ML) offer promising avenues for improvement. This research explores a hybrid approach, combining several standalone ML models such as Random Forest (RF), XGBoost, K-Nearest Neighbors (KNN), and AdaBoost, in a voting-based hybrid classifier for effective IoT intrusion detection. This ensemble method leverages the strengths of individual algorithms to enhance accuracy and address challenges related to data complexity and scalability. Using the widely-cited IoT-23 dataset, a prominent benchmark in IoT cybersecurity research, we evaluate our hybrid classifiers for both binary and multi-class intrusion detection problems, ensuring a fair comparison with existing literature. Results demonstrate that our proposed hybrid models, designed for robustness and scalability, outperform standalone approaches in IoT environments. This work contributes to the development of advanced, intelligent IDS frameworks capable of addressing evolving cyber threats. </t>
+  </si>
+  <si>
+    <t>Enhanced Anomaly Detection in IoMT Networks using Ensemble AI Models on the CICIoMT2024 Dataset</t>
+  </si>
+  <si>
+    <t>The rapid proliferation of Internet of Medical Things (IoMT) devices in healthcare has introduced unique cybersecurity challenges, primarily due to the diverse communication protocols and critical nature of these devices This research aims to develop an advanced, real-time anomaly detection framework tailored for IoMT network traffic, leveraging AI/ML models and the CICIoMT2024 dataset By integrating multi-protocol (MQTT, WiFi), attack-specific (DoS, DDoS), time-series (active/idle states), and device-specific (Bluetooth) data, our study captures a comprehensive range of IoMT interactions As part of our data analysis, various machine learning techniques are employed which include an ensemble model using XGBoost for improved performance against specific attack types, sequential models comprised of LSTM and CNN-LSTM that leverage time dependencies, and unsupervised models such as Autoencoders and Isolation Forest that are good in general anomaly detection The results of the experiment prove with an ensemble model lowers false positive rates and reduced detections.</t>
+  </si>
+  <si>
+    <t>Evaluating the Potential of Quantum Machine Learning in Cybersecurity: A Case-Study on PCA-based Intrusion Detection Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantum computing promises to revolutionize our understanding of the limits of computation, and its implications in cryptography have long been evident. Today, cryptographers are actively devising post-quantum solutions to counter the threats posed by quantum-enabled adversaries. Meanwhile, quantum scientists are innovating quantum protocols to empower defenders. However, the broader impact of quantum computing and quantum machine learning (QML) on other cybersecurity domains still needs to be explored. In this work, we investigate the potential impact of QML on cybersecurity applications of traditional ML. First, we explore the potential advantages of quantum computing in machine learning problems specifically related to cybersecurity. Then, we describe a methodology to quantify the future impact of fault-tolerant QML algorithms on real-world problems. As a case study, we apply our approach to standard methods and datasets in network intrusion detection, one of the most studied applications of machine learning in cybersecurity. Our results provide insight into the conditions for obtaining a quantum advantage and the need for future quantum hardware and software advancements. </t>
+  </si>
+  <si>
+    <t>A Computational Model for Ransomware Detection Using Cross-Domain Entropy Signatures</t>
+  </si>
+  <si>
+    <t>Detecting encryption-driven cyber threats remains a large challenge due to the evolving techniques employed to evade traditional detection mechanisms. An entropy-based computational framework was introduced to analyze multi-domain system variations, enabling the identification of malicious encryption behaviors through entropy deviations. By integrating entropy patterns across file operations, memory allocations, and network transmissions, a detection methodology was developed to differentiate between benign and ransomware-induced entropy shifts. A mathematical model was formulated to quantify entropy dynamics, incorporating time-dependent variations and weighted domain contributions to enhance anomaly detection. Experimental evaluations demonstrated that the proposed approach achieved high accuracy across diverse ransomware families while maintaining low false positive rates. Computational efficiency analysis indicated minimal processing overhead, suggesting feasibility for real-time implementation in security-sensitive environments. The study highlighted entropy fluctuations as a useful indicator for identifying malicious encryption processes, reinforcing entropy-driven methodologies as a viable component of cybersecurity strategies.</t>
+  </si>
+  <si>
+    <t>Federated Learning-Driven Cybersecurity Framework for IoT Networks with Privacy-Preserving and Real-Time Threat Detection Capabilities</t>
+  </si>
+  <si>
+    <t>The rapid expansion of the Internet of Things (IoT) ecosystem has transformed various sectors but has also introduced significant cybersecurity challenges. Traditional centralized security methods often struggle to balance privacy preservation and real-time threat detection in IoT networks. To address these issues, this study proposes a Federated Learning-Driven Cybersecurity Framework designed specifically for IoT environments. The framework enables decentralized data processing by training models locally on edge devices, ensuring data privacy. Secure aggregation of these locally trained models is achieved using homomorphic encryption, allowing collaborative learning without exposing sensitive information. The proposed framework utilizes recurrent neural networks (RNNs) for anomaly detection, optimized for resource-constrained IoT networks. Experimental results demonstrate that the system effectively detects complex cyber threats, including distributed denial-of-service (DDoS) attacks, with over 98% accuracy. Additionally, it improves energy efficiency by reducing resource consumption by 20% compared to centralized approaches. This research addresses critical gaps in IoT cybersecurity by integrating federated learning with advanced threat detection techniques. The framework offers a scalable and privacy-preserving solution adaptable to various IoT applications. Future work will explore the integration of blockchain for transparent model aggregation and quantum-resistant cryptographic methods to further enhance security in evolving technological landscapes.</t>
+  </si>
+  <si>
+    <t>Supply Chain Network Security Investment Strategies Based on Nonlinear Budget Constraints: The Moderating Roles of Market Share and Attack Risk</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In the context of the rapid development of digital supply chain networks, dealing with the increasing cybersecurity threats and formulating effective security investment strategies to defend against cyberattack risks are the core issues in supply chain management. Cybersecurity investment decision-making is a key strategic task in enterprise supply chain manage-ment. Traditional game theory models and linear programming methods make it challenging to deal with complex problems such as multi-party par-ticipation in the supply chain, resource constraints, and risk uncertainty, re-sulting in enterprises facing high risks and uncertainties in the field of cy-bersecurity. To effectively meet this challenge, this study proposes a nonlin-ear budget-constrained cybersecurity investment optimization model based on variational inequality and projection shrinkage algorithm. This method simulates the impact of market competition on security investment by intro-ducing market share variables, combining variational inequality and projec-tion shrinkage algorithm to solve the model, and analyzing the effect of dif-ferent variables such as budget constraints, cyberattack losses, and market share on supply chain network security. In numerical analysis, the model achieved high cybersecurity levels of 0.96 and 0.95 in the experimental sce-narios of two retailers and two demand markets, respectively, and the budget constraint analysis revealed the profound impact of budget constraints on cybersecurity investment. Through numerical experiments and comparative analysis, the effectiveness and operability of this method in improving sup-ply chain network security are verified.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Quantum-driven Zero Trust Framework with Dynamic Anomaly Detection in 7G Technology: A Neural Network Approach
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> As cyber threats become more complex, modern networks struggle to balance security, scalability, and computational efficiency. While quantum computing offers a promising solution, adoption is limited by scalability constraints, inefficiencies in data encoding, and high computational costs. To address these challenges, we propose the Quantum Neural Network-Enhanced Zero Trust Framework (QNN-ZTF), integrating Zero Trust Architecture, Intrusion Detection Systems, and Quantum Neural Networks (QNNs) for enhanced security. Leveraging superposition, entanglement, and variational optimization, QNN-ZTF enables real-time anomaly detection and adaptive policy enforcement. Key contributions include a hybrid quantum-classical architecture for scalability, dynamic anomaly scoring for improved detection accuracy, and quantum micro-segmentation to contain threats and restrict lateral movement. Evaluation results show improved cyber threat mitigation, demonstrating the framework's effectiveness in reducing false positives and response times. This research establishes a scalable, adaptive, and quantum-optimized cybersecurity model, advancing quantum-enhanced security for next-generation networks.</t>
+  </si>
+  <si>
+    <t>Network Intrusion Datasets: A Survey, Limitations, and Recommendations</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Data-driven cyberthreat detection has become a crucial defense technique in modern cybersecurity. Network defense, supported by Network Intrusion Detection Systems (NIDSs), has also increasingly adopted data-driven approaches, leading to greater reliance on data. Despite the importance of data, its scarcity has long been recognized as a major obstacle in NIDS research. In response, the community has published many new datasets recently. However, many of them remain largely unknown and unanalyzed, leaving researchers uncertain about their suitability for specific use cases. In this paper, we aim to address this knowledge gap by performing a systematic literature review (SLR) of 89 public datasets for NIDS research. Each dataset is comparatively analyzed across 13 key properties, and its potential applications are outlined. Beyond the review, we also discuss domain-specific challenges and common data limitations to facilitate a critical view on data quality. To aid in data selection, we conduct a dataset popularity analysis in contemporary state-of-the-art NIDS research. Furthermore, the paper presents best practices for dataset selection, generation, and usage. By providing a comprehensive overview of the domain and its data, this work aims to guide future research toward improving data quality and the robustness of NIDS solutions.</t>
+  </si>
+  <si>
+    <t>Can LLMs Hack Enterprise Networks? Autonomous Assumed Breach Penetration-Testing Active Directory Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Penetration-testing, while critical for validating defenses and uncovering vulnerabilities, is often limited by high operational costs and the scarcity of human expertise. This paper investigates the feasibility and effectiveness of using Large Language Model (LLM)-driven autonomous systems to address these challenges in real-world Microsoft Active Directory (AD) enterprise networks. Our novel prototype, cochise, represents the first demonstration of a fully autonomous, LLM-driven framework capable of compromising accounts within a real-life Microsoft AD testbed (GOAD). The evaluation deliberately utilizes GOAD to capture the intricate interactions and sometimes nondeterministic outcomes of live network pen-testing, moving beyond the limitations of synthetic benchmarks. We perform our empirical evaluation using five LLMs, comparing reasoning to non-reasoning models as well as including open-weight models. Through comprehensive quantitative and qualitative analysis, incorporating insights from cybersecurity experts, we demonstrate that autonomous LLMs can effectively conduct Assumed Breach simulations. Key findings highlight their ability to dynamically adapt attack strategies, perform inter-context attacks, and generate scenario-specific attack parameters. Cochise also exhibits robust self-correction mechanisms, automatically installing missing tools and rectifying invalid command generations. Critically, we find that the associated costs are competitive with those incurred by professional pen-testers, suggesting a path toward democratizing access to essential security testing for organizations with budgetary constraints. However, our research also illuminates existing limitations, including instances of LLM ``going down rabbit holes'', challenges in comprehensive information transfer between planning and execution modules, and critical safety concerns that necessitate human oversight. </t>
+  </si>
+  <si>
+    <t>Optimal Security Response to Network Intrusions in IT Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cybersecurity is one of the most pressing technological challenges of our time and requires measures from all sectors of society. A key measure is automated security response, which enables automated mitigation and recovery from cyber attacks. Significant strides toward such automation have been made due to the development of rule-based response systems. However, these systems have a critical drawback: they depend on domain experts to configure the rules, a process that is both error-prone and inefficient. Framing security response as an optimal control problem shows promise in addressing this limitation but introduces new challenges. Chief among them is bridging the gap between theoretical optimality and operational performance. Current response systems with theoretical optimality guarantees have only been validated analytically or in simulation, leaving their practical utility unproven. This thesis tackles the aforementioned challenges by developing a practical methodology for optimal security response in IT infrastructures. It encompasses two systems. First, it includes an emulation system that replicates key components of the target infrastructure. We use this system to gather measurements and logs, based on which we identify a game-theoretic model. Second, it includes a simulation system where game-theoretic response strategies are optimized through stochastic approximation to meet a given objective, such as mitigating potential attacks while maintaining operational services. These strategies are then evaluated and refined in the emulation system to close the gap between theoretical and operational performance. We prove structural properties of optimal response strategies and derive efficient algorithms for computing them. This enables us to solve a previously unsolved problem: demonstrating optimal security response against network intrusions on an IT infrastructure.</t>
+  </si>
+  <si>
+    <t>CryptoDNA: A Machine Learning Paradigm for DDoS Detection in Healthcare IoT, Inspired by crypto jacking prevention Models</t>
+  </si>
+  <si>
+    <t>The rapid integration of the Internet of Things (IoT) and Internet of Medical (IoM) devices in the healthcare industry has markedly improved patient care and hospital operations but has concurrently brought substantial risks. Distributed Denial-of-Service (DDoS) attacks present significant dangers, jeopardizing operational stability and patient safety. This study introduces CryptoDNA, an innovative machine learning detection framework influenced by cryptojacking detection methods, designed to identify and alleviate DDoS attacks in healthcare IoT settings. The proposed approach relies on behavioral analytics, including atypical resource usage and network activity patterns. Key features derived from cryptojacking-inspired methodologies include entropy-based analysis of traffic, time-series monitoring of device performance, and dynamic anomaly detection. A lightweight architecture ensures inter-compatibility with resource-constrained IoT devices while maintaining high detection accuracy. The proposed architecture and model were tested in real-world and synthetic datasets to demonstrate the model's superior performance, achieving over 96% accuracy with minimal computational overhead. Comparative analysis reveals its resilience against emerging attack vectors and scalability across diverse device ecosystems. By bridging principles from cryptojacking and DDoS detection, CryptoDNA offers a robust, innovative solution to fortify the healthcare IoT landscape against evolving cyber threats and highlights the potential of interdisciplinary approaches in adaptive cybersecurity defense mechanisms for critical healthcare infrastructures</t>
+  </si>
+  <si>
+    <t>When Everyday Devices Become Weapons: A Closer Look at the Pager and Walkie-talkie Attacks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Battery-powered technologies like pagers and walkie-talkies have long been integral to civilian and military operations. However, the potential for such everyday devices to be weaponized has largely been underestimated in the realm of cybersecurity. In September 2024, Lebanon experienced a series of unprecedented, coordinated explosions triggered through compromised pagers and walkie-talkies, creating a new category of attack in the domain of cyber-physical warfare. This attack not only disrupted critical communication networks but also resulted in injuries, loss of life, and exposed significant national security vulnerabilities, prompting governments and organizations worldwide to reevaluate their cybersecurity frameworks. This article provides an in-depth investigation into the infamous Pager and Walkie-Talkie attacks, analyzing both technical and non-technical dimensions. Furthermore, the study extends its scope to explore vulnerabilities in other battery-powered infrastructures, such as battery management systems, highlighting their potential exploitation. Existing prevention and detection techniques are reviewed, with an emphasis on their limitations and the challenges they face in addressing emerging threats. Finally, the article discusses emerging methodologies, particularly focusing on the role of physical inspection, as a critical component of future security measures. This research aims to provide actionable insights to bolster the resilience of cyber-physical systems in an increasingly interconnected world. </t>
+  </si>
+  <si>
+    <t>TORCHLIGHT: Shedding LIGHT on Real-World Attacks on Cloudless IoT Devices Concealed within the Tor Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The rapidly expanding Internet of Things (IoT) landscape is shifting toward cloudless architectures, removing reliance on centralized cloud services but exposing devices directly to the internet and increasing their vulnerability to cyberattacks. Our research revealed an unexpected pattern of substantial Tor network traffic targeting cloudless IoT devices. suggesting that attackers are using Tor to anonymously exploit undisclosed vulnerabilities (possibly obtained from underground markets). To delve deeper into this phenomenon, we developed TORCHLIGHT, a tool designed to detect both known and unknown threats targeting cloudless IoT devices by analyzing Tor traffic. TORCHLIGHT filters traffic via specific IP patterns, strategically deploys virtual private server (VPS) nodes for cost-effective detection, and uses a chain-of-thought (CoT) process with large language models (LLMs) for accurate threat identification. Our results are significant: for the first time, we have demonstrated that attackers are indeed using Tor to conceal their identities while targeting cloudless IoT devices. Over a period of 12 months, TORCHLIGHT analyzed 26 TB of traffic, revealing 45 vulnerabilities, including 29 zero-day exploits with 25 CVE-IDs assigned (5 CRITICAL, 3 HIGH, 16 MEDIUM, and 1 LOW) and an estimated value of approximately $312,000. These vulnerabilities affect around 12.71 million devices across 148 countries, exposing them to severe risks such as information disclosure, authentication bypass, and arbitrary command execution. The findings have attracted significant attention, sparking widespread discussion in cybersecurity circles, reaching the top 25 on Hacker News, and generating over 190,000 views. </t>
+  </si>
+  <si>
+    <t>Using hypervisors to create a cyber polygon</t>
+  </si>
+  <si>
+    <t>Cyber polygon used to train cybersecurity professionals, test new security technologies and simulate attacks play an important role in ensuring cybersecurity. The creation of such training grounds is based on the use of hypervisors, which allow efficient management of virtual machines, isolating operating systems and resources of a physical computer from virtual machines, ensuring a high level of security and stability. The paper analyses various aspects of using hypervisors in cyber polygons, including types of hypervisors, their main functions, and the specifics of their use in modelling cyber threats. The article shows the ability of hypervisors to increase the efficiency of hardware resources, create complex virtual environments for detailed modelling of network structures and simulation of real situations in cyberspace</t>
+  </si>
+  <si>
+    <t>Adaptive Cybersecurity: Dynamically Retrainable Firewalls for Real-Time Network Protection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The growing complexity of cyber attacks has necessitated the evolution of firewall technologies from static models to adaptive, machine learning-driven systems. This research introduces "Dynamically Retrainable Firewalls", which respond to emerging threats in real-time. Unlike traditional firewalls that rely on static rules to inspect traffic, these advanced systems leverage machine learning algorithms to analyze network traffic pattern dynamically and identify threats. The study explores architectures such as micro-services and distributed systems for real-time adaptability, data sources for model retraining, and dynamic threat identification through reinforcement and continual learning. It also discusses strategies to improve performance, reduce latency, optimize resource utilization, and address integration issues with present-day concepts such as Zero Trust and mixed environments. By critically assessing the literature, analyzing case studies, and elucidating areas of future research, this work suggests dynamically retrainable firewalls as a more robust form of network security. Additionally, it considers emerging trends such as advancements in AI and quantum computing, ethical issues, and other regulatory questions surrounding future AI systems. These findings provide valuable information on the future state of adaptive cyber security, focusing on the need for proactive and adaptive measures that counter cyber threats that continue to evolve. </t>
+  </si>
+  <si>
+    <t>Integrating Cybersecurity in Predictive Cost-Benefit Power Scheduling: A DeepStack Model with Dynamic Defense Mechanism</t>
+  </si>
+  <si>
+    <t>This paper introduces a novel, deep learning-based predictive model tailored to address wind curtailment in contemporary power systems, while enhancing cybersecurity measures through the implementation of a Dynamic Defense Mechanism (DDM). The augmented BiLSTM architecture facilitates accurate short-term predictions for wind power. In addition, a ConvGAN-driven step for stochastic scenario generation and a hierarchical, multi-stage optimization framework, which includes cases with and without Battery Energy Storage (BES), significantly minimizes operational costs. The inclusion of DDM strategically alters network reactances, thereby obfuscating the system's operational parameters to deter cyber threats. This robust solution not only integrates wind power more efficiently into power grids, leveraging BES potential to improve the economic efficiency of the system, but also boosting the cyber security of the system. Validation using the Illinois 200-bus system demonstrates the model's potential, achieving a 98% accuracy in forecasting and substantial cost reductions of over 3.8%. The results underscore the dual benefits of enhancing system reliability and security through advanced deep learning architectures and the strategic application of cybersecurity measures.</t>
+  </si>
+  <si>
+    <t>A Novel Approach to Network Traffic Analysis: the HERA tool</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Cybersecurity threats highlight the need for robust network intrusion detection systems to identify malicious behaviour. These systems rely heavily on large datasets to train machine learning models capable of detecting patterns and predicting threats. In the past two decades, researchers have produced a multitude of datasets, however, some widely utilised recent datasets generated with CICFlowMeter contain inaccuracies. These result in flow generation and feature extraction inconsistencies, leading to skewed results and reduced system effectiveness. Other tools in this context lack ease of use, customizable feature sets, and flow labelling options. In this work, we introduce HERA, a new open-source tool that generates flow files and labelled or unlabelled datasets with user-defined features. Validated and tested with the UNSW-NB15 dataset, HERA demonstrated accurate flow and label generation.</t>
+  </si>
+  <si>
+    <t>Cybersecurity in Transportation Systems: Policies and Technology Directions</t>
+  </si>
+  <si>
+    <t>The transportation industry is experiencing vast digitalization as a plethora of technologies are being implemented to improve efficiency, functionality, and safety. Although technological advancements bring many benefits to transportation, integrating cyberspace across transportation sectors has introduced new and deliberate cyber threats. In the past, public agencies assumed digital infrastructure was secured since its vulnerabilities were unknown to adversaries. However, with the expansion of cyberspace, this assumption has become invalid. With the rapid advancement of wireless technologies, transportation systems are increasingly interconnected with both transportation and non-transportation networks in an internet-of-things ecosystem, expanding cyberspace in transportation and increasing threats and vulnerabilities. This study investigates some prominent reasons for the increase in cyber vulnerabilities in transportation. In addition, this study presents various collaborative strategies among stakeholders that could help improve cybersecurity in the transportation industry. These strategies address programmatic and policy aspects and suggest avenues for technological research and development. The latter highlights opportunities for future research to enhance the cybersecurity of transportation systems and infrastructure by leveraging hybrid approaches and emerging technologies.</t>
+  </si>
+  <si>
+    <t>CONTINUUM: Detecting APT Attacks through Spatial-Temporal Graph Neural Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Advanced Persistent Threats (APTs) represent a significant challenge in cybersecurity due to their sophisticated and stealthy nature. Traditional Intrusion Detection Systems (IDS) often fall short in detecting these multi-stage attacks. Recently, Graph Neural Networks (GNNs) have been employed to enhance IDS capabilities by analyzing the complex relationships within networked data. However, existing GNN-based solutions are hampered by high false positive rates and substantial resource consumption. In this paper, we present a novel IDS designed to detect APTs using a Spatio-Temporal Graph Neural Network Autoencoder. Our approach leverages spatial information to understand the interactions between entities within a graph and temporal information to capture the evolution of the graph over time. This dual perspective is crucial for identifying the sequential stages of APTs. Furthermore, to address privacy and scalability concerns, we deploy our architecture in a federated learning environment. This setup ensures that local data remains on-premise while encrypted model-weights are shared and aggregated using homomorphic encryption, maintaining data privacy and security. Our evaluation shows that this system effectively detects APTs with lower false positive rates and optimized resource usage compared to existing methods, highlighting the potential of spatio-temporal analysis and federated learning in enhancing cybersecurity defenses. </t>
+  </si>
+  <si>
+    <t>Predicting Vulnerability to Malware Using Machine Learning Models: A Study on Microsoft Windows Machines</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In an era of escalating cyber threats, malware poses significant risks to individuals and organizations, potentially leading to data breaches, system failures, and substantial financial losses. This study addresses the urgent need for effective malware detection strategies by leveraging Machine Learning (ML) techniques on extensive datasets collected from Microsoft Windows Defender. Our research aims to develop an advanced ML model that accurately predicts malware vulnerabilities based on the specific conditions of individual machines. Moving beyond traditional signature-based detection methods, we incorporate historical data and innovative feature engineering to enhance detection capabilities. This study makes several contributions: first, it advances existing malware detection techniques by employing sophisticated ML algorithms; second, it utilizes a large-scale, real-world dataset to ensure the applicability of findings; third, it highlights the importance of feature analysis in identifying key indicators of malware infections; and fourth, it proposes models that can be adapted for enterprise environments, offering a proactive approach to safeguarding extensive networks against emerging threats. We aim to improve cybersecurity resilience, providing critical insights for practitioners in the field and addressing the evolving challenges posed by malware in a digital landscape. Finally, discussions on results, insights, and conclusions are presented</t>
+  </si>
+  <si>
+    <t>BARTPredict: Empowering IoT Security with LLM-Driven Cyber Threat Prediction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The integration of Internet of Things (IoT) technology in various domains has led to operational advancements, but it has also introduced new vulnerabilities to cybersecurity threats, as evidenced by recent widespread cyberattacks on IoT devices. Intrusion detection systems are often reactive, triggered by specific patterns or anomalies observed within the network. To address this challenge, this work proposes a proactive approach to anticipate and preemptively mitigate malicious activities, aiming to prevent potential damage before it occurs. This paper proposes an innovative intrusion prediction framework empowered by Pre-trained Large Language Models (LLMs). The framework incorporates two LLMs: a fine-tuned Bidirectional and AutoRegressive Transformers (BART) model for predicting network traffic and a fine-tuned Bidirectional Encoder Representations from Transformers (BERT) model for evaluating the predicted traffic. By harnessing the bidirectional capabilities of BART the framework then identifies malicious packets among these predictions. Evaluated using the CICIoT2023 IoT attack dataset, our framework showcases a notable enhancement in predictive performance, attaining an impressive 98% overall accuracy, providing a powerful response to the cybersecurity challenges that confront IoT networks. </t>
+  </si>
+  <si>
+    <t>FAPL-DM-BC: A Secure and Scalable FL Framework with Adaptive Privacy and Dynamic Masking, Blockchain, and XAI for the IoVs</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The FAPL-DM-BC solution is a new FL-based privacy, security, and scalability solution for the Internet of Vehicles (IoV). It leverages Federated Adaptive Privacy-Aware Learning (FAPL) and Dynamic Masking (DM) to learn and adaptively change privacy policies in response to changing data sensitivity and state in real-time, for the optimal privacy-utility tradeoff. Secure Logging and Verification, Blockchain-based provenance and decentralized validation, and Cloud Microservices Secure Aggregation using FedAvg (Federated Averaging) and Secure Multi-Party Computation (SMPC). Two-model feedback, driven by Model-Agnostic Explainable AI (XAI), certifies local predictions and explanations to drive it to the next level of efficiency. Combining local feedback with world knowledge through a weighted mean computation, FAPL-DM-BC assures federated learning that is secure, scalable, and interpretable. Self-driving cars, traffic management, and forecasting, vehicular network cybersecurity in real-time, and smart cities are a few possible applications of this integrated, privacy-safe, and high-performance IoV platform.</t>
+  </si>
+  <si>
+    <t>State-of-the-art AI-based Learning Approaches for Deepfake Generation and Detection, Analyzing Opportunities, Threading through Pros, Cons, and Future Prospects</t>
+  </si>
+  <si>
+    <t>The rapid advancement of deepfake technologies, specifically designed to create incredibly lifelike facial imagery and video content, has ignited a remarkable level of interest and curiosity across many fields, including forensic analysis, cybersecurity and the innovative creation of digital characters. By harnessing the latest breakthroughs in deep learning methods, such as Generative Adversarial Networks, Variational Autoencoders, Few-Shot Learning Strategies, and Transformers, the outcomes achieved in generating deepfakes have been nothing short of astounding and transformative. Also, the ongoing evolution of detection technologies is being developed to counteract the potential for misuse associated with deepfakes, effectively addressing critical concerns that range from political manipulation to the dissemination of fake news and the ever-growing issue of cyberbullying. This comprehensive review paper meticulously investigates the most recent developments in deepfake generation and detection, including around 400 publications, providing an in-depth analysis of the cutting-edge innovations shaping this rapidly evolving landscape. Starting with a thorough examination of systematic literature review methodologies, we embark on a journey that delves into the complex technical intricacies inherent in the various techniques used for deepfake generation, comprehensively addressing the challenges faced, potential solutions available, and the nuanced details surrounding manipulation formulations. Subsequently, the paper is dedicated to accurately benchmarking leading approaches against prominent datasets, offering thorough assessments of the contributions that have significantly impacted these vital domains. Ultimately, we engage in a thoughtful discussion of the existing challenges, paving the way for continuous advancements in this critical and ever-dynamic study area.</t>
+  </si>
+  <si>
+    <t>U-GIFT: Uncertainty-Guided Firewall for Toxic Speech in Few-Shot Scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> With the widespread use of social media, user-generated content has surged on online platforms. When such content includes hateful, abusive, offensive, or cyberbullying behavior, it is classified as toxic speech, posing a significant threat to the online ecosystem's integrity and safety. While manual content moderation is still prevalent, the overwhelming volume of content and the psychological strain on human moderators underscore the need for automated toxic speech detection. Previously proposed detection methods often rely on large annotated datasets; however, acquiring such datasets is both costly and challenging in practice. To address this issue, we propose an uncertainty-guided firewall for toxic speech in few-shot scenarios, U-GIFT, that utilizes self-training to enhance detection performance even when labeled data is limited. Specifically, U-GIFT combines active learning with Bayesian Neural Networks (BNNs) to automatically identify high-quality samples from unlabeled data, prioritizing the selection of pseudo-labels with higher confidence for training based on uncertainty estimates derived from model predictions. Extensive experiments demonstrate that U-GIFT significantly outperforms competitive baselines in few-shot detection scenarios. In the 5-shot setting, it achieves a 14.92\% performance improvement over the basic model. Importantly, U-GIFT is user-friendly and adaptable to various pre-trained language models (PLMs). It also exhibits robust performance in scenarios with sample imbalance and cross-domain settings, while showcasing strong generalization across various language applications. We believe that U-GIFT provides an efficient solution for few-shot toxic speech detection, offering substantial support for automated content moderation in cyberspace, thereby acting as a firewall to promote advancements in cybersecurity.</t>
+  </si>
+  <si>
+    <t>LENS-XAI: Redefining Lightweight and Explainable Network Security through Knowledge Distillation and Variational Autoencoders for Scalable Intrusion Detection in Cybersecurity</t>
+  </si>
+  <si>
+    <t>The rapid proliferation of Industrial Internet of Things (IIoT) systems necessitates advanced, interpretable, and scalable intrusion detection systems (IDS) to combat emerging cyber threats. Traditional IDS face challenges such as high computational demands, limited explainability, and inflexibility against evolving attack patterns. To address these limitations, this study introduces the Lightweight Explainable Network Security framework (LENS-XAI), which combines robust intrusion detection with enhanced interpretability and scalability. LENS-XAI integrates knowledge distillation, variational autoencoder models, and attribution-based explainability techniques to achieve high detection accuracy and transparency in decision-making. By leveraging a training set comprising 10% of the available data, the framework optimizes computational efficiency without sacrificing performance. Experimental evaluation on four benchmark datasets: Edge-IIoTset, UKM-IDS20, CTU-13, and NSL-KDD, demonstrates the framework's superior performance, achieving detection accuracies of 95.34%, 99.92%, 98.42%, and 99.34%, respectively. Additionally, the framework excels in reducing false positives and adapting to complex attack scenarios, outperforming existing state-of-the-art methods. Key strengths of LENS-XAI include its lightweight design, suitable for resource-constrained environments, and its scalability across diverse IIoT and cybersecurity contexts. Moreover, the explainability module enhances trust and transparency, critical for practical deployment in dynamic and sensitive applications. This research contributes significantly to advancing IDS by addressing computational efficiency, feature interpretability, and real-world applicability. Future work could focus on extending the framework to ensemble AI systems for distributed environments, further enhancing its robustness and adaptability.</t>
+  </si>
+  <si>
+    <t>Collaborative Approaches to Enhancing Smart Vehicle Cybersecurity by AI-Driven Threat Detection</t>
+  </si>
+  <si>
+    <t>The introduction sets the stage for exploring collaborative approaches to bolstering smart vehicle cybersecurity through AI-driven threat detection. As the automotive industry increasingly adopts connected and automated vehicles (CAVs), the need for robust cybersecurity measures becomes paramount. With the emergence of new vulnerabilities and security requirements, the integration of advanced technologies such as 5G networks, blockchain, and quantum computing presents promising avenues for enhancing CAV cybersecurity . Additionally, the roadmap for cybersecurity in autonomous vehicles emphasizes the importance of efficient intrusion detection systems and AI-based techniques, along with the integration of secure hardware, software stacks, and advanced threat intelligence to address cybersecurity challenges in future autonomous vehicles.</t>
+  </si>
+  <si>
+    <t>Interactive cybersecurity training system based on simulation environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Rapid progress in the development of information technology has led to a significant increase in the number and complexity of cyber threats. Traditional methods of cybersecurity training based on theoretical knowledge do not provide a sufficient level of practical skills to effectively counter real threats. The article explores the possibilities of integrating simulation environments into the cybersecurity training process as an effective approach to improving the quality of training. The article presents the architecture of a simulation environment based on a cluster of KVM hypervisors, which allows creating scalable and flexible platforms at minimal cost. The article describes the implementation of various scenarios using open source software tools such as pfSense, OPNsense, Security Onion, Kali Linux, Parrot Security OS, Ubuntu Linux, Oracle Linux, FreeBSD, and others, which create realistic conditions for practical training.</t>
+  </si>
+  <si>
+    <t>Malware Classification using a Hybrid Hidden Markov Model-Convolutional Neural Network</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The proliferation of malware variants poses a significant challenges to traditional malware detection approaches, such as signature-based methods, necessitating the development of advanced machine learning techniques. In this research, we present a novel approach based on a hybrid architecture combining features extracted using a Hidden Markov Model (HMM), with a Convolutional Neural Network (CNN) then used for malware classification. Inspired by the strong results in previous work using an HMM-Random Forest model, we propose integrating HMMs, which serve to capture sequential patterns in opcode sequences, with CNNs, which are adept at extracting hierarchical features. We demonstrate the effectiveness of our approach on the popular Malicia dataset, and we obtain superior performance, as compared to other machine learning methods -- our results surpass the aforementioned HMM-Random Forest model. Our findings underscore the potential of hybrid HMM-CNN architectures in bolstering malware classification capabilities, offering several promising avenues for further research in the field of cybersecurity. </t>
+  </si>
+  <si>
+    <t>A Review of the Duality of Adversarial Learning in Network Intrusion: Attacks and Countermeasures</t>
+  </si>
+  <si>
+    <t>Deep learning solutions are instrumental in cybersecurity, harnessing their ability to analyze vast datasets, identify complex patterns, and detect anomalies. However, malevolent actors can exploit these capabilities to orchestrate sophisticated attacks, posing significant challenges to defenders and traditional security measures. Adversarial attacks, particularly those targeting vulnerabilities in deep learning models, present a nuanced and substantial threat to cybersecurity. Our study delves into adversarial learning threats such as Data Poisoning, Test Time Evasion, and Reverse Engineering, specifically impacting Network Intrusion Detection Systems. Our research explores the intricacies and countermeasures of attacks to deepen understanding of network security challenges amidst adversarial threats. In our study, we present insights into the dynamic realm of adversarial learning and its implications for network intrusion. The intersection of adversarial attacks and defenses within network traffic data, coupled with advances in machine learning and deep learning techniques, represents a relatively underexplored domain. Our research lays the groundwork for strengthening defense mechanisms to address the potential breaches in network security and privacy posed by adversarial attacks. Through our in-depth analysis, we identify domain-specific research gaps, such as the scarcity of real-life attack data and the evaluation of AI-based solutions for network traffic. Our focus on these challenges aims to stimulate future research efforts toward the development of resilient network defense strategies.</t>
+  </si>
+  <si>
+    <t>BotSim: LLM-Powered Malicious Social Botnet Simulation</t>
+  </si>
+  <si>
+    <t>Social media platforms like X(Twitter) and Reddit are vital to global communication. However, advancements in Large Language Model (LLM) technology give rise to social media bots with unprecedented intelligence. These bots adeptly simulate human profiles, conversations, and interactions, disseminating large amounts of false information and posing significant challenges to platform regulation. To better understand and counter these threats, we innovatively design BotSim, a malicious social botnet simulation powered by LLM. BotSim mimics the information dissemination patterns of real-world social networks, creating a virtual environment composed of intelligent agent bots and real human users. In the temporal simulation constructed by BotSim, these advanced agent bots autonomously engage in social interactions such as posting and commenting, effectively modeling scenarios of information flow and user interaction. Building on the BotSim framework, we construct a highly human-like, LLM-driven bot dataset called BotSim-24 and benchmark multiple bot detection strategies against it. The experimental results indicate that detection methods effective on traditional bot datasets perform worse on BotSim-24, highlighting the urgent need for new detection strategies to address the cybersecurity threats posed by these advanced bots.</t>
+  </si>
+  <si>
+    <t>Quantum community detection via deterministic elimination</t>
+  </si>
+  <si>
+    <t>We propose a quantum algorithm for calculating the structural properties of complex networks and graphs. The corresponding protocol -- deteQt -- is designed to perform large-scale community and botnet detection, where a specific subgraph of a larger graph is identified based on its properties. We construct a workflow relying on ground state preparation of the network modularity matrix or graph Laplacian. The corresponding maximum modularity vector is encoded into a -qubit register that contains community information. We develop a strategy for ``signing'' this vector via quantum signal processing, such that it closely resembles a hypergraph state, and project it onto a suitable linear combination of such states to detect botnets. As part of the workflow, and of potential independent interest, we present a readout technique that allows filtering out the incorrect solutions deterministically. This can reduce the scaling for the number of samples from exponential to polynomial. The approach serves as a building block for graph analysis with quantum speed up and enables the cybersecurity of large-scale networks</t>
+  </si>
+  <si>
+    <t>Automated Penetration Testing: Formalization and Realization</t>
+  </si>
+  <si>
+    <t>Recent changes in standards and regulations, driven by the increasing importance of software systems in meeting societal needs, mandate increased security testing of software systems. Penetration testing has been shown to be a reliable method to asses software system security. However, manual penetration testing is labor-intensive and requires highly skilled practitioners. Given the shortage of cybersecurity experts and current societal needs, increasing the degree of automation involved in penetration testing can aid in fulfilling the demands for increased security testing. In this work, we formally express the penetration testing problem at the architectural level and suggest a general self-organizing architecture that can be instantiated to automate penetration testing of real systems. We further describe and implement a specialization of the architecture in the ADAPT tool, targeting systems composed of hosts and services. We evaluate and demonstrate the feasibility of ADAPT by automatically performing penetration tests with success against: Metasploitable2, Metasploitable3, and a realistic virtual network used as a lab environment for penetration tester training</t>
+  </si>
+  <si>
+    <t>A technical solution for the rule of law, peace, security, and evolvability of global cyberspace -- solve the three genetic defects of IP network</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Since its inception in the 1960s, the internet has profoundly transformed human life. However, its original design now struggles to meet the evolving demands of modern society. Three primary defects have emerged: First, the concentration of power among a few dominant entities has intensified international conflicts and widened the technological divide. Second, the Internet Protocol (IP)-based system lacks inherent security, leading to frequent global cybersecurity incidents. Third, the rigidity of the IP protocol has hindered the sustainable development of cyberspace, as it resists necessary adaptations and innovations. Addressing these issues is crucial for the future resilience and security of the global digital landscape. To address these challenges, we propose the Co-governed Multi-Identifier Network (CoG-MIN briefly as MIN), a novel network architecture that leverages blockchain technology to ensure equal participation of countries worldwide in cyberspace governance and the rule of law. As a next-generation network system, CoG-MIN integrates mechanisms such as user authentication, data signatures, and encryption to significantly enhance network security. In testing environments, CoG-MIN has consistently withstood extensive attacks during various international cybersecurity competitions. Additionally, CoG-MIN supports the evolution and interoperability of different identifier systems, remains IP-compatible, and facilitates a gradual transition away from IP, providing an adaptable ecosystem for diverse network architectures. This adaptability fosters the development and evolution of diverse network architectures within CoG-MIN, making it a natural progression for the internet's future development. We further introduce a trilogy of cyberspace security theorems... (Due to character limitations, the full abstract is available in the paper PDF.) </t>
+  </si>
+  <si>
+    <t>Enhancing Cybersecurity in IoT Networks: A Deep Learning Approach to Anomaly Detection</t>
+  </si>
+  <si>
+    <t>With the proliferation of the Internet and smart devices, IoT technology has seen significant advancements and has become an integral component of smart homes, urban security, smart logistics, and other sectors. IoT facilitates real-time monitoring of critical production indicators, enabling businesses to detect potential quality issues, anticipate equipment malfunctions, and refine processes, thereby minimizing losses and reducing costs. Furthermore, IoT enhances real-time asset tracking, optimizing asset utilization and management. However, the expansion of IoT has also led to a rise in cybercrimes, with devices increasingly serving as vectors for malicious attacks. As the number of IoT devices grows, there is an urgent need for robust network security measures to counter these escalating threats. This paper introduces a deep learning model incorporating LSTM and attention mechanisms, a pivotal strategy in combating cybercrime in IoT networks. Our experiments, conducted on datasets including IoT-23, BoT-IoT, IoT network intrusion, MQTT, and MQTTset, demonstrate that our proposed method outperforms existing baselines.</t>
+  </si>
+  <si>
+    <t>Digital Transformation in the Water Distribution System based on the Digital Twins Concept</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Digital Twins have emerged as a disruptive technology with great potential; they can enhance WDS by offering real-time monitoring, predictive maintenance, and optimization capabilities. This paper describes the development of a state-of-the-art DT platform for WDS, introducing advanced technologies such as the Internet of Things, Artificial Intelligence, and Machine Learning models. This paper provides insight into the architecture of the proposed platform-CAUCCES-that, informed by both historical and meteorological data, effectively deploys AI/ML models like LSTM networks, Prophet, LightGBM, and XGBoost in trying to predict water consumption patterns. Furthermore, we delve into how optimization in the maintenance of WDS can be achieved by formulating a Constraint Programming problem for scheduling, hence minimizing the operational cost efficiently with reduced environmental impacts. It also focuses on cybersecurity and protection to ensure the integrity and reliability of the DT platform. In this view, the system will contribute to improvements in decision-making capabilities, operational efficiency, and system reliability, with reassurance being drawn from the important role it can play toward sustainable management of water resources.</t>
+  </si>
+  <si>
+    <t>siForest: Detecting Network Anomalies with Set-Structured Isolation Forest</t>
+  </si>
+  <si>
+    <t>As cyber threats continue to evolve in sophistication and scale, the ability to detect anomalous network behavior has become critical for maintaining robust cybersecurity defenses. Modern cybersecurity systems face the overwhelming challenge of analyzing billions of daily network interactions to identify potential threats, making efficient and accurate anomaly detection algorithms crucial for network defense. This paper investigates the use of variations of the Isolation Forest (iForest) machine learning algorithm for detecting anomalies in internet scan data. In particular, it presents the Set-Partitioned Isolation Forest (siForest), a novel extension of the iForest method designed to detect anomalies in set-structured data. By treating instances such as sets of multiple network scans with the same IP address as cohesive units, siForest effectively addresses some challenges of analyzing complex, multidimensional datasets. Extensive experiments on synthetic datasets simulating diverse anomaly scenarios in network traffic demonstrate that siForest has the potential to outperform traditional approaches on some types of internet scan data.</t>
+  </si>
+  <si>
+    <t>PBP: Post-training Backdoor Purification for Malware Classifiers</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In recent years, the rise of machine learning (ML) in cybersecurity has brought new challenges, including the increasing threat of backdoor poisoning attacks on ML malware classifiers. For instance, adversaries could inject malicious samples into public malware repositories, contaminating the training data and potentially misclassifying malware by the ML model. Current countermeasures predominantly focus on detecting poisoned samples by leveraging disagreements within the outputs of a diverse set of ensemble models on training data points. However, these methods are not suitable for scenarios where Machine Learning-as-a-Service (MLaaS) is used or when users aim to remove backdoors from a model after it has been trained. Addressing this scenario, we introduce PBP, a post-training defense for malware classifiers that mitigates various types of backdoor embeddings without assuming any specific backdoor embedding mechanism. Our method exploits the influence of backdoor attacks on the activation distribution of neural networks, independent of the trigger-embedding method. In the presence of a backdoor attack, the activation distribution of each layer is distorted into a mixture of distributions. By regulating the statistics of the batch normalization layers, we can guide a backdoored model to perform similarly to a clean one. Our method demonstrates substantial advantages over several state-of-the-art methods, as evidenced by experiments on two datasets, two types of backdoor methods, and various attack configurations. Notably, our approach requires only a small portion of the training data -- only 1\% -- to purify the backdoor and reduce the attack success rate from 100\% to almost 0\%, a 100-fold improvement over the baseline methods. Our code is available at \url{https://github.com/judydnguyen/pbp-backdoor-purification-official}.</t>
+  </si>
+  <si>
+    <t>warm Intelligence-Driven Client Selection for Federated Learning in Cybersecurity applications</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> This study addresses a critical gap in the literature regarding the use of Swarm Intelligence Optimization (SI) algorithms for client selection in Federated Learning (FL), with a focus on cybersecurity applications. Existing research primarily explores optimization techniques for centralized machine learning, leaving the unique challenges of client diveristy, non-IID data distributions, and adversarial noise in decentralized FL largely unexamined. To bridge this gap, we evaluate nine SI algorithms-Grey Wolf Optimization (GWO), Particle Swarm Optimization (PSO), Cuckoo Search, Bat Algorithm, Bee Colony, Ant Colony Optimization, Fish Swarm, Glow Worm, and Intelligent Water Droplet-across four experimental scenarios: fixed client participation, dynamic participation patterns, hetergeneous non-IID data distributions, and adversarial noise conditions. Results indicate that GWO exhibits superior adaptability and robustness, achieving the highest accuracy, recall and F1-scoress across all configurations, while PSO and Cuckoo Search also demonstrate strong performance. These findings underscore the potential of SI algorithms to address decentralized and adversarial FL challenges, offereing scalable and resilient solutions for cybersecurity applications, including intrusion detection in IoT and large-scale networks. </t>
+  </si>
+  <si>
+    <t>Combining Threat Intelligence with IoT Scanning to Predict Cyber Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> While the Web has become a global platform for communication, malicious actors, including hackers and hacktivist groups, often disseminate ideological content and coordinate activities through the "Dark Web", an obscure counterpart of the conventional web. Presently, challenges such as information overload and the fragmented nature of cyber threat data impede comprehensive profiling of these actors, thereby limiting the efficacy of predictive analyses of their online activities. Concurrently, the proliferation of internet-connected devices has surpassed the global human population, with this disparity projected to widen as the Internet of Things (IoT) expands. Technical communities are actively advancing IoT-related research to address its growing societal integration. This paper proposes a novel predictive threat intelligence framework designed to systematically collect, analyze, and visualize Dark Web data to identify malicious websites and correlate this information with potential IoT vulnerabilities. The methodology integrates automated data harvesting, analytical techniques, and visual mapping tools, while also examining vulnerabilities in IoT devices to assess exploitability. By bridging gaps in cybersecurity research, this study aims to enhance predictive threat modeling and inform policy development, thereby contributing to intelligence research initiatives focused on mitigating cyber risks in an increasingly interconnected digital ecosystem.</t>
+  </si>
+  <si>
+    <t>A Lightweight Edge-CNN-Transformer Model for Detecting Coordinated Cyber and Digital Twin Attacks in Cooperative Smart Farming</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The agriculture sector is increasingly adopting innovative technologies to meet the growing food demands of the global population. To optimize resource utilization and minimize crop losses, farmers are joining cooperatives to share their data and resources among member farms. However, while farmers benefit from this data sharing and interconnection, it exposes them to cybersecurity threats and privacy concerns. A cyberattack on one farm can have widespread consequences, affecting the targeted farm as well as all member farms within a cooperative. In this research, we address existing gaps by proposing a novel and secure architecture for Cooperative Smart Farming (CSF). First, we highlight the role of edge-based DTs in enhancing the efficiency and resilience of agricultural operations. To validate this, we develop a test environment for CSF, implementing various cyberattacks on both the DTs and their physical counterparts using different attack vectors. We collect two smart farming network datasets to identify potential threats. After identifying these threats, we focus on preventing the transmission of malicious data from compromised farms to the central cloud server. To achieve this, we propose a CNN-Transformer-based network anomaly detection model, specifically designed for deployment at the edge. As a proof of concept, we implement this model and evaluate its performance by varying the number of encoder layers. Additionally, we apply Post-Quantization to compress the model and demonstrate the impact of compression on its performance in edge environments. Finally, we compare the model's performance with traditional machine learning approaches to assess its overall effectiveness. </t>
+  </si>
+  <si>
+    <t>Robust Defense Against Extreme Grid Events Using Dual-Policy Reinforcement Learning Agents</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Reinforcement learning (RL) agents are powerful tools for managing power grids. They use large amounts of data to inform their actions and receive rewards or penalties as feedback to learn favorable responses for the system. Once trained, these agents can efficiently make decisions that would be too computationally complex for a human operator. This ability is especially valuable in decarbonizing power networks, where the demand for RL agents is increasing. These agents are well suited to control grid actions since the action space is constantly growing due to uncertainties in renewable generation, microgrid integration, and cybersecurity threats. To assess the efficacy of RL agents in response to an adverse grid event, we use the Grid2Op platform for agent training. We employ a proximal policy optimization (PPO) algorithm in conjunction with graph neural networks (GNNs). By simulating agents' responses to grid events, we assess their performance in avoiding grid failure for as long as possible. The performance of an agent is expressed concisely through its reward function, which helps the agent learn the most optimal ways to reconfigure a grid's topology amidst certain events. To model multi-actor scenarios that threaten modern power networks, particularly those resulting from cyberattacks, we integrate an opponent that acts iteratively against a given agent. This interplay between the RL agent and opponent is utilized in N-k contingency screening, providing a novel alternative to the traditional security assessment</t>
+  </si>
+  <si>
+    <t>SDN-Based Smart Cyber Switching (SCS) for Cyber Restoration of a Digital Substation</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> In recent years, critical infrastructure and power grids have increasingly been targets of cyber-attacks, causing widespread and extended blackouts. Digital substations are particularly vulnerable to such cyber incursions, jeopardizing grid stability. This paper addresses these risks by proposing a cybersecurity framework that leverages software-defined networking (SDN) to bolster the resilience of substations based on the IEC-61850 standard. The research introduces a strategy involving smart cyber switching (SCS) for mitigation and concurrent intelligent electronic device (CIED) for restoration, ensuring ongoing operational integrity and cybersecurity within a substation. The SCS framework improves the physical network's behavior (i.e., leveraging commercial SDN capabilities) by incorporating an adaptive port controller (APC) module for dynamic port management and an intrusion detection system (IDS) to detect and counteract malicious IEC-61850-based sampled value (SV) and generic object-oriented system event (GOOSE) messages within the substation's communication network. The framework's effectiveness is validated through comprehensive simulations and a hardware-in-the-loop (HIL) testbed, demonstrating its ability to sustain substation operations during cyber-attacks and significantly improve the overall resilience of the power grid.</t>
+  </si>
+  <si>
+    <t>Towards Characterizing Cyber Networks with Large Language Models</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Threat hunting analyzes large, noisy, high-dimensional data to find sparse adversarial behavior. We believe adversarial activities, however they are disguised, are extremely difficult to completely obscure in high dimensional space. In this paper, we employ these latent features of cyber data to find anomalies via a prototype tool called Cyber Log Embeddings Model (CLEM). CLEM was trained on Zeek network traffic logs from both a real-world production network and an from Internet of Things (IoT) cybersecurity testbed. The model is deliberately overtrained on a sliding window of data to characterize each window closely. We use the Adjusted Rand Index (ARI) to comparing the k-means clustering of CLEM output to expert labeling of the embeddings. Our approach demonstrates that there is promise in using natural language modeling to understand cyber data. </t>
+  </si>
+  <si>
+    <t>Cybercrime Prediction via Geographically Weighted Learning</t>
+  </si>
+  <si>
+    <t>Inspired by the success of Geographically Weighted Regression and its accounting for spatial variations, we propose GeogGNN -- A graph neural network model that accounts for geographical latitude and longitudinal points. Using a synthetically generated dataset, we apply the algorithm for a 4-class classification problem in cybersecurity with seemingly realistic geographic coordinates centered in the Gulf Cooperation Council region. We demonstrate that it has higher accuracy than standard neural networks and convolutional neural networks that treat the coordinates as features. Encouraged by the speed-up in model accuracy by the GeogGNN model, we provide a general mathematical result that demonstrates that a geometrically weighted neural network will, in principle, always display higher accuracy in the classification of spatially dependent data by making use of spatial continuity and local averaging features.</t>
+  </si>
+  <si>
+    <t>Tactical Edge IoT in Defense and National Security</t>
+  </si>
+  <si>
+    <t>The deployment of Internet of Things (IoT) systems in Defense and National Security faces some limitations that can be addressed with Edge Computing approaches. The Edge Computing and IoT paradigms combined bring potential benefits, since they confront the limitations of traditional centralized cloud computing approaches, which enable easy scalability, real-time applications or mobility support, but whose use poses certain risks in aspects like cybersecurity. This chapter identifies scenarios in which Defense and National Security can leverage Commercial Off-The-Shelf (COTS) Edge IoT capabilities to deliver greater survivability to warfighters or first responders, while lowering costs and increasing operational efficiency and effectiveness. In addition, it presents the general design of a Tactical Edge IoT communications architecture, it identifies the open challenges for a widespread adoption and provides research guidelines and some recommendations for enabling cost-effective Edge IoT for Defense and National Security.</t>
+  </si>
+  <si>
+    <t>Computer Application Research based on Chinese Human Resources and Network Information Security Technology Management and Analysis In Chinese Universities</t>
+  </si>
+  <si>
+    <t>This study investigates the current state of computer network security and human resource management within Chinese universities, emphasizing the growing importance of safeguarding digital infrastructures. To support the analysis, interviews were conducted with managers from two leading Chinese cybersecurity firms and the qualitative data obtained was carefully analyzed to extract key insights and conclusions</t>
+  </si>
+  <si>
+    <t>ADAPT: A Game-Theoretic and Neuro-Symbolic Framework for Automated Distributed Adaptive Penetration Testing</t>
+  </si>
+  <si>
+    <t>The integration of AI into modern critical infrastructure systems, such as healthcare, has introduced new vulnerabilities that can significantly impact workflow, efficiency, and safety. Additionally, the increased connectivity has made traditional human-driven penetration testing insufficient for assessing risks and developing remediation strategies. Consequently, there is a pressing need for a distributed, adaptive, and efficient automated penetration testing framework that not only identifies vulnerabilities but also provides countermeasures to enhance security posture. This work presents ADAPT, a game-theoretic and neuro-symbolic framework for automated distributed adaptive penetration testing, specifically designed to address the unique cybersecurity challenges of AI-enabled healthcare infrastructure networks. We use a healthcare system case study to illustrate the methodologies within ADAPT. The proposed solution enables a learning-based risk assessment. Numerical experiments are used to demonstrate effective countermeasures against various tactical techniques employed by adversarial AI.</t>
+  </si>
+  <si>
+    <t>Securing Healthcare with Deep Learning: A CNN-Based Model for medical IoT Threat Detection</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The increasing integration of the Internet of Medical Things (IoMT) into healthcare systems has significantly enhanced patient care but has also introduced critical cybersecurity challenges. This paper presents a novel approach based on Convolutional Neural Networks (CNNs) for detecting cyberattacks within IoMT environments. Unlike previous studies that predominantly utilized traditional machine learning (ML) models or simpler Deep Neural Networks (DNNs), the proposed model leverages the capabilities of CNNs to effectively analyze the temporal characteristics of network traffic data. Trained and evaluated on the CICIoMT2024 dataset, which comprises 18 distinct types of cyberattacks across a range of IoMT devices, the proposed CNN model demonstrates superior performance compared to previous state-of-the-art methods, achieving a perfect accuracy of 99% in binary, categorical, and multiclass classification tasks. This performance surpasses that of conventional ML models such as Logistic Regression, AdaBoost, DNNs, and Random Forests. These findings highlight the potential of CNNs to substantially improve IoMT cybersecurity, thereby ensuring the protection and integrity of connected healthcare systems.</t>
+  </si>
+  <si>
+    <t>Resilient-By-Design: A Resiliency Framework for Future Wireless Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Our future society will be increasingly digitalised, hyper-connected and globally data driven. The sixth generation (6G) and beyond 6G wireless networks are expected to bridge the digital and physical worlds by providing wireless connectivity as a service to different vertical sectors, including industries, smart cities, eHealth and autonomous transportation. Such far reaching integration will render the society increasingly reliant on wireless networks. While this has the potential to greatly enhance our quality and ease of life, any disruption to these networks would also have significant impact with overreaching consequences. Disruptions can happen due to a variety of reasons, including planned outages, failures due to the nature of wireless propagation, natural disasters, and deliberate cybersecurity attacks. Hence, 6G and beyond 6G networks should not only provide near instant and virtually unlimited connectivity, but also be resilient against internal and external disruptions. This paper proposes a resilient-by-design framework towards this end. First, we provide an overview of the disruption landscape. Thereafter, we comprehensively outline the main features of the proposed concept. Finally, we detail the four key steps of the framework, namely predict, preempt, protect and progress. A simple but illustrative preliminary simulation result is also presented to highlight the potential advantages and efficiency of the proposed approach in addressing outages. </t>
+  </si>
+  <si>
+    <t>Survey of Load-Altering Attacks Against Power Grids: Attack Impact, Detection and Mitigation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The growing penetration of IoT devices in power grids despite its benefits, raises cybersecurity concerns. In particular, load-altering attacks (LAAs) targeting high-wattage IoT-controllable load devices pose serious risks to grid stability and disrupt electricity markets. This paper provides a comprehensive review of LAAs, highlighting the threat model, analyzing their impact on transmission and distribution networks, and the electricity market dynamics. We also review the detection and localization schemes for LAAs that employ either model-based or data-driven approaches, with some hybrid methods combining the strengths of both. Additionally, mitigation techniques are examined, focusing on both preventive measures, designed to thwart attack execution, and reactive methods, which aim to optimize responses to ongoing attacks. We look into the application of each study and highlight potential streams for future research. </t>
+  </si>
+  <si>
+    <t>Countering Autonomous Cyber Threats</t>
+  </si>
+  <si>
+    <t>Enhancing Enterprise Security with Zero Trust Architecture</t>
+  </si>
+  <si>
+    <t>Zero Trust Architecture (ZTA) represents a transformative approach to modern cybersecurity, directly addressing the shortcomings of traditional perimeter-based security models. With the rise of cloud computing, remote work, and increasingly sophisticated cyber threats, perimeter defenses have proven ineffective at mitigating risks, particularly those involving insider threats and lateral movement within networks. ZTA shifts the security paradigm by assuming that no user, device, or system can be trusted by default, requiring continuous verification and the enforcement of least privilege access for all entities. This paper explores the key components of ZTA, such as identity and access management (IAM), micro-segmentation, continuous monitoring, and behavioral analytics, and evaluates their effectiveness in reducing vulnerabilities across diverse sectors, including finance, healthcare, and technology. Through case studies and industry reports, the advantages of ZTA in mitigating insider threats and minimizing attack surfaces are discussed. Additionally, the paper addresses the challenges faced during ZTA implementation, such as scalability, integration complexity, and costs, while providing best practices for overcoming these obstacles. Lastly, future research directions focusing on emerging technologies like AI, machine learning, blockchain, and their integration into ZTA are examined to enhance its capabilities further.</t>
+  </si>
+  <si>
+    <t>Hierarchical Multi-agent Reinforcement Learning for Cyber Network Defense</t>
+  </si>
+  <si>
+    <t>Recent advances in multi-agent reinforcement learning (MARL) have created opportunities to solve complex real-world tasks. Cybersecurity is a notable application area, where defending networks against sophisticated adversaries remains a challenging task typically performed by teams of security operators. In this work, we explore novel MARL strategies for building autonomous cyber network defenses that address challenges such as large policy spaces, partial observability, and stealthy, deceptive adversarial strategies. To facilitate efficient and generalized learning, we propose a hierarchical Proximal Policy Optimization (PPO) architecture that decomposes the cyber defense task into specific sub-tasks like network investigation and host recovery. Our approach involves training sub-policies for each sub-task using PPO enhanced with domain expertise. These sub-policies are then leveraged by a master defense policy that coordinates their selection to solve complex network defense tasks. Furthermore, the sub-policies can be fine-tuned and transferred with minimal cost to defend against shifts in adversarial behavior or changes in network settings. We conduct extensive experiments using CybORG Cage 4, the state-of-the-art MARL environment for cyber defense. Comparisons with multiple baselines across different adversaries show that our hierarchical learning approach achieves top performance in terms of convergence speed, episodic return, and several interpretable metrics relevant to cybersecurity, including the fraction of clean machines on the network, precision, and false positives on recoveries.</t>
+  </si>
+  <si>
+    <t>Synthetic Network Traffic Data Generation: A Comparative Study</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The generation of synthetic network traffic data is essential for network security testing, machine learning model training, and performance analysis. However, existing methods for synthetic data generation differ significantly in their ability to maintain statistical fidelity, utility for classification tasks, and class balance. This study presents a comparative analysis of twelve synthetic network traffic data generation methods, encompassing non-AI (statistical), classical AI, and generative AI techniques. Using NSL-KDD and CIC-IDS2017 datasets, we evaluate the fidelity, utility, class balance, and scalability of these methods under standardized performance metrics. Results demonstrate that GAN-based models, particularly CTGAN and CopulaGAN, achieve superior fidelity and utility, making them ideal for high-quality synthetic data generation. Statistical methods such as SMOTE and Cluster Centroid effectively maintain class balance but fail to capture complex traffic structures. Meanwhile, diffusion models exhibit computational inefficiencies, limiting their scalability. Our findings provide a structured benchmarking framework for selecting the most suitable synthetic data generation techniques for network traffic analysis and cybersecurity applications.</t>
+  </si>
+  <si>
+    <t>Towards more realistic co-simulation of cyber-physical energy distribution systems</t>
+  </si>
+  <si>
+    <t>The increased integration of information and communications technology at the distribution grid level offers broader opportunities for active operational management concepts. At the same time, requirements for resilience against internal and external threats to the power supply, such as outages or cyberattacks, are increasing. The emerging threat landscape needs to be investigated to ensure the security of supply of future distribution grids. This extended abstract presents a co-simulation environment to study communication infrastructures for the resilient operation of distribution grids. For this purpose, a communication network emulation and a power grid simulation are combined in a common modular environment. This will provide the basis for cybersecurity investigations and testing of new active operation management concepts for smart grids. Exemplary laboratory tests and attack replications will be used to demonstrate the diverse use cases of our co-simulation approach.</t>
+  </si>
+  <si>
+    <t>Cyber Threats to Canadian Federal Election: Emerging Threats, Assessment, and Mitigation Strategies</t>
+  </si>
+  <si>
+    <t>As Canada prepares for the 2025 federal election, ensuring the integrity and security of the electoral process against cyber threats is crucial. Recent foreign interference in elections globally highlight the increasing sophistication of adversaries in exploiting technical and human vulnerabilities. Such vulnerabilities also exist in Canada's electoral system that relies on a complex network of IT systems, vendors, and personnel. To mitigate these vulnerabilities, a threat assessment is crucial to identify emerging threats, develop incident response capabilities, and build public trust and resilience against cyber threats. Therefore, this paper presents a comprehensive national cyber threat assessment, following the NIST Special Publication 800-30 framework, focusing on identifying and mitigating cybersecurity risks to the upcoming 2025 Canadian federal election. The research identifies three major threats: misinformation, disinformation, and malinformation (MDM) campaigns; attacks on critical infrastructure and election support systems; and espionage by malicious actors. Through detailed analysis, the assessment offers insights into the capabilities, intent, and potential impact of these threats. The paper also discusses emerging technologies and their influence on election security and proposes a multi-faceted approach to risk mitigation ahead of the election.</t>
+  </si>
+  <si>
+    <t>Towards the generation of hierarchical attack models from cybersecurity vulnerabilities using language models</t>
+  </si>
+  <si>
+    <t xml:space="preserve">This paper investigates the use of a pre-trained language model and siamese network to discern sibling relationships between text-based cybersecurity vulnerability data. The ultimate purpose of the approach presented in this paper is towards the construction of hierarchical attack models based on a set of text descriptions characterising potential/observed vulnerabilities in a given system. Due to the nature of the data, and the uncertainty sensitive environment in which the problem is presented, a practically oriented soft computing approach is necessary. Therefore, a key focus of this work is to investigate practical questions surrounding the reliability of predicted links towards the construction of such models, to which end conceptual and practical challenges and solutions associated with the proposed approach are outlined, such as dataset complexity and stability of predictions. Accordingly, the contributions of this paper focus on producing neural networks using a pre-trained language model for predicting sibling relationships between cybersecurity vulnerabilities, then outlining how to apply this capability towards the generation of hierarchical attack models. In addition, two data sampling mechanisms for tackling data complexity, and a consensus mechanism for reducing the amount of false positive predictions are outlined. Each of these approaches is compared and contrasted using empirical results from three sets of cybersecurity data to determine their effectiveness. </t>
+  </si>
+  <si>
+    <t>Towards a Self-rescuing System for UAVs Under GNSS Attack</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> There has been substantial growth in the UAV market along with an expansion in their applications. However, the successful execution of a UAV mission is very often dependent on the use of a GNSS. Unfortunately, the vulnerability of GNSS signals, due to their lack of encryption and authentication, poses a significant cybersecurity issue. This vulnerability makes various attacks, particularly the "GNSS spoofing attack," and "GNSS jamming attack" easily executable. Generally speaking, during this attack, the drone is manipulated into altering its path, usually resulting in an immediate forced landing or crash. As far as we know, we are the first to propose a lightweight-solution that enable a drone to autonomously rescue itself, assuming it is under GNSS attack and the GNSS is no longer available, and return safely to its initial takeoff position, thereby preventing any potential crashes. During the flight, wind plays a critical role as it can instantaneously alter the drone's position. To solve this problem, we have devised a highly effective 2-phases solution: (i) Forward Phase, for monitoring and recording the forward journey, and (ii) Backward Phase, that generates a backward route, based on the Forward Phase and wind presence. The final solution ensures strong performance in consistently returning the drone to the original position, even in wind situations, while maintaining a very fast computation time.</t>
+  </si>
+  <si>
+    <t>Adversarial Challenges in Network Intrusion Detection Systems: Research Insights and Future Prospects</t>
+  </si>
+  <si>
+    <t>Machine learning has brought significant advances in cybersecurity, particularly in the development of Intrusion Detection Systems (IDS). These improvements are mainly attributed to the ability of machine learning algorithms to identify complex relationships between features and effectively generalize to unseen data. Deep neural networks, in particular, contributed to this progress by enabling the analysis of large amounts of training data, significantly enhancing detection performance. However, machine learning models remain vulnerable to adversarial attacks, where carefully crafted input data can mislead the model into making incorrect predictions. While adversarial threats in unstructured data, such as images and text, have been extensively studied, their impact on structured data like network traffic is less explored. This survey aims to address this gap by providing a comprehensive review of machine learning-based Network Intrusion Detection Systems (NIDS) and thoroughly analyzing their susceptibility to adversarial attacks. We critically examine existing research in NIDS, highlighting key trends, strengths, and limitations, while identifying areas that require further exploration. Additionally, we discuss emerging challenges in the field and offer insights for the development of more robust and resilient NIDS. In summary, this paper enhances the understanding of adversarial attacks and defenses in NIDS and guide future research in improving the robustness of machine learning models in cybersecurity applications.</t>
+  </si>
+  <si>
+    <t>Comparing Unidirectional, Bidirectional, and Word2vec Models for Discovering Vulnerabilities in Compiled Lifted Code</t>
+  </si>
+  <si>
+    <t>Ransomware and other forms of malware cause significant financial and operational damage to organizations by exploiting long-standing and often difficult-to-detect software vulnerabilities. To detect vulnerabilities such as buffer overflows in compiled code, this research investigates the application of unidirectional transformer-based embeddings, specifically GPT-2. Using a dataset of LLVM functions, we trained a GPT-2 model to generate embeddings, which were subsequently used to build LSTM neural networks to differentiate between vulnerable and non-vulnerable code. Our study reveals that embeddings from the GPT-2 model significantly outperform those from bidirectional models of BERT and RoBERTa, achieving an accuracy of 92.5% and an F1-score of 89.7%. LSTM neural networks were developed with both frozen and unfrozen embedding model layers. The model with the highest performance was achieved when the embedding layers were unfrozen. Further, the research finds that, in exploring the impact of different optimizers within this domain, the SGD optimizer demonstrates superior performance over Adam. Overall, these findings reveal important insights into the potential of unidirectional transformer-based approaches in enhancing cybersecurity defenses.</t>
+  </si>
+  <si>
+    <t>GISExplainer: On Explainability of Graph Neural Networks via Game-theoretic Interaction Subgraphs</t>
+  </si>
+  <si>
+    <t>Explainability is crucial for the application of black-box Graph Neural Networks (GNNs) in critical fields such as healthcare, finance, cybersecurity, and more. Various feature attribution methods, especially the perturbation-based methods, have been proposed to indicate how much each node/edge contributes to the model predictions. However, these methods fail to generate connected explanatory subgraphs that consider the causal interaction between edges within different coalition scales, which will result in unfaithful explanations. In our study, we propose GISExplainer, a novel game-theoretic interaction based explanation method that uncovers what the underlying GNNs have learned for node classification by discovering human-interpretable causal explanatory subgraphs. First, GISExplainer defines a causal attribution mechanism that considers the game-theoretic interaction of multi-granularity coalitions in candidate explanatory subgraph to quantify the causal effect of an edge on the prediction. Second, GISExplainer assumes that the coalitions with negative effects on the predictions are also significant for model interpretation, and the contribution of the computation graph stems from the combined influence of both positive and negative interactions within the coalitions. Then, GISExplainer regards the explanation task as a sequential decision process, in which a salient edges is successively selected and connected to the previously selected subgraph based on its causal effect to form an explanatory subgraph, ultimately striving for better explanations. Additionally, an efficiency optimization scheme is proposed for the causal attribution mechanism through coalition sampling. Extensive experiments demonstrate that GISExplainer achieves better performance than state-of-the-art approaches w.r.t. two quantitative metrics: Fidelity and Sparsity.</t>
+  </si>
+  <si>
+    <t>MEGA-PT: A Meta-Game Framework for Agile Penetration Testing</t>
+  </si>
+  <si>
+    <t>Penetration testing is an essential means of proactive defense in the face of escalating cybersecurity incidents. Traditional manual penetration testing methods are time-consuming, resource-intensive, and prone to human errors. Current trends in automated penetration testing are also impractical, facing significant challenges such as the curse of dimensionality, scalability issues, and lack of adaptability to network changes. To address these issues, we propose MEGA-PT, a meta-game penetration testing framework, featuring micro tactic games for node-level local interactions and a macro strategy process for network-wide attack chains. The micro- and macro-level modeling enables distributed, adaptive, collaborative, and fast penetration testing. MEGA-PT offers agile solutions for various security schemes, including optimal local penetration plans, purple teaming solutions, and risk assessment, providing fundamental principles to guide future automated penetration testing. Our experiments demonstrate the effectiveness and agility of our model by providing improved defense strategies and adaptability to changes at both local and network levels.</t>
+  </si>
+  <si>
+    <t>Cyber-Physical Authentication Scheme for Secure V2G Transactions</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The rapid adoption of electric vehicles (EVs) globally has catalyzed the need for robust cybersecurity measures within vehicle-to-grid (V2G) networks. As these networks are increasingly being integrated into smart charging infrastructures, they also introduce new vulnerabilities that threaten grid stability and user privacy This paper proposes a cyber-physical authentication protocol and trading smart contract tailored to plug and charge (PnC) operations within blockchain-based V2G systems. The protocol leverages advanced cryptographic techniques and blockchain to ensure secure, transparent, and tamper-proof energy transactions between EVs and charging stations. Key contributions include the development of a cyber-physical authentication method, the implementation of a smart contract framework for secure energy trading, and a detailed security and privacy analysis. The proposed protocol effectively mitigates risks such as man-in-the-middle (MitM) attacks and replay attacks while preserving user anonymity and data integrity</t>
+  </si>
+  <si>
+    <t>Maritime Cybersecurity: A Comprehensive Review</t>
+  </si>
+  <si>
+    <t>The maritime industry stands at a critical juncture, where the imperative for technological advancement intersects with the pressing need for robust cybersecurity measures. Maritime cybersecurity refers to the protection of computer systems and digital assests within the maritime industry, as well as the broader network of interconnected components that make up the maritime ecosystem. In this survey, we aim to identify the significant domains of maritime cybersecurity and measure their effectiveness. We have provided an in-depth analysis of threats in key maritime systems, including AIS, GNSS, ECDIS, VDR, RADAR, VSAT, and GMDSS, while exploring real-world cyber incidents that have impacted the sector. A multi-dimensional taxonomy of maritime cyber attacks is presented, offering insights into threat actors, motivations, and impacts. We have also evaluated various security solutions, from integrated solutions to component specific solutions. Finally, we have shared open challenges and future solutions. In the supplementary section, we have presented definitions and vulnerabilities of vessel components that have discussed in this survey. By addressing all these critical issues with key interconnected aspects, this review aims to foster a more resilient maritime ecosystem.</t>
+  </si>
+  <si>
+    <t>CyberNFTs: Conceptualizing a decentralized and reward-driven intrusion detection system with ML</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> The rapid evolution of the Internet, particularly the emergence of Web3, has transformed the ways people interact and share data. Web3, although still not well defined, is thought to be a return to the decentralization of corporations' power over user data. Despite the obsolescence of the idea of building systems to detect and prevent cyber intrusions, this is still a topic of interest. This paper proposes a novel conceptual approach for implementing decentralized collaborative intrusion detection networks (CIDN) through a proof-of-concept. The study employs an analytical and comparative methodology, examining the synergy between cutting-edge Web3 technologies and information security. The proposed model incorporates blockchain concepts, cyber non-fungible token (cyberNFT) rewards, machine learning algorithms, and publish/subscribe architectures. Finally, the paper discusses the strengths and limitations of the proposed system, offering insights into the potential of decentralized cybersecurity models. </t>
+  </si>
+  <si>
+    <t>Hackphyr: A Local Fine-Tuned LLM Agent for Network Security Environments</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Large Language Models (LLMs) have shown remarkable potential across various domains, including cybersecurity. Using commercial cloud-based LLMs may be undesirable due to privacy concerns, costs, and network connectivity constraints. In this paper, we present Hackphyr, a locally fine-tuned LLM to be used as a red-team agent within network security environments. Our fine-tuned 7 billion parameter model can run on a single GPU card and achieves performance comparable with much larger and more powerful commercial models such as GPT-4. Hackphyr clearly outperforms other models, including GPT-3.5-turbo, and baselines, such as Q-learning agents in complex, previously unseen scenarios. To achieve this performance, we generated a new task-specific cybersecurity dataset to enhance the base model's capabilities. Finally, we conducted a comprehensive analysis of the agents' behaviors that provides insights into the planning abilities and potential shortcomings of such agents, contributing to the broader understanding of LLM-based agents in cybersecurity contexts </t>
+  </si>
+  <si>
+    <t>DrLLM: Prompt-Enhanced Distributed Denial-of-Service Resistance Method with Large Language Models</t>
+  </si>
+  <si>
+    <t>The increasing number of Distributed Denial of Service (DDoS) attacks poses a major threat to the Internet, highlighting the importance of DDoS mitigation. Most existing approaches require complex training methods to learn data features, which increases the complexity and generality of the application. In this paper, we propose DrLLM, which aims to mine anomalous traffic information in zero-shot scenarios through Large Language Models (LLMs). To bridge the gap between DrLLM and existing approaches, we embed the global and local information of the traffic data into the reasoning paradigm and design three modules, namely Knowledge Embedding, Token Embedding, and Progressive Role Reasoning, for data representation and reasoning. In addition we explore the generalization of prompt engineering in the cybersecurity domain to improve the classification capability of DrLLM. Our ablation experiments demonstrate the applicability of DrLLM in zero-shot scenarios and further demonstrate the potential of LLMs in the network domains. DrLLM implementation code has been open-sourced at https://github.com/liuup/DrLLM</t>
+  </si>
+  <si>
+    <t>LSTM Recurrent Neural Networks for Cybersecurity Named Entity Recognition</t>
+  </si>
+  <si>
+    <t>The automated and timely conversion of cybersecurity information from unstructured online sources, such as blogs and articles to more formal representations has become a necessity for many applications in the domain nowadays. Named Entity Recognition (NER) is one of the early phases towards this goal. It involves the detection of the relevant domain entities, such as product, version, attack name, etc. in technical documents. Although generally considered a simple task in the information extraction field, it is quite challenging in some domains like cybersecurity because of the complex structure of its entities. The state of the art methods require time-consuming and labor intensive feature engineering that describes the properties of the entities, their context, domain knowledge, and linguistic characteristics. The model demonstrated in this paper is domain independent and does not rely on any features specific to the entities in the cybersecurity domain, hence does not require expert knowledge to perform feature engineering. The method used relies on a type of recurrent neural networks called Long Short-Term Memory (LSTM) and the Conditional Random Fields (CRFs) method. The results we obtained showed that this method outperforms the state of the art methods given an annotated corpus of a decent size</t>
+  </si>
+  <si>
+    <t>Federated Learning in Adversarial Environments: Testbed Design and Poisoning Resilience in Cybersecurity</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> This paper presents the design and implementation of a Federated Learning (FL) testbed, focusing on its application in cybersecurity and evaluating its resilience against poisoning attacks. Federated Learning allows multiple clients to collaboratively train a global model while keeping their data decentralized, addressing critical needs for data privacy and security, particularly in sensitive fields like cybersecurity. Our testbed, built using Raspberry Pi and Nvidia Jetson hardware by running the Flower framework, facilitates experimentation with various FL frameworks, assessing their performance, scalability, and ease of integration. Through a case study on federated intrusion detection systems, the testbed's capabilities are shown in detecting anomalies and securing critical infrastructure without exposing sensitive network data. Comprehensive poisoning tests, targeting both model and data integrity, evaluate the system's robustness under adversarial conditions. The results show that while federated learning enhances data privacy and distributed learning, it remains vulnerable to poisoning attacks, which must be mitigated to ensure its reliability in real-world applications. </t>
+  </si>
+  <si>
+    <t>Cybersecurity Software Tool Evaluation Using a 'Perfect' Network Model</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cybersecurity software tool evaluation is difficult due to the inherently adversarial nature of the field. A penetration testing (or offensive) tool must be tested against a viable defensive adversary and a defensive tool must, similarly, be tested against a viable offensive adversary. Characterizing the tool's performance inherently depends on the quality of the adversary, which can vary from test to test. This paper proposes the use of a 'perfect' network, representing computing systems, a network and the attack pathways through it as a methodology to use for testing cybersecurity decision-making tools. This facilitates testing by providing a known and consistent standard for comparison. It also allows testing to include researcher-selected levels of error, noise and uncertainty to evaluate cybersecurity tools under these experimental conditions. </t>
+  </si>
+  <si>
     <r>
-      <t>Huichun Li</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF1F1F1F"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
-      <t>Chengli Zhao</t>
-    </r>
-  </si>
-  <si>
-    <t>Penetration Testing for System Security: Methods and Practical Approaches</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Penetration testing refers to the process of simulating hacker attacks to evaluate the security of information systems . This study aims not only to clarify the theoretical foundations of penetration testing but also to explain and demonstrate the complete testing process, including how network system administrators may simulate attacks using various penetration testing methods. Methodologically, the paper outlines the five basic stages of a typical penetration test: intelligence gathering, vulnerability scanning, vulnerability exploitation, privilege escalation, and post-exploitation activities. In each phase, specific tools and techniques are examined in detail, along with practical guidance on their use. To enhance the practical relevance of the study, the paper also presents a real-life case study, illustrating how a complete penetration test is conducted in a real-world environment. Through this case, readers can gain insights into the detailed procedures and applied techniques, thereby deepening their understanding of the practical value of penetration testing. Finally, the paper summarizes the importance and necessity of penetration testing in securing information systems and maintaining network integrity, and it explores future trends and development directions for the field. Overall, the findings of this paper offer valuable references for both researchers and practitioners, contributing meaningfully to the improvement of penetration testing practices and the advancement of cybersecurity as a whole. </t>
-  </si>
-  <si>
-    <t>Vehicular Intrusion Detection System for Controller Area Network: A Comprehensive Survey and Evaluation</t>
-  </si>
-  <si>
-    <t>The progress of automotive technologies has made cybersecurity a crucial focus, leading to various cyber attacks. These attacks primarily target the Controller Area Network (CAN) and specialized Electronic Control Units (ECUs). In order to mitigate these attacks and bolster the security of vehicular systems, numerous defense solutions have been proposed.These solutions aim to detect diverse forms of vehicular attacks. However, the practical implementation of these solutions still presents certain limitations and challenges. In light of these circumstances, this paper undertakes a thorough examination of existing vehicular attacks and defense strategies employed against the CAN and ECUs. The objective is to provide valuable insights and inform the future design of Vehicular Intrusion Detection Systems (VIDS). The findings of our investigation reveal that the examined VIDS primarily concentrate on particular categories of attacks, neglecting the broader spectrum of potential threats. Moreover, we provide a comprehensive overview of the significant challenges encountered in implementing a robust and feasible VIDS. Additionally, we put forth several defense recommendations based on our study findings, aiming to inform and guide the future design of VIDS in the context of vehicular security.</t>
-  </si>
-  <si>
-    <t>Neuromorphic Mimicry Attacks Exploiting Brain-Inspired Computing for Covert Cyber Intrusions</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Neuromorphic computing, inspired by the human brain's neural architecture, is revolutionizing artificial intelligence and edge computing with its low-power, adaptive, and event-driven designs. However, these unique characteristics introduce novel cybersecurity risks. This paper proposes Neuromorphic Mimicry Attacks (NMAs), a groundbreaking class of threats that exploit the probabilistic and non-deterministic nature of neuromorphic chips to execute covert intrusions. By mimicking legitimate neural activity through techniques such as synaptic weight tampering and sensory input poisoning, NMAs evade traditional intrusion detection systems, posing risks to applications such as autonomous vehicles, smart medical implants, and IoT networks. This research develops a theoretical framework for NMAs, evaluates their impact using a simulated neuromorphic chip dataset, and proposes countermeasures, including neural-specific anomaly detection and secure synaptic learning protocols. The findings underscore the critical need for tailored cybersecurity measures to protect brain-inspired computing, offering a pioneering exploration of this emerging threat landscape. </t>
-  </si>
-  <si>
-    <t>A Non-Zero-Sum Game Model for Optimal Cyber Defense Strategies</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> In the contemporary digital landscape, cybersecurity has become a critical issue due to the increasing frequency and sophistication of cyber attacks. This study utilizes a non-zero-sum game theoretical framework to model the strategic interactions between cyber attackers and defenders, with the objective of identifying optimal strategies for both. By defining precise payoff functions that incorporate the probabilities and costs associated with various exploits, as well as the values of network nodes and the costs of deploying honeypots, we derive Nash equilibria that inform strategic decisions. The proposed model is validated through extensive simulations, demonstrating its effectiveness in enhancing network security. Our results indicate that high-probability, low-cost exploits like Phishing and Social Engineering are more likely to be used by attackers, necessitating prioritized defense mechanisms. Our findings also show that increasing the number of network nodes dilutes the attacker's efforts, thereby improving the defender's payoff. This study provides valuable insights into optimizing resource allocation for cybersecurity and highlights the scalability and practical applicability of the game-theoretic approach. △</t>
-  </si>
-  <si>
-    <t>Adaptive Pruning of Deep Neural Networks for Resource-Aware Embedded Intrusion Detection on the Edge</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Artificial neural network pruning is a method in which artificial neural network sizes can be reduced while attempting to preserve the predicting capabilities of the network. This is done to make the model smaller or faster during inference time. In this work we analyze the ability of a selection of artificial neural network pruning methods to generalize to a new cybersecurity dataset utilizing a simpler network type than was designed for. We analyze each method using a variety of pruning degrees to best understand how each algorithm responds to the new environment. This has allowed us to determine the most well fit pruning method of those we searched for the task. Unexpectedly, we have found that many of them do not generalize to the problem well, leaving only a few algorithms working to an acceptable degree. </t>
-  </si>
-  <si>
-    <t>A Survey of Learning-Based Intrusion Detection Systems for In-Vehicle Network</t>
-  </si>
-  <si>
-    <t>Connected and Autonomous Vehicles (CAVs) enhance mobility but face cybersecurity threats, particularly through the insecure Controller Area Network (CAN) bus. Cyberattacks can have devastating consequences in connected vehicles, including the loss of control over critical systems, necessitating robust security solutions. In-vehicle Intrusion Detection Systems (IDSs) offer a promising approach by detecting malicious activities in real time. This survey provides a comprehensive review of state-of-the-art research on learning-based in-vehicle IDSs, focusing on Machine Learning (ML), Deep Learning (DL), and Federated Learning (FL) approaches. Based on the reviewed studies, we critically examine existing IDS approaches, categorising them by the types of attacks they detect - known, unknown, and combined known-unknown attacks - while identifying their limitations. We also review the evaluation metrics used in research, emphasising the need to consider multiple criteria to meet the requirements of safety-critical systems. Additionally, we analyse FL-based IDSs and highlight their limitations. By doing so, this survey helps identify effective security measures, address existing limitations, and guide future research toward more resilient and adaptive protection mechanisms, ensuring the safety and reliability of CAVs.</t>
-  </si>
-  <si>
-    <t>Modeling Interdependent Cybersecurity Threats Using Bayesian Networks: A Case Study on In-Vehicle Infotainment Systems</t>
-  </si>
-  <si>
-    <t>Cybersecurity threats are increasingly marked by interdependence, uncertainty, and evolving complexity challenges that traditional assessment methods such as CVSS, STRIDE, and attack trees fail to adequately capture. This paper reviews the application of Bayesian Networks (BNs) in cybersecurity risk modeling, highlighting their capacity to represent probabilistic dependencies, integrate diverse threat indicators, and support reasoning under uncertainty. A structured case study is presented in which a STRIDE-based attack tree for an automotive In-Vehicle Infotainment (IVI) system is transformed into a Bayesian Network. Logical relationships are encoded using Conditional Probability Tables (CPTs), and threat likelihoods are derived from normalized DREAD scores. The model enables not only probabilistic inference of system compromise likelihood but also supports causal analysis using do-calculus and local sensitivity analysis to identify high-impact vulnerabilities. These analyses provide insight into the most influential nodes within the threat propagation chain, informing targeted mitigation strategies. While demonstrating the potential of BNs for dynamic and context-aware risk assessment, the study also outlines limitations related to scalability, reliance on expert input, static structure assumptions, and limited temporal modeling. The paper concludes by advocating for future enhancements through Dynamic Bayesian Networks, structure learning, and adaptive inference to better support real-time cybersecurity decision-making in complex environments.</t>
-  </si>
-  <si>
-    <t>The Geography of Transportation Cybersecurity: Visitor Flows, Industry Clusters, and Spatial Dynamics</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The rapid evolution of the transportation cybersecurity ecosystem, encompassing cybersecurity, automotive, and transportation and logistics sectors, will lead to the formation of distinct spatial clusters and visitor flow patterns across the US. This study examines the spatiotemporal dynamics of visitor flows, analyzing how socioeconomic factors shape industry clustering and workforce distribution within these evolving sectors. To model and predict visitor flow patterns, we develop a BiTransGCN framework, integrating an attention-based Transformer architecture with a Graph Convolutional Network backbone. By integrating AI-enabled forecasting techniques with spatial analysis, this study improves our ability to track, interpret, and anticipate changes in industry clustering and mobility trends, thereby supporting strategic planning for a secure and resilient transportation network. It offers a data-driven foundation for economic planning, workforce development, and targeted investments in the transportation cybersecurity ecosystem. </t>
-  </si>
-  <si>
-    <t>Building a global quantum internet using a satellite constellation with inter-satellite links</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The quantum internet is a global network to distribute entanglement and communicate quantum information with applications in cybersecurity, quantum computing, and quantum sensing. Here, we propose building a quantum internet using a constellation of low-Earth-orbit satellites equipped with inter-satellite laser links. Our proposal is based on the downlink model of photon transmission, where satellites carry entangled photon sources and/or have a mirror relay system to redirect the photon path in space. We show that few MHz entanglement distribution rates are possible between the US, Europe, and Asia, with a multiplexed entangled-photon source generating pairs at 10 GHz. Our proposal demonstrates the importance of passive optics in realizing a satellite-based quantum internet, which reduces dependency on quantum memory and repeater technologies. </t>
-  </si>
-  <si>
-    <t>Security through the Eyes of AI: How Visualization is Shaping Malware Detection</t>
-  </si>
-  <si>
-    <t>Malware, a persistent cybersecurity threat, increasingly targets interconnected digital systems such as desktop, mobile, and IoT platforms through sophisticated attack vectors. By exploiting these vulnerabilities, attackers compromise the integrity and resilience of modern digital ecosystems. To address this risk, security experts actively employ Machine Learning or Deep Learning-based strategies, integrating static, dynamic, or hybrid approaches to categorize malware instances. Despite their advantages, these methods have inherent drawbacks and malware variants persistently evolve with increased sophistication, necessitating advancements in detection strategies. Visualization-based techniques are emerging as scalable and interpretable solutions for detecting and understanding malicious behaviors across diverse platforms including desktop, mobile, IoT, and distributed systems as well as through analysis of network packet capture files. In this comprehensive survey of more than 100 high-quality research articles, we evaluate existing visualization-based approaches applied to malware detection and classification. As a first contribution, we propose a new all-encompassing framework to study the landscape of visualization-based malware detection techniques. Within this framework, we systematically analyze state-of-the-art approaches across the critical stages of the malware detection pipeline. By analyzing not only the single techniques but also how they are combined to produce the final solution, we shed light on the main challenges in visualization-based approaches and provide insights into the advancements and potential future directions in this critical field.</t>
-  </si>
-  <si>
-    <t>Open Challenges in Multi-Agent Security: Towards Secure Systems of Interacting AI Agents</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Decentralized AI agents will soon interact across internet platforms, creating security challenges beyond traditional cybersecurity and AI safety frameworks. Free-form protocols are essential for AI's task generalization but enable new threats like secret collusion and coordinated swarm attacks. Network effects can rapidly spread privacy breaches, disinformation, jailbreaks, and data poisoning, while multi-agent dispersion and stealth optimization help adversaries evade oversightcreating novel persistent threats at a systemic level. Despite their critical importance, these security challenges remain understudied, with research fragmented across disparate fields including AI security, multi-agent learning, complex systems, cybersecurity, game theory, distributed systems, and technical AI governance. We introduce \textbf{multi-agent security}, a new field dedicated to securing networks of decentralized AI agents against threats that emerge or amplify through their interactionswhether direct or indirect via shared environmentswith each other, humans, and institutions, and characterize fundamental security-performance trade-offs. Our preliminary work (1) taxonomizes the threat landscape arising from interacting AI agents, (2) surveys security-performance tradeoffs in decentralized AI systems, and (3) proposes a unified research agenda addressing open challenges in designing secure agent systems and interaction environments. By identifying these gaps, we aim to guide research in this critical area to unlock the socioeconomic potential of large-scale agent deployment on the internet, foster public trust, and mitigate national security risks in critical infrastructure and defense contexts.</t>
-  </si>
-  <si>
-    <t>From Texts to Shields: Convergence of Large Language Models and Cybersecurity</t>
-  </si>
-  <si>
-    <t>This report explores the convergence of large language models (LLMs) and cybersecurity, synthesizing interdisciplinary insights from network security, artificial intelligence, formal methods, and human-centered design. It examines emerging applications of LLMs in software and network security, 5G vulnerability analysis, and generative security engineering. The report highlights the role of agentic LLMs in automating complex tasks, improving operational efficiency, and enabling reasoning-driven security analytics. Socio-technical challenges associated with the deployment of LLMs -- including trust, transparency, and ethical considerations -- can be addressed through strategies such as human-in-the-loop systems, role-specific training, and proactive robustness testing. The report further outlines critical research challenges in ensuring interpretability, safety, and fairness in LLM-based systems, particularly in high-stakes domains. By integrating technical advances with organizational and societal considerations, this report presents a forward-looking research agenda for the secure and effective adoption of LLMs in cybersecurity.</t>
-  </si>
-  <si>
-    <t>PICO: Secure Transformers via Robust Prompt Isolation and Cybersecurity Oversight</t>
-  </si>
-  <si>
-    <t>We propose a robust transformer architecture designed to prevent prompt injection attacks and ensure secure, reliable response generation. Our PICO (Prompt Isolation and Cybersecurity Oversight) framework structurally separates trusted system instructions from untrusted user inputs through dual channels that are processed independently and merged only by a controlled, gated fusion mechanism. In addition, we integrate a specialized Security Expert Agent within a Mixture-of-Experts (MoE) framework and incorporate a Cybersecurity Knowledge Graph (CKG) to supply domain-specific reasoning. Our training design further ensures that the system prompt branch remains immutable while the rest of the network learns to handle adversarial inputs safely. This PICO framework is presented via a general mathematical formulation, then elaborated in terms of the specifics of transformer architecture, and fleshed out via hypothetical case studies including Policy Puppetry attacks. While the most effective implementation may involve training transformers in a PICO-based way from scratch, we also present a cost-effective fine-tuning approach.</t>
-  </si>
-  <si>
-    <t>The Dark Side of Digital Twins: Adversarial Attacks on AI-Driven Water Forecasting</t>
-  </si>
-  <si>
-    <t>Digital twins (DTs) are improving water distribution systems by using real-time data, analytics, and prediction models to optimize operations. This paper presents a DT platform designed for a Spanish water supply network, utilizing Long Short-Term Memory (LSTM) networks to predict water consumption. However, machine learning models are vulnerable to adversarial attacks, such as the Fast Gradient Sign Method (FGSM) and Projected Gradient Descent (PGD). These attacks manipulate critical model parameters, injecting subtle distortions that degrade forecasting accuracy. To further exploit these vulnerabilities, we introduce a Learning Automata (LA) and Random LA-based approach that dynamically adjusts perturbations, making adversarial attacks more difficult to detect. Experimental results show that this approach significantly impacts prediction reliability, causing the Mean Absolute Percentage Error (MAPE) to rise from 26% to over 35%. Moreover, adaptive attack strategies amplify this effect, highlighting cybersecurity risks in AI-driven DTs. These findings emphasize the urgent need for robust defenses, including adversarial training, anomaly detection, and secure data pipelines.</t>
-  </si>
-  <si>
-    <t>A Virtual Cybersecurity Department for Securing Digital Twins in Water Distribution Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Digital twins (DTs) help improve real-time monitoring and decision-making in water distribution systems. However, their connectivity makes them easy targets for cyberattacks such as scanning, denial-of-service (DoS), and unauthorized access. Small and medium-sized enterprises (SMEs) that manage these systems often do not have enough budget or staff to build strong cybersecurity teams. To solve this problem, we present a Virtual Cybersecurity Department (VCD), an affordable and automated framework designed for SMEs. The VCD uses open-source tools like Zabbix for real-time monitoring, Suricata for network intrusion detection, Fail2Ban to block repeated login attempts, and simple firewall settings. To improve threat detection, we also add a machine-learning-based IDS trained on the OD-IDS2022 dataset using an improved ensemble model. This model detects cyber threats such as brute-force attacks, remote code execution (RCE), and network flooding, with 92\% accuracy and fewer false alarms. Our solution gives SMEs a practical and efficient way to secure water systems using low-cost and easy-to-manage tools. </t>
-  </si>
-  <si>
-    <t>Cybersecurity for Autonomous Vehicles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The increasing adoption of autonomous vehicles is bringing a major shift in the automotive industry. However, as these vehicles become more connected, cybersecurity threats have emerged as a serious concern. Protecting the security and integrity of autonomous systems is essential to prevent malicious activities that can harm passengers, other road users, and the overall transportation network. This paper focuses on addressing the cybersecurity issues in autonomous vehicles by examining the challenges and risks involved, which are important for building a secure future. Since autonomous vehicles depend on the communication between sensors, artificial intelligence, external infrastructure, and other systems, they are exposed to different types of cyber threats. A cybersecurity breach in an autonomous vehicle can cause serious problems, including a loss of public trust and safety. Therefore, it is very important to develop and apply strong cybersecurity measures to support the growth and acceptance of self-driving cars. This paper discusses major cybersecurity challenges like vulnerabilities in software and hardware, risks from wireless communication, and threats through external interfaces. It also reviews existing solutions such as secure software development, intrusion detection systems, cryptographic protocols, and anomaly detection methods. Additionally, the paper highlights the role of regulatory bodies, industry collaborations, and cybersecurity standards in creating a secure environment for autonomous vehicles. Setting clear rules and best practices is necessary for consistent protection across manufacturers and regions. By analyzing the current cybersecurity landscape and suggesting practical countermeasures, this paper aims to contribute to the safe development and public trust of autonomous vehicle technology. </t>
-  </si>
-  <si>
-    <t>Feature Selection via GANs (GANFS): Enhancing Machine Learning Models for DDoS Mitigation</t>
-  </si>
-  <si>
-    <t>Distributed Denial of Service (DDoS) attacks represent a persistent and evolving threat to modern networked systems, capable of causing large-scale service disruptions. The complexity of such attacks, often hidden within high-dimensional and redundant network traffic data, necessitates robust and intelligent feature selection techniques for effective detection. Traditional methods such as filter-based, wrapper-based, and embedded approaches, each offer strengths but struggle with scalability or adaptability in complex attack environments. In this study, we explore these existing techniques through a detailed comparative analysis and highlight their limitations when applied to large-scale DDoS detection tasks. Building upon these insights, we introduce a novel Generative Adversarial Network-based Feature Selection (GANFS) method that leverages adversarial learning dynamics to identify the most informative features. By training a GAN exclusively on attack traffic and employing a perturbation-based sensitivity analysis on the Discriminator, GANFS effectively ranks feature importance without relying on full supervision. Experimental evaluations using the CIC-DDoS2019 dataset demonstrate that GANFS not only improves the accuracy of downstream classifiers but also enhances computational efficiency by significantly reducing feature dimensionality. These results point to the potential of integrating generative learning models into cybersecurity pipelines to build more adaptive and scalable detection systems.</t>
-  </si>
-  <si>
-    <t>Cluster-Aware Attacks on Graph Watermarks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data from domains such as social networks, healthcare, finance, and cybersecurity can be represented as graph-structured information. Given the sensitive nature of this data and their frequent distribution among collaborators, ensuring secure and attributable sharing is essential. Graph watermarking enables attribution by embedding user-specific signatures into graph-structured data. While prior work has addressed random perturbation attacks, the threat posed by adversaries leveraging structural properties through community detection remains unexplored. In this work, we introduce a cluster-aware threat model in which adversaries apply community-guided modifications to evade detection. We propose two novel attack strategies and evaluate them on real-world social network graphs. Our results show that cluster-aware attacks can reduce attribution accuracy by up to 80% more than random baselines under equivalent perturbation budgets on sparse graphs. To mitigate this threat, we propose a lightweight embedding enhancement that distributes watermark nodes across graph communities. This approach improves attribution accuracy by up to 60% under attack on dense graphs, without increasing runtime or structural distortion. Our findings underscore the importance of cluster-topological awareness in both watermarking design and adversarial modeling. </t>
-  </si>
-  <si>
-    <t>Structural Resilience Analysis of an Internet Fragment Against Targeted and Random Attacks -- A Case Study Based on iThena Project Data</t>
-  </si>
-  <si>
-    <t>This article presents an analysis of the structural resilience of a fragment of Internet topology against both targeted and random attacks, based on empirical data obtained from the iThena project. Using a processed visualization of the network, a graph representing node connections was generated and subsequently subjected to detailed analysis using centrality metrics and community detection algorithms. Two attack scenarios were carried out: removal of nodes with the highest betweenness centrality and random removal of an equivalent number of nodes. The results indicate that targeted attacks have a significantly more destructive impact on the cohesion and functionality of the network than random disruptions. The article highlights the importance of identifying critical nodes and developing monitoring and protection mechanisms for Internet infrastructure in the context of cybersecurity.</t>
-  </si>
-  <si>
-    <t>Integrating Graph Theoretical Approaches in Cybersecurity Education CSCI-RTED</t>
-  </si>
-  <si>
-    <t>As cybersecurity threats continue to evolve, the need for advanced tools to analyze and understand complex cyber environments has become increasingly critical. Graph theory offers a powerful framework for modeling relationships within cyber ecosystems, making it highly applicable to cybersecurity. This paper focuses on the development of an enriched version of the widely recognized NSL-KDD dataset, incorporating graph-theoretical concepts to enhance its practical value. The enriched dataset provides a resource for students and professionals to engage in hands-on analysis, enabling them to explore graph-based methodologies for identifying network behavior and vulnerabilities. To validate the effectiveness of this dataset, we employed IBM Auto AI, demonstrating its capability in real-world applications such as classification and threat prediction. By addressing the need for graph-theoretical datasets, this study provides a practical tool for equipping future cybersecurity professionals with the skills necessary to confront complex cyber challenges.</t>
-  </si>
-  <si>
-    <t>Cyber Value At Risk Model for IoT Ecosystems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The Internet of Things (IoT) presents unique cybersecurity challenges due to its interconnected nature and diverse application domains. This paper explores the application of Cyber Value-at-Risk (Cy-VaR) models to assess and mitigate cybersecurity risks in IoT environments. Cy-VaR, rooted in Value at Risk principles, provides a framework to quantify the potential financial impacts of cybersecurity incidents. Initially developed to evaluate overall risk exposure across scenarios, our approach extends Cy-VaR to consider specific IoT layers: perception, network, and application. Each layer encompasses distinct functionalities and vulnerabilities, from sensor data acquisition (perception layer) to secure data transmission (network layer) and application-specific services (application layer). By calculating Cy- VaR for each layer and scenario, organizations can prioritize security investments effectively. This paper discusses methodologies and models, including scenario-based Cy-VaR and layer-specific risk assessments, emphasizing their application in enhancing IoT cybersecurity resilience. </t>
-  </si>
-  <si>
-    <t>Towards Explainable and Lightweight AI for Real-Time Cyber Threat Hunting in Edge Networks</t>
-  </si>
-  <si>
-    <t>As cyber threats continue to evolve, securing edge networks has become increasingly challenging due to their distributed nature and resource limitations. Many AI-driven threat detection systems rely on complex deep learning models, which, despite their high accuracy, suffer from two major drawbacks: lack of interpretability and high computational cost. Black-box AI models make it difficult for security analysts to understand the reasoning behind their predictions, limiting their practical deployment. Moreover, conventional deep learning techniques demand significant computational resources, rendering them unsuitable for edge devices with limited processing power. To address these issues, this study introduces an Explainable and Lightweight AI (ELAI) framework designed for real-time cyber threat detection in edge networks. Our approach integrates interpretable machine learning algorithms with optimized lightweight deep learning techniques, ensuring both transparency and computational efficiency. The proposed system leverages decision trees, attention-based deep learning, and federated learning to enhance detection accuracy while maintaining explainability. We evaluate ELAI using benchmark cybersecurity datasets, such as CICIDS and UNSW-NB15, assessing its performance across diverse cyberattack scenarios. Experimental results demonstrate that the proposed framework achieves high detection rates with minimal false positives, all while significantly reducing computational demands compared to traditional deep learning methods. The key contributions of this work include: (1) a novel interpretable AI-based cybersecurity model tailored for edge computing environments, (2) an optimized lightweight deep learning approach for real-time cyber threat detection, and (3) a comprehensive analysis of explainability techniques in AI-driven cybersecurity applications.</t>
-  </si>
-  <si>
-    <t>Exploring the Role of Large Language Models in Cybersecurity: A Systematic Survey</t>
-  </si>
-  <si>
-    <t>With the rapid development of technology and the acceleration of digitalisation, the frequency and complexity of cyber security threats are increasing. Traditional cybersecurity approaches, often based on static rules and predefined scenarios, are struggling to adapt to the rapidly evolving nature of modern cyberattacks. There is an urgent need for more adaptive and intelligent defence strategies. The emergence of Large Language Model (LLM) provides an innovative solution to cope with the increasingly severe cyber threats, and its potential in analysing complex attack patterns, predicting threats and assisting real-time response has attracted a lot of attention in the field of cybersecurity, and exploring how to effectively use LLM to defend against cyberattacks has become a hot topic in the current research field. This survey examines the applications of LLM from the perspective of the cyber attack lifecycle, focusing on the three phases of defense reconnaissance, foothold establishment, and lateral movement, and it analyzes the potential of LLMs in Cyber Threat Intelligence (CTI) tasks. Meanwhile, we investigate how LLM-based security solutions are deployed and applied in different network scenarios. It also summarizes the internal and external risk issues faced by LLM during its application. Finally, this survey also points out the facing risk issues and possible future research directions in this domain.</t>
-  </si>
-  <si>
-    <t>Rethinking trust in the digital age: An investigation of zero trust architecture's social consequences on organizational culture, collaboration, and knowledge sharing</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> As cyber threats escalate, Zero Trust Architecture (ZTA) replaces outdated perimeter security with strict never trust, always verify protocols. However, ZTA's dual nature as both technical infrastructure and social intervention creates an unresolved tension: its very mechanisms for security may systematically erode the trust foundations enabling effective collaboration. This integrative research combines case study analysis, employee surveys, and social network mapping reveals how ZTA disrupts knowledge-sharing, disproportionately hindering low-altruism employees, while surveillance erodes collective psychological ownership. Networked organizations, reliant on fluid trust, face fragmentation risks. Mitigation strategies include adaptive authorization frameworks using behavioral analytics and transparent communication reframing security as shared responsibility. Interdepartmental collaboration in security design preserves organizational trust structures identified through sociometric mapping. This research provides a framework balancing technical rigor with cultural sensitivity, proving cybersecurity can coexist with innovation by aligning verification with organizational psychology. The findings pioneer a paradigm where security and trust evolve synergistically critical for digital resilience in hybrid work environments. Future security must harmonize protocols with trust cultivation, ensuring defenses adapt to social dynamics driving modern enterprises.</t>
-  </si>
-  <si>
-    <t>Designing a reliable lateral movement detector using a graph foundation model</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Foundation models have recently emerged as a new paradigm in machine learning (ML). These models are pre-trained on large and diverse datasets and can subsequently be applied to various downstream tasks with little or no retraining. This allows people without advanced ML expertise to build ML applications, accelerating innovation across many fields. However, the adoption of foundation models in cybersecurity is hindered by their inability to efficiently process data such as network traffic captures or binary executables. The recent introduction of graph foundation models (GFMs) could make a significant difference, as graphs are well-suited to representing these types of data. We study the usability of GFMs in cybersecurity through the lens of one specific use case, namely lateral movement detection. Using a pre-trained GFM, we build a detector that reaches state-of-the-art performance without requiring any training on domain-specific data. This case study thus provides compelling evidence of the potential of GFMs for cybersecurity. </t>
-  </si>
-  <si>
-    <t>Investigating cybersecurity incidents using large language models in latest-generation wireless networks</t>
-  </si>
-  <si>
-    <t>The purpose of research: Detection of cybersecurity incidents and analysis of decision support and assessment of the effectiveness of measures to counter information security threats based on modern generative models. The methods of research: Emulation of signal propagation data in MIMO systems, synthesis of adversarial examples, execution of adversarial attacks on machine learning models, fine tuning of large language models for detecting adversarial attacks, explainability of decisions on detecting cybersecurity incidents based on the prompts technique. Scientific novelty: A binary classification of data poisoning attacks was performed using large language models, and the possibility of using large language models for investigating cybersecurity incidents in the latest generation wireless networks was investigated. The result of research: Fine-tuning of large language models was performed on the prepared data of the emulated wireless network segment. Six large language models were compared for detecting adversarial attacks, and the capabilities of explaining decisions made by a large language model were investigated. The Gemma-7b model showed the best results according to the metrics Precision = 0.89, Recall = 0.89 and F1-Score = 0.89. Based on various explainability prompts, the Gemma-7b model notes inconsistencies in the compromised data under study, performs feature importance analysis and provides various recommendations for mitigating the consequences of adversarial attacks. Large language models integrated with binary classifiers of network threats have significant potential for practical application in the field of cybersecurity incident investigation, decision support and assessing the effectiveness of measures to counter information security threats</t>
-  </si>
-  <si>
-    <t>The Evolution of Zero Trust Architecture (ZTA) from Concept to Implementation</t>
-  </si>
-  <si>
-    <t>Zero Trust Architecture (ZTA) is one of the paradigm changes in cybersecurity, from the traditional perimeter-based model to perimeterless. This article studies the core concepts of ZTA, its beginning, a few use cases and future trends. Emphasising the always verify and least privilege access, some key tenets of ZTA have grown to be integration technologies like Identity Management, Multi-Factor Authentication (MFA) and real-time analytics. ZTA is expected to strengthen cloud environments, education, work environments (including from home) while controlling other risks like lateral movement and insider threats. Despite ZTA's benefits, it comes with challenges in the form of complexity, performance overhead and vulnerabilities in the control plane. These require phased implementation and continuous refinement to keep up with evolving organisational needs and threat landscapes. Emerging technologies, such as Artificial Intelligence (AI) and Machine Learning (ML) will further automate policy enforcement and threat detection in keeping up with dynamic cyber threats.</t>
-  </si>
-  <si>
-    <t>Intelligent DoS and DDoS Detection: A Hybrid GRU-NTM Approach to Network Security</t>
-  </si>
-  <si>
-    <t>Detecting Denial of Service (DoS) and Distributed Denial of Service (DDoS) attacks remains a critical challenge in cybersecurity. This research introduces a hybrid deep learning model combining Gated Recurrent Units (GRUs) and a Neural Turing Machine (NTM) for enhanced intrusion detection. Trained on the UNSW-NB15 and BoT-IoT datasets, the model employs GRU layers for sequential data processing and an NTM for long-term pattern recognition. The proposed approach achieves 99% accuracy in distinguishing between normal, DoS, and DDoS traffic. These findings offer promising advancements in real-time threat detection and contribute to improved network security across various domains.</t>
-  </si>
-  <si>
-    <t>WeiDetect: Weibull Distribution-Based Defense against Poisoning Attacks in Federated Learning for Network Intrusion Detection Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> In the era of data expansion, ensuring data privacy has become increasingly critical, posing significant challenges to traditional AI-based applications. In addition, the increasing adoption of IoT devices has introduced significant cybersecurity challenges, making traditional Network Intrusion Detection Systems (NIDS) less effective against evolving threats, and privacy concerns and regulatory restrictions limit their deployment. Federated Learning (FL) has emerged as a promising solution, allowing decentralized model training while maintaining data privacy to solve these issues. However, despite implementing privacy-preserving technologies, FL systems remain vulnerable to adversarial attacks. Furthermore, data distribution among clients is not heterogeneous in the FL scenario. We propose WeiDetect, a two-phase, server-side defense mechanism for FL-based NIDS that detects malicious participants to address these challenges. In the first phase, local models are evaluated using a validation dataset to generate validation scores. These scores are then analyzed using a Weibull distribution, identifying and removing malicious models. We conducted experiments to evaluate the effectiveness of our approach in diverse attack settings. Our evaluation included two popular datasets, CIC-Darknet2020 and CSE-CIC-IDS2018, tested under non-IID data distributions. Our findings highlight that WeiDetect outperforms state-of-the-art defense approaches, improving higher target class recall up to 70% and enhancing the global model's F1 score by 1% to 14%. </t>
-  </si>
-  <si>
-    <t>Hierarchical Local-Global Feature Learning for Few-shot Malicious Traffic Detection</t>
-  </si>
-  <si>
-    <t>With the rapid growth of internet traffic, malicious network attacks have become increasingly frequent and sophisticated, posing significant threats to global cybersecurity. Traditional detection methods, including rule-based and machine learning-based approaches, struggle to accurately identify emerging threats, particularly in scenarios with limited samples. While recent advances in few-shot learning have partially addressed the data scarcity issue, existing methods still exhibit high false positive rates and lack the capability to effectively capture crucial local traffic patterns. In this paper, we propose HLoG, a novel hierarchical few-shot malicious traffic detection framework that leverages both local and global features extracted from network sessions. HLoG employs a sliding-window approach to segment sessions into phases, capturing fine-grained local interaction patterns through hierarchical bidirectional GRU encoding, while simultaneously modeling global contextual dependencies. We further design a session similarity assessment module that integrates local similarity with global self-attention-enhanced representations, achieving accurate and robust few-shot traffic classification. Comprehensive experiments on three meticulously reconstructed datasets demonstrate that HLoG significantly outperforms existing state-of-the-art methods. Particularly, HLoG achieves superior recall rates while substantially reducing false positives, highlighting its effectiveness and practical value in real-world cybersecurity applications.</t>
-  </si>
-  <si>
-    <t>Accelerating IoV Intrusion Detection: Benchmarking GPU-Accelerated vs CPU-Based ML Libraries</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The Internet of Vehicles (IoV) may face challenging cybersecurity attacks that may require sophisticated intrusion detection systems, necessitating a rapid development and response system. This research investigates the performance advantages of GPU-accelerated libraries (cuML) compared to traditional CPU-based implementations (scikit-learn), focusing on the speed and efficiency required for machine learning models used in IoV threat detection environments. The comprehensive evaluations conducted employ four machine learning approaches (Random Forest, KNN, Logistic Regression, XGBoost) across three distinct IoV security datasets (OTIDS, GIDS, CICIoV2024). Our findings demonstrate that GPU-accelerated implementations dramatically improved computational efficiency, with training times reduced by a factor of up to 159 and prediction speeds accelerated by up to 95 times compared to traditional CPU processing, all while preserving detection accuracy. This remarkable performance breakthrough empowers researchers and security specialists to harness GPU acceleration for creating faster, more effective threat detection systems that meet the urgent real-time security demands of today's connected vehicle networks.</t>
-  </si>
-  <si>
-    <t>Adaptive Federated Learning with Functional Encryption: A Comparison of Classical and Quantum-safe Options</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Federated Learning (FL) is a collaborative method for training machine learning models while preserving the confidentiality of the participants' training data. Nevertheless, FL is vulnerable to reconstruction attacks that exploit shared parameters to reveal private training data. In this paper, we address this issue in the cybersecurity domain by applying Multi-Input Functional Encryption (MIFE) to a recent FL implementation for training ML-based network intrusion detection systems. We assess both classical and post-quantum solutions in terms of memory cost and computational overhead in the FL process, highlighting their impact on convergence time. </t>
-  </si>
-  <si>
-    <t>Methodology for Detecting Energy Anomalies due to Multi-Replay Attacks on Electric Vehicle Charging Infrastructure</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The increasing deployment of Electric Vehicle Charging Infrastructures (EVCIs) introduces cybersecurity challenges, particularly due to inherent vulnerabilities, making them susceptible to cyberattacks. The vulnerable points in EVCI are charging ports, which serve as the links between the EVs and the EVCI as they transfer the data along with the power. Data spoofing attacks targeting these ports can compromise security, reliability, and overall system performance by introducing anomalies in operational data. An efficient method for identifying the charging port current magnitude variations is presented in this research. The MATLAB/SIMULINK environment simulates an EVCI system for various data generating scenarios. A Temporal Convolution Network - Autoencoder (TCN-AE) model is used in training the multivariate time series data of EVCI and reconstructing it. The abnormalities in data are that various charging port current magnitudes are replaced with their respective data of different durations, thus enabling the replay attack scenarios. To detect anomalies, the error between the original and reconstructed data is computed, and these error values are used for detecting the anomalies. With the help of the mean vector and covariance matrices of the errors, the anomaly score is computed in the form of Mahalanobis distance. The threshold is obtained from the short sub-sequence of the errors and optimized for the whole time series data. The obtained optimal threshold is compared with the anomaly score to detect the anomaly. The model demonstrates robust performance in data reconstruction by identifying anomalies with an accuracy of 99.64%, to enhance the reliability and security in operations of EVCI. </t>
-  </si>
-  <si>
-    <t>Training Large Language Models for Advanced Typosquatting Detection</t>
-  </si>
-  <si>
-    <t>Typosquatting is a long-standing cyber threat that exploits human error in typing URLs to deceive users, distribute malware, and conduct phishing attacks. With the proliferation of domain names and new Top-Level Domains (TLDs), typosquatting techniques have grown more sophisticated, posing significant risks to individuals, businesses, and national cybersecurity infrastructure. Traditional detection methods primarily focus on well-known impersonation patterns, leaving gaps in identifying more complex attacks. This study introduces a novel approach leveraging large language models (LLMs) to enhance typosquatting detection. By training an LLM on character-level transformations and pattern-based heuristics rather than domain-specific data, a more adaptable and resilient detection mechanism develops. Experimental results indicate that the Phi-4 14B model outperformed other tested models when properly fine tuned achieving a 98% accuracy rate with only a few thousand training samples. This research highlights the potential of LLMs in cybersecurity applications, specifically in mitigating domain-based deception tactics, and provides insights into optimizing machine learning strategies for threat detection.</t>
-  </si>
-  <si>
-    <t>Redefining Network Topology in Complex Systems: Merging Centrality Metrics, Spectral Theory, and Diffusion Dynamics</t>
-  </si>
-  <si>
-    <t>This paper introduces a novel framework that combines traditional centrality measures with eigenvalue spectra and diffusion processes for a more comprehensive analysis of complex networks. While centrality measures such as degree, closeness, and betweenness have been commonly used to assess nodal importance, they provide limited insight into dynamic network behaviors. By incorporating eigenvalue analysis, which evaluates network robustness and connectivity through spectral properties, and diffusion processes that model information flow, this framework offers a deeper understanding of how networks function under dynamic conditions. Applied to synthetic networks, the approach identifies key nodes not only by centrality but also by their role in diffusion dynamics and vulnerability points, offering a multi-dimensional view that traditional methods alone cannot. This integrated analysis enables a more precise identification of critical nodes and potential weaknesses, with implications for improving network resilience in fields ranging from epidemiology to cybersecurity. Keywords: Centrality measures, eigenvalue spectra, diffusion processes, network analysis, network robustness, information flow, synthetic networks.</t>
-  </si>
-  <si>
-    <t>Advancing CAN Network Security through RBM-Based Synthetic Attack Data Generation for Intrusion Detection Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The rapid development of network technologies and industrial intelligence has augmented the connectivity and intelligence within the automotive industry. Notably, in the Internet of Vehicles (IoV), the Controller Area Network (CAN), which is crucial for the communication of electronic control units but lacks inbuilt security measures, has become extremely vulnerable to severe cybersecurity threats. Meanwhile, the efficacy of Intrusion Detection Systems (IDS) is hampered by the scarcity of sufficient attack data for robust model training. To overcome this limitation, we introduce a novel methodology leveraging the Restricted Boltzmann Machine (RBM) to generate synthetic CAN attack data, thereby producing training datasets with a more balanced sample distribution. Specifically, we design a CAN Data Processing Module for transforming raw CAN data into an RBM-trainable format, and a Negative Sample Generation Module to generate data reflecting the distribution of CAN data frames denoting network intrusions. Experimental results show the generated data significantly improves IDS performance, with CANet accuracy rising from 0.6477 to 0.9725 and EfficientNet from 0.1067 to 0.1555. Code is available at https://github.com/wangkai-tech23/CANDataSynthetic. </t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF333333"/>
-        <rFont val="Times New Roman"/>
-        <family val="1"/>
-      </rPr>
       <t>The widespread adoption of Internet of Things (IoT) devices has introduced significant </t>
     </r>
     <r>
@@ -2254,393 +2728,27 @@
     </r>
   </si>
   <si>
-    <t>Power Networks SCADA Communication Cybersecurity, A Qiskit Implementation</t>
-  </si>
-  <si>
-    <t>The cyber-physical system of electricity power networks utilizes supervisory control and data acquisition systems (SCADA), which are inherently vulnerable to cyber threats if usually connected with the internet technology (IT). Power system operations are conducted through communication systems that are mapped to standards, protocols, ports, and addresses. Real-time situational awareness is a standard term with implications and applications in both power systems and cybersecurity. In the plausible quantum world (Q-world), conventional approaches will likely face new challenges. The unique art of transmitting a quantum state from one place, Alice, to another, Bob, is known as quantum communication. Quantum communication for SCADA communication in a plausible quantum era thus obviously entails wired communication through optical fiber networks complying with the typical cybersecurity criteria of confidentiality, integrity, and availability for classical internet technology unless a quantum internet (qinternet) transpires practically. When combined with the reverse order of AIC for operational technology, the cybersecurity criteria for power networks' critical infrastructure drill down to more specific sub-areas. Unlike other communication modes, such as information technology (IT) in broadband internet connections, SCADA for power networks, one of the critical infrastructures, is intricately intertwined with operations technology (OT), which significantly increases complexity. Though it is desirable to have a barrier called a demilitarized zone (DMZ), some overlap is inevitable. This paper highlights the opportunities and challenges in securing SCADA communication in the plausible quantum computing and communication regime, along with a corresponding integrated Qiskit implementation for possible future framework development.</t>
-  </si>
-  <si>
-    <t>EVSOAR: Security Orchestration, Automation and Response via EV Charging Stations</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Vehicle cybersecurity has emerged as a critical concern, driven by the innovation in the automotive industry, e.g., automomous, electric, or connnected vehicles. Current efforts to address these challenges are constrained by the limited computational resources of vehicles and the reliance on connected infrastructures. This motivated the foundation of Vehicle Security Operations Centers (VSOCs) that extend IT-based Security Operations Centers (SOCs) to cover the entire automotive ecosystem, both the in-vehicle and off-vehicle scopes. Security Orchestration, Automation, and Response (SOAR) tools are considered key for impelementing an effective cybersecurity solution. However, existing state-of-the-art solutions depend on infrastructure networks such as 4G, 5G, and WiFi, which often face scalability and congestion issues. To address these limitations, we propose a novel SOAR architecture EVSOAR that leverages the EV charging stations for connectivity and computing to enhance vehicle cybersecurity. Our EV-specific SOAR architecture enables real-time analysis and automated responses to cybersecurity threats closer to the EV, reducing the cellular latency, bandwidth, and interference limitations. Our experimental results demonstrate a significant improvement in latency, stability, and scalability through the infrastructure and the capacity to deploy computationally intensive applications, that are otherwise infeasible within the resource constraints of individual vehicles. </t>
-  </si>
-  <si>
-    <t>Assessment of Cyberattack Detection-Isolation Algorithm for CAV Platoons Using SUMO</t>
-  </si>
-  <si>
-    <t>A Connected Autonomous Vehicle (CAV) platoon in an evolving real-world driving environment relies strongly on accurate vehicle-to-vehicle (V2V) and vehicle-to-infrastructure (V2I) communication for its safe and efficient operation. However, a cyberattack on this communication network can corrupt the appropriate control actions, tamper with system measurement, and drive the platoon to unsafe or undesired conditions. As a first step toward practicable resilience against such V2V-V2I attacks, in this paper, we implemented a unified V2V-V2I cyberattack detection scheme and a V2I isolation scheme for a CAV platoon under changing driving conditions in Simulation of Urban MObility (SUMO). The implemented algorithm utilizes vehicle-specific residual generators that are designed based on analytical disturbance-to-state stability, robustness, and sensitivity performance constraints. Our case studies include two driving scenarios where highway driving is simulated using the Next-Generation Simulation (NGSIM) data and urban driving follows the benchmark EPA Urban Dynamometer Driving Schedule (UDDS). The results validate the applicability of the algorithm to ensure CAV cybersecurity and demonstrate the promising potential for practical test-bed implementation in the future.</t>
-  </si>
-  <si>
-    <t>Quantum Computing and Cybersecurity Education: A Novel Curriculum for Enhancing Graduate STEM Learning</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Quantum computing is an emerging paradigm with the potential to transform numerous application areas by addressing problems considered intractable in the classical domain. However, its integration into cyberspace introduces significant security and privacy challenges. The exponential rise in cyber attacks, further complicated by quantum capabilities, poses serious risks to financial systems and national security. The scope of quantum threats extends beyond traditional software, operating system, and network vulnerabilities, necessitating a shift in cybersecurity education. Traditional cybersecurity education, often reliant on didactic methods, lacks hands on, student centered learning experiences necessary to prepare students for these evolving challenges. There is an urgent need for curricula that address both classical and quantum security threats through experiential learning. In this work, we present the design and evaluation of EE 597: Introduction to Hardware Security, a graduate level course integrating hands-on quantum security learning with classical security concepts through simulations and cloud-based quantum hardware. Unlike conventional courses focused on quantum threats to cryptographic systems, EE 597 explores security challenges specific to quantum computing itself. We employ a mixed-methods evaluation using pre and post surveys to assess student learning outcomes and engagement. Results indicate significant improvements in students' understanding of quantum and hardware security, with strong positive feedback on course structure and remote instruction (mean scores: 3.33 to 3.83 on a 4 point scale). </t>
-  </si>
-  <si>
-    <t>Domination in Graph Theory: A Bibliometric Analysis of Research Trends, Collaboration and Citation Networks</t>
-  </si>
-  <si>
-    <t>This study conducts a comprehensive bibliometric analysis of research on domination in graph theory from 1961 to 2024, based on Scopus-indexed publications retrieved using the query (dominating OR domination) AND graph. The analysis examines publication trends, key contributors, collaboration patterns, citation impact, and emerging research themes. Results indicate a significant and sustained increase in research output, particularly in recent decades. Henning, M.A., Hedetniemi, S.T., and Haynes, T.W. are identified as the most highly cited researchers, underscoring their foundational contributions to the field. Co-authorship network analysis reveals strong international collaborations, with Sheikhholeslami, S.M. exhibiting the highest total link strength, while the United States emerges as the leading hub for global research partnerships. Keyword co-occurrence analysis identifies four major research clusters: graph algorithms, graph-theoretic foundations, domination variants, and binary graph operations. Notably, recent studies increasingly focus on how domination properties evolve under different graph operations. Citation network analysis confirms the enduring influence of foundational studies while highlighting a shift towards computational and applied methodologies. These findings highlight the transition from theoretical to applied research, emphasizing the role of advanced algorithms, interdisciplinary approaches, and large-scale computational techniques. Future research directions should explore machine learning-based optimization, domination in evolving networks, and applications in cybersecurity, bioinformatics, and large-scale social networks.</t>
-  </si>
-  <si>
-    <t>PacketCLIP: Multi-Modal Embedding of Network Traffic and Language for Cybersecurity Reasoning</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Traffic classification is vital for cybersecurity, yet encrypted traffic poses significant challenges. We present PacketCLIP, a multi-modal framework combining packet data with natural language semantics through contrastive pretraining and hierarchical Graph Neural Network (GNN) reasoning. PacketCLIP integrates semantic reasoning with efficient classification, enabling robust detection of anomalies in encrypted network flows. By aligning textual descriptions with packet behaviors, it offers enhanced interpretability, scalability, and practical applicability across diverse security scenarios. PacketCLIP achieves a 95% mean AUC, outperforms baselines by 11.6%, and reduces model size by 92%, making it ideal for real-time anomaly detection. By bridging advanced machine learning techniques and practical cybersecurity needs, PacketCLIP provides a foundation for scalable, efficient, and interpretable solutions to tackle encrypted traffic classification and network intrusion detection challenges in resource-constrained environments.</t>
-  </si>
-  <si>
-    <t>Network Anomaly Detection for IoT Using Hyperdimensional Computing on NSL-KDD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">With the rapid growth of IoT devices, ensuring robust network security has become a critical challenge. Traditional intrusion detection systems (IDSs) often face limitations in detecting sophisticated attacks within high-dimensional and complex data environments. This paper presents a novel approach to network anomaly detection using hyperdimensional computing (HDC) techniques, specifically applied to the NSL-KDD dataset. The proposed method leverages the efficiency of HDC in processing large-scale data to identify both known and unknown attack patterns. The model achieved an accuracy of 91.55% on the KDDTrain+ subset, outperforming traditional approaches. These comparative evaluations underscore the model's superior performance, highlighting its potential in advancing anomaly detection for IoT networks and contributing to more secure and intelligent cybersecurity solutions. </t>
-  </si>
-  <si>
-    <t>A Kolmogorov-Arnold Network for Explainable Detection of Cyberattacks on EV Chargers</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The increasing adoption of Electric Vehicles (EVs) and the expansion of charging infrastructure and their reliance on communication expose Electric Vehicle Supply Equipment (EVSE) to cyberattacks. This paper presents a novel Kolmogorov-Arnold Network (KAN)-based framework for detecting cyberattacks on EV chargers using only power consumption measurements. Leveraging the KAN's capability to model nonlinear, high-dimensional functions and its inherently interpretable architecture, the framework effectively differentiates between normal and malicious charging scenarios. The model is trained offline on a comprehensive dataset containing over 100,000 cyberattack cases generated through an experimental setup. Once trained, the KAN model can be deployed within individual chargers for real-time detection of abnormal charging behaviors indicative of cyberattacks. Our results demonstrate that the proposed KAN-based approach can accurately detect cyberattacks on EV chargers with Precision and F1-score of 99% and 92%, respectively, outperforming existing detection methods. Additionally, the proposed KANs's enable the extraction of mathematical formulas representing KAN's detection decisions, addressing interpretability, a key challenge in deep learning-based cybersecurity frameworks. This work marks a significant step toward building secure and explainable EV charging infrastructure.</t>
-  </si>
-  <si>
-    <t>The Road Less Traveled: Investigating Robustness and Explainability in CNN Malware Detection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Machine learning has become a key tool in cybersecurity, improving both attack strategies and defense mechanisms. Deep learning models, particularly Convolutional Neural Networks (CNNs), have demonstrated high accuracy in detecting malware images generated from binary data. However, the decision-making process of these black-box models remains difficult to interpret. This study addresses this challenge by integrating quantitative analysis with explainability tools such as Occlusion Maps, HiResCAM, and SHAP to better understand CNN behavior in malware classification. We further demonstrate that obfuscation techniques can reduce model accuracy by up to 50%, and propose a mitigation strategy to enhance robustness. Additionally, we analyze heatmaps from multiple tests and outline a methodology for identification of artifacts, aiding researchers in conducting detailed manual investigations. This work contributes to improving the interpretability and resilience of deep learning-based intrusion detection systems </t>
-  </si>
-  <si>
-    <t>CAGN-GAT Fusion: A Hybrid Contrastive Attentive Graph Neural Network for Network Intrusion Detection</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Cybersecurity threats are growing, making network intrusion detection essential. Traditional machine learning models remain effective in resource-limited environments due to their efficiency, requiring fewer parameters and less computational time. However, handling short and highly imbalanced datasets remains challenging. In this study, we propose the fusion of a Contrastive Attentive Graph Network and Graph Attention Network (CAGN-GAT Fusion) and benchmark it against 15 other models, including both Graph Neural Networks (GNNs) and traditional ML models. Our evaluation is conducted on four benchmark datasets (KDD-CUP-1999, NSL-KDD, UNSW-NB15, and CICIDS2017) using a short and proportionally imbalanced dataset with a constant size of 5000 samples to ensure fairness in comparison. Results show that CAGN-GAT Fusion demonstrates stable and competitive accuracy, recall, and F1-score, even though it does not achieve the highest performance in every dataset. Our analysis also highlights the impact of adaptive graph construction techniques, including small changes in connections (edge perturbation) and selective hiding of features (feature masking), improving detection performance. The findings confirm that GNNs, particularly CAGN-GAT Fusion, are robust and computationally efficient, making them well-suited for resource-constrained environments. Future work will explore GraphSAGE layers and multiview graph construction techniques to further enhance adaptability and detection accuracy.</t>
-  </si>
-  <si>
-    <t>Towards Zero Touch Networks: Cross-Layer Automated Security Solutions for 6G Wireless Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The transition from 5G to 6G mobile networks necessitates network automation to meet the escalating demands for high data rates, ultra-low latency, and integrated technology. Recently, Zero-Touch Networks (ZTNs), driven by Artificial Intelligence (AI) and Machine Learning (ML), are designed to automate the entire lifecycle of network operations with minimal human intervention, presenting a promising solution for enhancing automation in 5G/6G networks. However, the implementation of ZTNs brings forth the need for autonomous and robust cybersecurity solutions, as ZTNs rely heavily on automation. AI/ML algorithms are widely used to develop cybersecurity mechanisms, but require substantial specialized expertise and encounter model drift issues, posing significant challenges in developing autonomous cybersecurity measures. Therefore, this paper proposes an automated security framework targeting Physical Layer Authentication (PLA) and Cross-Layer Intrusion Detection Systems (CLIDS) to address security concerns at multiple Internet protocol layers. The proposed framework employs drift-adaptive online learning techniques and a novel enhanced Successive Halving (SH)-based Automated ML (AutoML) method to automatically generate optimized ML models for dynamic networking environments. Experimental results illustrate that the proposed framework achieves high performance on the public Radio Frequency (RF) fingerprinting and the Canadian Institute for CICIDS2017 datasets, showcasing its effectiveness in addressing PLA and CLIDS tasks within dynamic and complex networking environments. Furthermore, the paper explores open challenges and research directions in the 5G/6G cybersecurity domain. This framework represents a significant advancement towards fully autonomous and secure 6G networks, paving the way for future innovations in network automation and cybersecurity.</t>
-  </si>
-  <si>
-    <t>SSD: A State-based Stealthy Backdoor Attack For Navigation System in UAV Route Planning</t>
-  </si>
-  <si>
-    <t>Unmanned aerial vehicles (UAVs) are increasingly employed to perform high-risk tasks that require minimal human intervention. However, UAVs face escalating cybersecurity threats, particularly from GNSS spoofing attacks. While previous studies have extensively investigated the impacts of GNSS spoofing on UAVs, few have focused on its effects on specific tasks. Moreover, the influence of UAV motion states on the assessment of network security risks is often overlooked. To address these gaps, we first provide a detailed evaluation of how motion states affect the effectiveness of network attacks. We demonstrate that nonlinear motion states not only enhance the effectiveness of position spoofing in GNSS spoofing attacks but also reduce the probability of speed-related attack detection. Building upon this, we propose a state-triggered backdoor attack method (SSD) to deceive GNSS systems and assess its risk to trajectory planning tasks. Extensive validation of SSD's effectiveness and stealthiness is conducted. Experimental results show that, with appropriately tuned hyperparameters, SSD significantly increases positioning errors and the risk of task failure, while maintaining 100% stealth across three state-of-the-art detectors</t>
-  </si>
-  <si>
-    <t>Rebalancing the Scales: A Systematic Mapping Study of Generative Adversarial Networks (GANs) in Addressing Data Imbalance</t>
-  </si>
-  <si>
-    <t>Machine learning algorithms are used in diverse domains, many of which face significant challenges due to data imbalance. Studies have explored various approaches to address the issue, like data preprocessing, cost-sensitive learning, and ensemble methods. Generative Adversarial Networks (GANs) showed immense potential as a data preprocessing technique that generates good quality synthetic data. This study employs a systematic mapping methodology to analyze 3041 papers on GAN-based sampling techniques for imbalanced data sourced from four digital libraries. A filtering process identified 100 key studies spanning domains such as healthcare, finance, and cybersecurity. Through comprehensive quantitative analysis, this research introduces three categorization mappings as application domains, GAN techniques, and GAN variants used to handle the imbalanced nature of the data. GAN-based over-sampling emerges as an effective preprocessing method. Advanced architectures and tailored frameworks helped GANs to improve further in the case of data imbalance. GAN variants like vanilla GAN, CTGAN, and CGAN show great adaptability in structured imbalanced data cases. Interest in GANs for imbalanced data has grown tremendously, touching a peak in recent years, with journals and conferences playing crucial roles in transmitting foundational theories and practical applications. While with these advances, none of the reviewed studies explicitly explore hybridized GAN frameworks with diffusion models or reinforcement learning techniques. This gap leads to a future research idea develop innovative approaches for effectively handling data imbalance.</t>
-  </si>
-  <si>
-    <t>Cyber security of OT networks: A tutorial and overview</t>
-  </si>
-  <si>
-    <t>This manuscript explores the cybersecurity challenges of Operational Technology (OT) networks, focusing on their critical role in industrial environments such as manufacturing, energy, and utilities. As OT systems increasingly integrate with Information Technology (IT) systems due to Industry 4.0 initiatives, they become more vulnerable to cyberattacks, which pose risks not only to data but also to physical infrastructure. The study examines key components of OT systems, such as SCADA (Supervisory Control and Data Acquisition), PLCs (Programmable Logic Controllers), and RTUs (Remote Terminal Units), and analyzes recent cyberattacks targeting OT environments. Furthermore, it highlights the security concerns arising from the convergence of IT and OT systems, examining attack vectors and the growing threats posed by malware, ransomware, and nation-state actors. Finally, the paper discusses modern approaches and tools used to secure these environments, providing insights into improving the cybersecurity posture of OT networks.</t>
-  </si>
-  <si>
-    <t>Hybrid Machine Learning Models for Intrusion Detection in IoT: Leveraging a Real-World IoT Dataset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The rapid growth of the Internet of Things (IoT) has revolutionized industries, enabling unprecedented connectivity and functionality. However, this expansion also increases vulnerabilities, exposing IoT networks to increasingly sophisticated cyberattacks. Intrusion Detection Systems (IDS) are crucial for mitigating these threats, and recent advancements in Machine Learning (ML) offer promising avenues for improvement. This research explores a hybrid approach, combining several standalone ML models such as Random Forest (RF), XGBoost, K-Nearest Neighbors (KNN), and AdaBoost, in a voting-based hybrid classifier for effective IoT intrusion detection. This ensemble method leverages the strengths of individual algorithms to enhance accuracy and address challenges related to data complexity and scalability. Using the widely-cited IoT-23 dataset, a prominent benchmark in IoT cybersecurity research, we evaluate our hybrid classifiers for both binary and multi-class intrusion detection problems, ensuring a fair comparison with existing literature. Results demonstrate that our proposed hybrid models, designed for robustness and scalability, outperform standalone approaches in IoT environments. This work contributes to the development of advanced, intelligent IDS frameworks capable of addressing evolving cyber threats. </t>
-  </si>
-  <si>
-    <t>Enhanced Anomaly Detection in IoMT Networks using Ensemble AI Models on the CICIoMT2024 Dataset</t>
-  </si>
-  <si>
-    <t>The rapid proliferation of Internet of Medical Things (IoMT) devices in healthcare has introduced unique cybersecurity challenges, primarily due to the diverse communication protocols and critical nature of these devices This research aims to develop an advanced, real-time anomaly detection framework tailored for IoMT network traffic, leveraging AI/ML models and the CICIoMT2024 dataset By integrating multi-protocol (MQTT, WiFi), attack-specific (DoS, DDoS), time-series (active/idle states), and device-specific (Bluetooth) data, our study captures a comprehensive range of IoMT interactions As part of our data analysis, various machine learning techniques are employed which include an ensemble model using XGBoost for improved performance against specific attack types, sequential models comprised of LSTM and CNN-LSTM that leverage time dependencies, and unsupervised models such as Autoencoders and Isolation Forest that are good in general anomaly detection The results of the experiment prove with an ensemble model lowers false positive rates and reduced detections.</t>
-  </si>
-  <si>
-    <t>Evaluating the Potential of Quantum Machine Learning in Cybersecurity: A Case-Study on PCA-based Intrusion Detection Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quantum computing promises to revolutionize our understanding of the limits of computation, and its implications in cryptography have long been evident. Today, cryptographers are actively devising post-quantum solutions to counter the threats posed by quantum-enabled adversaries. Meanwhile, quantum scientists are innovating quantum protocols to empower defenders. However, the broader impact of quantum computing and quantum machine learning (QML) on other cybersecurity domains still needs to be explored. In this work, we investigate the potential impact of QML on cybersecurity applications of traditional ML. First, we explore the potential advantages of quantum computing in machine learning problems specifically related to cybersecurity. Then, we describe a methodology to quantify the future impact of fault-tolerant QML algorithms on real-world problems. As a case study, we apply our approach to standard methods and datasets in network intrusion detection, one of the most studied applications of machine learning in cybersecurity. Our results provide insight into the conditions for obtaining a quantum advantage and the need for future quantum hardware and software advancements. </t>
-  </si>
-  <si>
-    <t>A Computational Model for Ransomware Detection Using Cross-Domain Entropy Signatures</t>
-  </si>
-  <si>
-    <t>Detecting encryption-driven cyber threats remains a large challenge due to the evolving techniques employed to evade traditional detection mechanisms. An entropy-based computational framework was introduced to analyze multi-domain system variations, enabling the identification of malicious encryption behaviors through entropy deviations. By integrating entropy patterns across file operations, memory allocations, and network transmissions, a detection methodology was developed to differentiate between benign and ransomware-induced entropy shifts. A mathematical model was formulated to quantify entropy dynamics, incorporating time-dependent variations and weighted domain contributions to enhance anomaly detection. Experimental evaluations demonstrated that the proposed approach achieved high accuracy across diverse ransomware families while maintaining low false positive rates. Computational efficiency analysis indicated minimal processing overhead, suggesting feasibility for real-time implementation in security-sensitive environments. The study highlighted entropy fluctuations as a useful indicator for identifying malicious encryption processes, reinforcing entropy-driven methodologies as a viable component of cybersecurity strategies.</t>
-  </si>
-  <si>
-    <t>Federated Learning-Driven Cybersecurity Framework for IoT Networks with Privacy-Preserving and Real-Time Threat Detection Capabilities</t>
-  </si>
-  <si>
-    <t>The rapid expansion of the Internet of Things (IoT) ecosystem has transformed various sectors but has also introduced significant cybersecurity challenges. Traditional centralized security methods often struggle to balance privacy preservation and real-time threat detection in IoT networks. To address these issues, this study proposes a Federated Learning-Driven Cybersecurity Framework designed specifically for IoT environments. The framework enables decentralized data processing by training models locally on edge devices, ensuring data privacy. Secure aggregation of these locally trained models is achieved using homomorphic encryption, allowing collaborative learning without exposing sensitive information. The proposed framework utilizes recurrent neural networks (RNNs) for anomaly detection, optimized for resource-constrained IoT networks. Experimental results demonstrate that the system effectively detects complex cyber threats, including distributed denial-of-service (DDoS) attacks, with over 98% accuracy. Additionally, it improves energy efficiency by reducing resource consumption by 20% compared to centralized approaches. This research addresses critical gaps in IoT cybersecurity by integrating federated learning with advanced threat detection techniques. The framework offers a scalable and privacy-preserving solution adaptable to various IoT applications. Future work will explore the integration of blockchain for transparent model aggregation and quantum-resistant cryptographic methods to further enhance security in evolving technological landscapes.</t>
-  </si>
-  <si>
-    <t>Supply Chain Network Security Investment Strategies Based on Nonlinear Budget Constraints: The Moderating Roles of Market Share and Attack Risk</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> In the context of the rapid development of digital supply chain networks, dealing with the increasing cybersecurity threats and formulating effective security investment strategies to defend against cyberattack risks are the core issues in supply chain management. Cybersecurity investment decision-making is a key strategic task in enterprise supply chain manage-ment. Traditional game theory models and linear programming methods make it challenging to deal with complex problems such as multi-party par-ticipation in the supply chain, resource constraints, and risk uncertainty, re-sulting in enterprises facing high risks and uncertainties in the field of cy-bersecurity. To effectively meet this challenge, this study proposes a nonlin-ear budget-constrained cybersecurity investment optimization model based on variational inequality and projection shrinkage algorithm. This method simulates the impact of market competition on security investment by intro-ducing market share variables, combining variational inequality and projec-tion shrinkage algorithm to solve the model, and analyzing the effect of dif-ferent variables such as budget constraints, cyberattack losses, and market share on supply chain network security. In numerical analysis, the model achieved high cybersecurity levels of 0.96 and 0.95 in the experimental sce-narios of two retailers and two demand markets, respectively, and the budget constraint analysis revealed the profound impact of budget constraints on cybersecurity investment. Through numerical experiments and comparative analysis, the effectiveness and operability of this method in improving sup-ply chain network security are verified.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-Quantum-driven Zero Trust Framework with Dynamic Anomaly Detection in 7G Technology: A Neural Network Approach
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> As cyber threats become more complex, modern networks struggle to balance security, scalability, and computational efficiency. While quantum computing offers a promising solution, adoption is limited by scalability constraints, inefficiencies in data encoding, and high computational costs. To address these challenges, we propose the Quantum Neural Network-Enhanced Zero Trust Framework (QNN-ZTF), integrating Zero Trust Architecture, Intrusion Detection Systems, and Quantum Neural Networks (QNNs) for enhanced security. Leveraging superposition, entanglement, and variational optimization, QNN-ZTF enables real-time anomaly detection and adaptive policy enforcement. Key contributions include a hybrid quantum-classical architecture for scalability, dynamic anomaly scoring for improved detection accuracy, and quantum micro-segmentation to contain threats and restrict lateral movement. Evaluation results show improved cyber threat mitigation, demonstrating the framework's effectiveness in reducing false positives and response times. This research establishes a scalable, adaptive, and quantum-optimized cybersecurity model, advancing quantum-enhanced security for next-generation networks.</t>
-  </si>
-  <si>
-    <t>Network Intrusion Datasets: A Survey, Limitations, and Recommendations</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Data-driven cyberthreat detection has become a crucial defense technique in modern cybersecurity. Network defense, supported by Network Intrusion Detection Systems (NIDSs), has also increasingly adopted data-driven approaches, leading to greater reliance on data. Despite the importance of data, its scarcity has long been recognized as a major obstacle in NIDS research. In response, the community has published many new datasets recently. However, many of them remain largely unknown and unanalyzed, leaving researchers uncertain about their suitability for specific use cases. In this paper, we aim to address this knowledge gap by performing a systematic literature review (SLR) of 89 public datasets for NIDS research. Each dataset is comparatively analyzed across 13 key properties, and its potential applications are outlined. Beyond the review, we also discuss domain-specific challenges and common data limitations to facilitate a critical view on data quality. To aid in data selection, we conduct a dataset popularity analysis in contemporary state-of-the-art NIDS research. Furthermore, the paper presents best practices for dataset selection, generation, and usage. By providing a comprehensive overview of the domain and its data, this work aims to guide future research toward improving data quality and the robustness of NIDS solutions.</t>
-  </si>
-  <si>
-    <t>Can LLMs Hack Enterprise Networks? Autonomous Assumed Breach Penetration-Testing Active Directory Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Penetration-testing, while critical for validating defenses and uncovering vulnerabilities, is often limited by high operational costs and the scarcity of human expertise. This paper investigates the feasibility and effectiveness of using Large Language Model (LLM)-driven autonomous systems to address these challenges in real-world Microsoft Active Directory (AD) enterprise networks. Our novel prototype, cochise, represents the first demonstration of a fully autonomous, LLM-driven framework capable of compromising accounts within a real-life Microsoft AD testbed (GOAD). The evaluation deliberately utilizes GOAD to capture the intricate interactions and sometimes nondeterministic outcomes of live network pen-testing, moving beyond the limitations of synthetic benchmarks. We perform our empirical evaluation using five LLMs, comparing reasoning to non-reasoning models as well as including open-weight models. Through comprehensive quantitative and qualitative analysis, incorporating insights from cybersecurity experts, we demonstrate that autonomous LLMs can effectively conduct Assumed Breach simulations. Key findings highlight their ability to dynamically adapt attack strategies, perform inter-context attacks, and generate scenario-specific attack parameters. Cochise also exhibits robust self-correction mechanisms, automatically installing missing tools and rectifying invalid command generations. Critically, we find that the associated costs are competitive with those incurred by professional pen-testers, suggesting a path toward democratizing access to essential security testing for organizations with budgetary constraints. However, our research also illuminates existing limitations, including instances of LLM ``going down rabbit holes'', challenges in comprehensive information transfer between planning and execution modules, and critical safety concerns that necessitate human oversight. </t>
-  </si>
-  <si>
-    <t>Optimal Security Response to Network Intrusions in IT Systems</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Cybersecurity is one of the most pressing technological challenges of our time and requires measures from all sectors of society. A key measure is automated security response, which enables automated mitigation and recovery from cyber attacks. Significant strides toward such automation have been made due to the development of rule-based response systems. However, these systems have a critical drawback: they depend on domain experts to configure the rules, a process that is both error-prone and inefficient. Framing security response as an optimal control problem shows promise in addressing this limitation but introduces new challenges. Chief among them is bridging the gap between theoretical optimality and operational performance. Current response systems with theoretical optimality guarantees have only been validated analytically or in simulation, leaving their practical utility unproven. This thesis tackles the aforementioned challenges by developing a practical methodology for optimal security response in IT infrastructures. It encompasses two systems. First, it includes an emulation system that replicates key components of the target infrastructure. We use this system to gather measurements and logs, based on which we identify a game-theoretic model. Second, it includes a simulation system where game-theoretic response strategies are optimized through stochastic approximation to meet a given objective, such as mitigating potential attacks while maintaining operational services. These strategies are then evaluated and refined in the emulation system to close the gap between theoretical and operational performance. We prove structural properties of optimal response strategies and derive efficient algorithms for computing them. This enables us to solve a previously unsolved problem: demonstrating optimal security response against network intrusions on an IT infrastructure.</t>
-  </si>
-  <si>
-    <t>CryptoDNA: A Machine Learning Paradigm for DDoS Detection in Healthcare IoT, Inspired by crypto jacking prevention Models</t>
-  </si>
-  <si>
-    <t>The rapid integration of the Internet of Things (IoT) and Internet of Medical (IoM) devices in the healthcare industry has markedly improved patient care and hospital operations but has concurrently brought substantial risks. Distributed Denial-of-Service (DDoS) attacks present significant dangers, jeopardizing operational stability and patient safety. This study introduces CryptoDNA, an innovative machine learning detection framework influenced by cryptojacking detection methods, designed to identify and alleviate DDoS attacks in healthcare IoT settings. The proposed approach relies on behavioral analytics, including atypical resource usage and network activity patterns. Key features derived from cryptojacking-inspired methodologies include entropy-based analysis of traffic, time-series monitoring of device performance, and dynamic anomaly detection. A lightweight architecture ensures inter-compatibility with resource-constrained IoT devices while maintaining high detection accuracy. The proposed architecture and model were tested in real-world and synthetic datasets to demonstrate the model's superior performance, achieving over 96% accuracy with minimal computational overhead. Comparative analysis reveals its resilience against emerging attack vectors and scalability across diverse device ecosystems. By bridging principles from cryptojacking and DDoS detection, CryptoDNA offers a robust, innovative solution to fortify the healthcare IoT landscape against evolving cyber threats and highlights the potential of interdisciplinary approaches in adaptive cybersecurity defense mechanisms for critical healthcare infrastructures</t>
-  </si>
-  <si>
-    <t>When Everyday Devices Become Weapons: A Closer Look at the Pager and Walkie-talkie Attacks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Battery-powered technologies like pagers and walkie-talkies have long been integral to civilian and military operations. However, the potential for such everyday devices to be weaponized has largely been underestimated in the realm of cybersecurity. In September 2024, Lebanon experienced a series of unprecedented, coordinated explosions triggered through compromised pagers and walkie-talkies, creating a new category of attack in the domain of cyber-physical warfare. This attack not only disrupted critical communication networks but also resulted in injuries, loss of life, and exposed significant national security vulnerabilities, prompting governments and organizations worldwide to reevaluate their cybersecurity frameworks. This article provides an in-depth investigation into the infamous Pager and Walkie-Talkie attacks, analyzing both technical and non-technical dimensions. Furthermore, the study extends its scope to explore vulnerabilities in other battery-powered infrastructures, such as battery management systems, highlighting their potential exploitation. Existing prevention and detection techniques are reviewed, with an emphasis on their limitations and the challenges they face in addressing emerging threats. Finally, the article discusses emerging methodologies, particularly focusing on the role of physical inspection, as a critical component of future security measures. This research aims to provide actionable insights to bolster the resilience of cyber-physical systems in an increasingly interconnected world. </t>
-  </si>
-  <si>
-    <t>TORCHLIGHT: Shedding LIGHT on Real-World Attacks on Cloudless IoT Devices Concealed within the Tor Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The rapidly expanding Internet of Things (IoT) landscape is shifting toward cloudless architectures, removing reliance on centralized cloud services but exposing devices directly to the internet and increasing their vulnerability to cyberattacks. Our research revealed an unexpected pattern of substantial Tor network traffic targeting cloudless IoT devices. suggesting that attackers are using Tor to anonymously exploit undisclosed vulnerabilities (possibly obtained from underground markets). To delve deeper into this phenomenon, we developed TORCHLIGHT, a tool designed to detect both known and unknown threats targeting cloudless IoT devices by analyzing Tor traffic. TORCHLIGHT filters traffic via specific IP patterns, strategically deploys virtual private server (VPS) nodes for cost-effective detection, and uses a chain-of-thought (CoT) process with large language models (LLMs) for accurate threat identification. Our results are significant: for the first time, we have demonstrated that attackers are indeed using Tor to conceal their identities while targeting cloudless IoT devices. Over a period of 12 months, TORCHLIGHT analyzed 26 TB of traffic, revealing 45 vulnerabilities, including 29 zero-day exploits with 25 CVE-IDs assigned (5 CRITICAL, 3 HIGH, 16 MEDIUM, and 1 LOW) and an estimated value of approximately $312,000. These vulnerabilities affect around 12.71 million devices across 148 countries, exposing them to severe risks such as information disclosure, authentication bypass, and arbitrary command execution. The findings have attracted significant attention, sparking widespread discussion in cybersecurity circles, reaching the top 25 on Hacker News, and generating over 190,000 views. </t>
-  </si>
-  <si>
-    <t>Using hypervisors to create a cyber polygon</t>
-  </si>
-  <si>
-    <t>Cyber polygon used to train cybersecurity professionals, test new security technologies and simulate attacks play an important role in ensuring cybersecurity. The creation of such training grounds is based on the use of hypervisors, which allow efficient management of virtual machines, isolating operating systems and resources of a physical computer from virtual machines, ensuring a high level of security and stability. The paper analyses various aspects of using hypervisors in cyber polygons, including types of hypervisors, their main functions, and the specifics of their use in modelling cyber threats. The article shows the ability of hypervisors to increase the efficiency of hardware resources, create complex virtual environments for detailed modelling of network structures and simulation of real situations in cyberspace</t>
-  </si>
-  <si>
-    <t>Adaptive Cybersecurity: Dynamically Retrainable Firewalls for Real-Time Network Protection</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The growing complexity of cyber attacks has necessitated the evolution of firewall technologies from static models to adaptive, machine learning-driven systems. This research introduces "Dynamically Retrainable Firewalls", which respond to emerging threats in real-time. Unlike traditional firewalls that rely on static rules to inspect traffic, these advanced systems leverage machine learning algorithms to analyze network traffic pattern dynamically and identify threats. The study explores architectures such as micro-services and distributed systems for real-time adaptability, data sources for model retraining, and dynamic threat identification through reinforcement and continual learning. It also discusses strategies to improve performance, reduce latency, optimize resource utilization, and address integration issues with present-day concepts such as Zero Trust and mixed environments. By critically assessing the literature, analyzing case studies, and elucidating areas of future research, this work suggests dynamically retrainable firewalls as a more robust form of network security. Additionally, it considers emerging trends such as advancements in AI and quantum computing, ethical issues, and other regulatory questions surrounding future AI systems. These findings provide valuable information on the future state of adaptive cyber security, focusing on the need for proactive and adaptive measures that counter cyber threats that continue to evolve. </t>
-  </si>
-  <si>
-    <t>Integrating Cybersecurity in Predictive Cost-Benefit Power Scheduling: A DeepStack Model with Dynamic Defense Mechanism</t>
-  </si>
-  <si>
-    <t>This paper introduces a novel, deep learning-based predictive model tailored to address wind curtailment in contemporary power systems, while enhancing cybersecurity measures through the implementation of a Dynamic Defense Mechanism (DDM). The augmented BiLSTM architecture facilitates accurate short-term predictions for wind power. In addition, a ConvGAN-driven step for stochastic scenario generation and a hierarchical, multi-stage optimization framework, which includes cases with and without Battery Energy Storage (BES), significantly minimizes operational costs. The inclusion of DDM strategically alters network reactances, thereby obfuscating the system's operational parameters to deter cyber threats. This robust solution not only integrates wind power more efficiently into power grids, leveraging BES potential to improve the economic efficiency of the system, but also boosting the cyber security of the system. Validation using the Illinois 200-bus system demonstrates the model's potential, achieving a 98% accuracy in forecasting and substantial cost reductions of over 3.8%. The results underscore the dual benefits of enhancing system reliability and security through advanced deep learning architectures and the strategic application of cybersecurity measures.</t>
-  </si>
-  <si>
-    <t>A Novel Approach to Network Traffic Analysis: the HERA tool</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Cybersecurity threats highlight the need for robust network intrusion detection systems to identify malicious behaviour. These systems rely heavily on large datasets to train machine learning models capable of detecting patterns and predicting threats. In the past two decades, researchers have produced a multitude of datasets, however, some widely utilised recent datasets generated with CICFlowMeter contain inaccuracies. These result in flow generation and feature extraction inconsistencies, leading to skewed results and reduced system effectiveness. Other tools in this context lack ease of use, customizable feature sets, and flow labelling options. In this work, we introduce HERA, a new open-source tool that generates flow files and labelled or unlabelled datasets with user-defined features. Validated and tested with the UNSW-NB15 dataset, HERA demonstrated accurate flow and label generation.</t>
-  </si>
-  <si>
-    <t>Cybersecurity in Transportation Systems: Policies and Technology Directions</t>
-  </si>
-  <si>
-    <t>The transportation industry is experiencing vast digitalization as a plethora of technologies are being implemented to improve efficiency, functionality, and safety. Although technological advancements bring many benefits to transportation, integrating cyberspace across transportation sectors has introduced new and deliberate cyber threats. In the past, public agencies assumed digital infrastructure was secured since its vulnerabilities were unknown to adversaries. However, with the expansion of cyberspace, this assumption has become invalid. With the rapid advancement of wireless technologies, transportation systems are increasingly interconnected with both transportation and non-transportation networks in an internet-of-things ecosystem, expanding cyberspace in transportation and increasing threats and vulnerabilities. This study investigates some prominent reasons for the increase in cyber vulnerabilities in transportation. In addition, this study presents various collaborative strategies among stakeholders that could help improve cybersecurity in the transportation industry. These strategies address programmatic and policy aspects and suggest avenues for technological research and development. The latter highlights opportunities for future research to enhance the cybersecurity of transportation systems and infrastructure by leveraging hybrid approaches and emerging technologies.</t>
-  </si>
-  <si>
-    <t>CONTINUUM: Detecting APT Attacks through Spatial-Temporal Graph Neural Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Advanced Persistent Threats (APTs) represent a significant challenge in cybersecurity due to their sophisticated and stealthy nature. Traditional Intrusion Detection Systems (IDS) often fall short in detecting these multi-stage attacks. Recently, Graph Neural Networks (GNNs) have been employed to enhance IDS capabilities by analyzing the complex relationships within networked data. However, existing GNN-based solutions are hampered by high false positive rates and substantial resource consumption. In this paper, we present a novel IDS designed to detect APTs using a Spatio-Temporal Graph Neural Network Autoencoder. Our approach leverages spatial information to understand the interactions between entities within a graph and temporal information to capture the evolution of the graph over time. This dual perspective is crucial for identifying the sequential stages of APTs. Furthermore, to address privacy and scalability concerns, we deploy our architecture in a federated learning environment. This setup ensures that local data remains on-premise while encrypted model-weights are shared and aggregated using homomorphic encryption, maintaining data privacy and security. Our evaluation shows that this system effectively detects APTs with lower false positive rates and optimized resource usage compared to existing methods, highlighting the potential of spatio-temporal analysis and federated learning in enhancing cybersecurity defenses. </t>
-  </si>
-  <si>
-    <t>Predicting Vulnerability to Malware Using Machine Learning Models: A Study on Microsoft Windows Machines</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> In an era of escalating cyber threats, malware poses significant risks to individuals and organizations, potentially leading to data breaches, system failures, and substantial financial losses. This study addresses the urgent need for effective malware detection strategies by leveraging Machine Learning (ML) techniques on extensive datasets collected from Microsoft Windows Defender. Our research aims to develop an advanced ML model that accurately predicts malware vulnerabilities based on the specific conditions of individual machines. Moving beyond traditional signature-based detection methods, we incorporate historical data and innovative feature engineering to enhance detection capabilities. This study makes several contributions: first, it advances existing malware detection techniques by employing sophisticated ML algorithms; second, it utilizes a large-scale, real-world dataset to ensure the applicability of findings; third, it highlights the importance of feature analysis in identifying key indicators of malware infections; and fourth, it proposes models that can be adapted for enterprise environments, offering a proactive approach to safeguarding extensive networks against emerging threats. We aim to improve cybersecurity resilience, providing critical insights for practitioners in the field and addressing the evolving challenges posed by malware in a digital landscape. Finally, discussions on results, insights, and conclusions are presented</t>
-  </si>
-  <si>
-    <t>BARTPredict: Empowering IoT Security with LLM-Driven Cyber Threat Prediction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The integration of Internet of Things (IoT) technology in various domains has led to operational advancements, but it has also introduced new vulnerabilities to cybersecurity threats, as evidenced by recent widespread cyberattacks on IoT devices. Intrusion detection systems are often reactive, triggered by specific patterns or anomalies observed within the network. To address this challenge, this work proposes a proactive approach to anticipate and preemptively mitigate malicious activities, aiming to prevent potential damage before it occurs. This paper proposes an innovative intrusion prediction framework empowered by Pre-trained Large Language Models (LLMs). The framework incorporates two LLMs: a fine-tuned Bidirectional and AutoRegressive Transformers (BART) model for predicting network traffic and a fine-tuned Bidirectional Encoder Representations from Transformers (BERT) model for evaluating the predicted traffic. By harnessing the bidirectional capabilities of BART the framework then identifies malicious packets among these predictions. Evaluated using the CICIoT2023 IoT attack dataset, our framework showcases a notable enhancement in predictive performance, attaining an impressive 98% overall accuracy, providing a powerful response to the cybersecurity challenges that confront IoT networks. </t>
-  </si>
-  <si>
-    <t>FAPL-DM-BC: A Secure and Scalable FL Framework with Adaptive Privacy and Dynamic Masking, Blockchain, and XAI for the IoVs</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The FAPL-DM-BC solution is a new FL-based privacy, security, and scalability solution for the Internet of Vehicles (IoV). It leverages Federated Adaptive Privacy-Aware Learning (FAPL) and Dynamic Masking (DM) to learn and adaptively change privacy policies in response to changing data sensitivity and state in real-time, for the optimal privacy-utility tradeoff. Secure Logging and Verification, Blockchain-based provenance and decentralized validation, and Cloud Microservices Secure Aggregation using FedAvg (Federated Averaging) and Secure Multi-Party Computation (SMPC). Two-model feedback, driven by Model-Agnostic Explainable AI (XAI), certifies local predictions and explanations to drive it to the next level of efficiency. Combining local feedback with world knowledge through a weighted mean computation, FAPL-DM-BC assures federated learning that is secure, scalable, and interpretable. Self-driving cars, traffic management, and forecasting, vehicular network cybersecurity in real-time, and smart cities are a few possible applications of this integrated, privacy-safe, and high-performance IoV platform.</t>
-  </si>
-  <si>
-    <t>State-of-the-art AI-based Learning Approaches for Deepfake Generation and Detection, Analyzing Opportunities, Threading through Pros, Cons, and Future Prospects</t>
-  </si>
-  <si>
-    <t>The rapid advancement of deepfake technologies, specifically designed to create incredibly lifelike facial imagery and video content, has ignited a remarkable level of interest and curiosity across many fields, including forensic analysis, cybersecurity and the innovative creation of digital characters. By harnessing the latest breakthroughs in deep learning methods, such as Generative Adversarial Networks, Variational Autoencoders, Few-Shot Learning Strategies, and Transformers, the outcomes achieved in generating deepfakes have been nothing short of astounding and transformative. Also, the ongoing evolution of detection technologies is being developed to counteract the potential for misuse associated with deepfakes, effectively addressing critical concerns that range from political manipulation to the dissemination of fake news and the ever-growing issue of cyberbullying. This comprehensive review paper meticulously investigates the most recent developments in deepfake generation and detection, including around 400 publications, providing an in-depth analysis of the cutting-edge innovations shaping this rapidly evolving landscape. Starting with a thorough examination of systematic literature review methodologies, we embark on a journey that delves into the complex technical intricacies inherent in the various techniques used for deepfake generation, comprehensively addressing the challenges faced, potential solutions available, and the nuanced details surrounding manipulation formulations. Subsequently, the paper is dedicated to accurately benchmarking leading approaches against prominent datasets, offering thorough assessments of the contributions that have significantly impacted these vital domains. Ultimately, we engage in a thoughtful discussion of the existing challenges, paving the way for continuous advancements in this critical and ever-dynamic study area.</t>
-  </si>
-  <si>
-    <t>U-GIFT: Uncertainty-Guided Firewall for Toxic Speech in Few-Shot Scenario</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> With the widespread use of social media, user-generated content has surged on online platforms. When such content includes hateful, abusive, offensive, or cyberbullying behavior, it is classified as toxic speech, posing a significant threat to the online ecosystem's integrity and safety. While manual content moderation is still prevalent, the overwhelming volume of content and the psychological strain on human moderators underscore the need for automated toxic speech detection. Previously proposed detection methods often rely on large annotated datasets; however, acquiring such datasets is both costly and challenging in practice. To address this issue, we propose an uncertainty-guided firewall for toxic speech in few-shot scenarios, U-GIFT, that utilizes self-training to enhance detection performance even when labeled data is limited. Specifically, U-GIFT combines active learning with Bayesian Neural Networks (BNNs) to automatically identify high-quality samples from unlabeled data, prioritizing the selection of pseudo-labels with higher confidence for training based on uncertainty estimates derived from model predictions. Extensive experiments demonstrate that U-GIFT significantly outperforms competitive baselines in few-shot detection scenarios. In the 5-shot setting, it achieves a 14.92\% performance improvement over the basic model. Importantly, U-GIFT is user-friendly and adaptable to various pre-trained language models (PLMs). It also exhibits robust performance in scenarios with sample imbalance and cross-domain settings, while showcasing strong generalization across various language applications. We believe that U-GIFT provides an efficient solution for few-shot toxic speech detection, offering substantial support for automated content moderation in cyberspace, thereby acting as a firewall to promote advancements in cybersecurity.</t>
-  </si>
-  <si>
-    <t>LENS-XAI: Redefining Lightweight and Explainable Network Security through Knowledge Distillation and Variational Autoencoders for Scalable Intrusion Detection in Cybersecurity</t>
-  </si>
-  <si>
-    <t>The rapid proliferation of Industrial Internet of Things (IIoT) systems necessitates advanced, interpretable, and scalable intrusion detection systems (IDS) to combat emerging cyber threats. Traditional IDS face challenges such as high computational demands, limited explainability, and inflexibility against evolving attack patterns. To address these limitations, this study introduces the Lightweight Explainable Network Security framework (LENS-XAI), which combines robust intrusion detection with enhanced interpretability and scalability. LENS-XAI integrates knowledge distillation, variational autoencoder models, and attribution-based explainability techniques to achieve high detection accuracy and transparency in decision-making. By leveraging a training set comprising 10% of the available data, the framework optimizes computational efficiency without sacrificing performance. Experimental evaluation on four benchmark datasets: Edge-IIoTset, UKM-IDS20, CTU-13, and NSL-KDD, demonstrates the framework's superior performance, achieving detection accuracies of 95.34%, 99.92%, 98.42%, and 99.34%, respectively. Additionally, the framework excels in reducing false positives and adapting to complex attack scenarios, outperforming existing state-of-the-art methods. Key strengths of LENS-XAI include its lightweight design, suitable for resource-constrained environments, and its scalability across diverse IIoT and cybersecurity contexts. Moreover, the explainability module enhances trust and transparency, critical for practical deployment in dynamic and sensitive applications. This research contributes significantly to advancing IDS by addressing computational efficiency, feature interpretability, and real-world applicability. Future work could focus on extending the framework to ensemble AI systems for distributed environments, further enhancing its robustness and adaptability.</t>
-  </si>
-  <si>
-    <t>Collaborative Approaches to Enhancing Smart Vehicle Cybersecurity by AI-Driven Threat Detection</t>
-  </si>
-  <si>
-    <t>The introduction sets the stage for exploring collaborative approaches to bolstering smart vehicle cybersecurity through AI-driven threat detection. As the automotive industry increasingly adopts connected and automated vehicles (CAVs), the need for robust cybersecurity measures becomes paramount. With the emergence of new vulnerabilities and security requirements, the integration of advanced technologies such as 5G networks, blockchain, and quantum computing presents promising avenues for enhancing CAV cybersecurity . Additionally, the roadmap for cybersecurity in autonomous vehicles emphasizes the importance of efficient intrusion detection systems and AI-based techniques, along with the integration of secure hardware, software stacks, and advanced threat intelligence to address cybersecurity challenges in future autonomous vehicles.</t>
-  </si>
-  <si>
-    <t>Interactive cybersecurity training system based on simulation environments</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Rapid progress in the development of information technology has led to a significant increase in the number and complexity of cyber threats. Traditional methods of cybersecurity training based on theoretical knowledge do not provide a sufficient level of practical skills to effectively counter real threats. The article explores the possibilities of integrating simulation environments into the cybersecurity training process as an effective approach to improving the quality of training. The article presents the architecture of a simulation environment based on a cluster of KVM hypervisors, which allows creating scalable and flexible platforms at minimal cost. The article describes the implementation of various scenarios using open source software tools such as pfSense, OPNsense, Security Onion, Kali Linux, Parrot Security OS, Ubuntu Linux, Oracle Linux, FreeBSD, and others, which create realistic conditions for practical training.</t>
-  </si>
-  <si>
-    <t>Malware Classification using a Hybrid Hidden Markov Model-Convolutional Neural Network</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The proliferation of malware variants poses a significant challenges to traditional malware detection approaches, such as signature-based methods, necessitating the development of advanced machine learning techniques. In this research, we present a novel approach based on a hybrid architecture combining features extracted using a Hidden Markov Model (HMM), with a Convolutional Neural Network (CNN) then used for malware classification. Inspired by the strong results in previous work using an HMM-Random Forest model, we propose integrating HMMs, which serve to capture sequential patterns in opcode sequences, with CNNs, which are adept at extracting hierarchical features. We demonstrate the effectiveness of our approach on the popular Malicia dataset, and we obtain superior performance, as compared to other machine learning methods -- our results surpass the aforementioned HMM-Random Forest model. Our findings underscore the potential of hybrid HMM-CNN architectures in bolstering malware classification capabilities, offering several promising avenues for further research in the field of cybersecurity. </t>
-  </si>
-  <si>
-    <t>A Review of the Duality of Adversarial Learning in Network Intrusion: Attacks and Countermeasures</t>
-  </si>
-  <si>
-    <t>Deep learning solutions are instrumental in cybersecurity, harnessing their ability to analyze vast datasets, identify complex patterns, and detect anomalies. However, malevolent actors can exploit these capabilities to orchestrate sophisticated attacks, posing significant challenges to defenders and traditional security measures. Adversarial attacks, particularly those targeting vulnerabilities in deep learning models, present a nuanced and substantial threat to cybersecurity. Our study delves into adversarial learning threats such as Data Poisoning, Test Time Evasion, and Reverse Engineering, specifically impacting Network Intrusion Detection Systems. Our research explores the intricacies and countermeasures of attacks to deepen understanding of network security challenges amidst adversarial threats. In our study, we present insights into the dynamic realm of adversarial learning and its implications for network intrusion. The intersection of adversarial attacks and defenses within network traffic data, coupled with advances in machine learning and deep learning techniques, represents a relatively underexplored domain. Our research lays the groundwork for strengthening defense mechanisms to address the potential breaches in network security and privacy posed by adversarial attacks. Through our in-depth analysis, we identify domain-specific research gaps, such as the scarcity of real-life attack data and the evaluation of AI-based solutions for network traffic. Our focus on these challenges aims to stimulate future research efforts toward the development of resilient network defense strategies.</t>
-  </si>
-  <si>
-    <t>BotSim: LLM-Powered Malicious Social Botnet Simulation</t>
-  </si>
-  <si>
-    <t>Social media platforms like X(Twitter) and Reddit are vital to global communication. However, advancements in Large Language Model (LLM) technology give rise to social media bots with unprecedented intelligence. These bots adeptly simulate human profiles, conversations, and interactions, disseminating large amounts of false information and posing significant challenges to platform regulation. To better understand and counter these threats, we innovatively design BotSim, a malicious social botnet simulation powered by LLM. BotSim mimics the information dissemination patterns of real-world social networks, creating a virtual environment composed of intelligent agent bots and real human users. In the temporal simulation constructed by BotSim, these advanced agent bots autonomously engage in social interactions such as posting and commenting, effectively modeling scenarios of information flow and user interaction. Building on the BotSim framework, we construct a highly human-like, LLM-driven bot dataset called BotSim-24 and benchmark multiple bot detection strategies against it. The experimental results indicate that detection methods effective on traditional bot datasets perform worse on BotSim-24, highlighting the urgent need for new detection strategies to address the cybersecurity threats posed by these advanced bots.</t>
-  </si>
-  <si>
-    <t>Quantum community detection via deterministic elimination</t>
-  </si>
-  <si>
-    <t>We propose a quantum algorithm for calculating the structural properties of complex networks and graphs. The corresponding protocol -- deteQt -- is designed to perform large-scale community and botnet detection, where a specific subgraph of a larger graph is identified based on its properties. We construct a workflow relying on ground state preparation of the network modularity matrix or graph Laplacian. The corresponding maximum modularity vector is encoded into a -qubit register that contains community information. We develop a strategy for ``signing'' this vector via quantum signal processing, such that it closely resembles a hypergraph state, and project it onto a suitable linear combination of such states to detect botnets. As part of the workflow, and of potential independent interest, we present a readout technique that allows filtering out the incorrect solutions deterministically. This can reduce the scaling for the number of samples from exponential to polynomial. The approach serves as a building block for graph analysis with quantum speed up and enables the cybersecurity of large-scale networks</t>
-  </si>
-  <si>
-    <t>Automated Penetration Testing: Formalization and Realization</t>
-  </si>
-  <si>
-    <t>Recent changes in standards and regulations, driven by the increasing importance of software systems in meeting societal needs, mandate increased security testing of software systems. Penetration testing has been shown to be a reliable method to asses software system security. However, manual penetration testing is labor-intensive and requires highly skilled practitioners. Given the shortage of cybersecurity experts and current societal needs, increasing the degree of automation involved in penetration testing can aid in fulfilling the demands for increased security testing. In this work, we formally express the penetration testing problem at the architectural level and suggest a general self-organizing architecture that can be instantiated to automate penetration testing of real systems. We further describe and implement a specialization of the architecture in the ADAPT tool, targeting systems composed of hosts and services. We evaluate and demonstrate the feasibility of ADAPT by automatically performing penetration tests with success against: Metasploitable2, Metasploitable3, and a realistic virtual network used as a lab environment for penetration tester training</t>
-  </si>
-  <si>
-    <t>A technical solution for the rule of law, peace, security, and evolvability of global cyberspace -- solve the three genetic defects of IP network</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Since its inception in the 1960s, the internet has profoundly transformed human life. However, its original design now struggles to meet the evolving demands of modern society. Three primary defects have emerged: First, the concentration of power among a few dominant entities has intensified international conflicts and widened the technological divide. Second, the Internet Protocol (IP)-based system lacks inherent security, leading to frequent global cybersecurity incidents. Third, the rigidity of the IP protocol has hindered the sustainable development of cyberspace, as it resists necessary adaptations and innovations. Addressing these issues is crucial for the future resilience and security of the global digital landscape. To address these challenges, we propose the Co-governed Multi-Identifier Network (CoG-MIN briefly as MIN), a novel network architecture that leverages blockchain technology to ensure equal participation of countries worldwide in cyberspace governance and the rule of law. As a next-generation network system, CoG-MIN integrates mechanisms such as user authentication, data signatures, and encryption to significantly enhance network security. In testing environments, CoG-MIN has consistently withstood extensive attacks during various international cybersecurity competitions. Additionally, CoG-MIN supports the evolution and interoperability of different identifier systems, remains IP-compatible, and facilitates a gradual transition away from IP, providing an adaptable ecosystem for diverse network architectures. This adaptability fosters the development and evolution of diverse network architectures within CoG-MIN, making it a natural progression for the internet's future development. We further introduce a trilogy of cyberspace security theorems... (Due to character limitations, the full abstract is available in the paper PDF.) </t>
-  </si>
-  <si>
-    <t>Enhancing Cybersecurity in IoT Networks: A Deep Learning Approach to Anomaly Detection</t>
-  </si>
-  <si>
-    <t>With the proliferation of the Internet and smart devices, IoT technology has seen significant advancements and has become an integral component of smart homes, urban security, smart logistics, and other sectors. IoT facilitates real-time monitoring of critical production indicators, enabling businesses to detect potential quality issues, anticipate equipment malfunctions, and refine processes, thereby minimizing losses and reducing costs. Furthermore, IoT enhances real-time asset tracking, optimizing asset utilization and management. However, the expansion of IoT has also led to a rise in cybercrimes, with devices increasingly serving as vectors for malicious attacks. As the number of IoT devices grows, there is an urgent need for robust network security measures to counter these escalating threats. This paper introduces a deep learning model incorporating LSTM and attention mechanisms, a pivotal strategy in combating cybercrime in IoT networks. Our experiments, conducted on datasets including IoT-23, BoT-IoT, IoT network intrusion, MQTT, and MQTTset, demonstrate that our proposed method outperforms existing baselines.</t>
-  </si>
-  <si>
-    <t>Digital Transformation in the Water Distribution System based on the Digital Twins Concept</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Digital Twins have emerged as a disruptive technology with great potential; they can enhance WDS by offering real-time monitoring, predictive maintenance, and optimization capabilities. This paper describes the development of a state-of-the-art DT platform for WDS, introducing advanced technologies such as the Internet of Things, Artificial Intelligence, and Machine Learning models. This paper provides insight into the architecture of the proposed platform-CAUCCES-that, informed by both historical and meteorological data, effectively deploys AI/ML models like LSTM networks, Prophet, LightGBM, and XGBoost in trying to predict water consumption patterns. Furthermore, we delve into how optimization in the maintenance of WDS can be achieved by formulating a Constraint Programming problem for scheduling, hence minimizing the operational cost efficiently with reduced environmental impacts. It also focuses on cybersecurity and protection to ensure the integrity and reliability of the DT platform. In this view, the system will contribute to improvements in decision-making capabilities, operational efficiency, and system reliability, with reassurance being drawn from the important role it can play toward sustainable management of water resources.</t>
-  </si>
-  <si>
-    <t>siForest: Detecting Network Anomalies with Set-Structured Isolation Forest</t>
-  </si>
-  <si>
-    <t>As cyber threats continue to evolve in sophistication and scale, the ability to detect anomalous network behavior has become critical for maintaining robust cybersecurity defenses. Modern cybersecurity systems face the overwhelming challenge of analyzing billions of daily network interactions to identify potential threats, making efficient and accurate anomaly detection algorithms crucial for network defense. This paper investigates the use of variations of the Isolation Forest (iForest) machine learning algorithm for detecting anomalies in internet scan data. In particular, it presents the Set-Partitioned Isolation Forest (siForest), a novel extension of the iForest method designed to detect anomalies in set-structured data. By treating instances such as sets of multiple network scans with the same IP address as cohesive units, siForest effectively addresses some challenges of analyzing complex, multidimensional datasets. Extensive experiments on synthetic datasets simulating diverse anomaly scenarios in network traffic demonstrate that siForest has the potential to outperform traditional approaches on some types of internet scan data.</t>
-  </si>
-  <si>
-    <t>PBP: Post-training Backdoor Purification for Malware Classifiers</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> In recent years, the rise of machine learning (ML) in cybersecurity has brought new challenges, including the increasing threat of backdoor poisoning attacks on ML malware classifiers. For instance, adversaries could inject malicious samples into public malware repositories, contaminating the training data and potentially misclassifying malware by the ML model. Current countermeasures predominantly focus on detecting poisoned samples by leveraging disagreements within the outputs of a diverse set of ensemble models on training data points. However, these methods are not suitable for scenarios where Machine Learning-as-a-Service (MLaaS) is used or when users aim to remove backdoors from a model after it has been trained. Addressing this scenario, we introduce PBP, a post-training defense for malware classifiers that mitigates various types of backdoor embeddings without assuming any specific backdoor embedding mechanism. Our method exploits the influence of backdoor attacks on the activation distribution of neural networks, independent of the trigger-embedding method. In the presence of a backdoor attack, the activation distribution of each layer is distorted into a mixture of distributions. By regulating the statistics of the batch normalization layers, we can guide a backdoored model to perform similarly to a clean one. Our method demonstrates substantial advantages over several state-of-the-art methods, as evidenced by experiments on two datasets, two types of backdoor methods, and various attack configurations. Notably, our approach requires only a small portion of the training data -- only 1\% -- to purify the backdoor and reduce the attack success rate from 100\% to almost 0\%, a 100-fold improvement over the baseline methods. Our code is available at \url{https://github.com/judydnguyen/pbp-backdoor-purification-official}.</t>
-  </si>
-  <si>
-    <t>warm Intelligence-Driven Client Selection for Federated Learning in Cybersecurity applications</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> This study addresses a critical gap in the literature regarding the use of Swarm Intelligence Optimization (SI) algorithms for client selection in Federated Learning (FL), with a focus on cybersecurity applications. Existing research primarily explores optimization techniques for centralized machine learning, leaving the unique challenges of client diveristy, non-IID data distributions, and adversarial noise in decentralized FL largely unexamined. To bridge this gap, we evaluate nine SI algorithms-Grey Wolf Optimization (GWO), Particle Swarm Optimization (PSO), Cuckoo Search, Bat Algorithm, Bee Colony, Ant Colony Optimization, Fish Swarm, Glow Worm, and Intelligent Water Droplet-across four experimental scenarios: fixed client participation, dynamic participation patterns, hetergeneous non-IID data distributions, and adversarial noise conditions. Results indicate that GWO exhibits superior adaptability and robustness, achieving the highest accuracy, recall and F1-scoress across all configurations, while PSO and Cuckoo Search also demonstrate strong performance. These findings underscore the potential of SI algorithms to address decentralized and adversarial FL challenges, offereing scalable and resilient solutions for cybersecurity applications, including intrusion detection in IoT and large-scale networks. </t>
-  </si>
-  <si>
-    <t>Combining Threat Intelligence with IoT Scanning to Predict Cyber Attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> While the Web has become a global platform for communication, malicious actors, including hackers and hacktivist groups, often disseminate ideological content and coordinate activities through the "Dark Web", an obscure counterpart of the conventional web. Presently, challenges such as information overload and the fragmented nature of cyber threat data impede comprehensive profiling of these actors, thereby limiting the efficacy of predictive analyses of their online activities. Concurrently, the proliferation of internet-connected devices has surpassed the global human population, with this disparity projected to widen as the Internet of Things (IoT) expands. Technical communities are actively advancing IoT-related research to address its growing societal integration. This paper proposes a novel predictive threat intelligence framework designed to systematically collect, analyze, and visualize Dark Web data to identify malicious websites and correlate this information with potential IoT vulnerabilities. The methodology integrates automated data harvesting, analytical techniques, and visual mapping tools, while also examining vulnerabilities in IoT devices to assess exploitability. By bridging gaps in cybersecurity research, this study aims to enhance predictive threat modeling and inform policy development, thereby contributing to intelligence research initiatives focused on mitigating cyber risks in an increasingly interconnected digital ecosystem.</t>
-  </si>
-  <si>
-    <t>A Lightweight Edge-CNN-Transformer Model for Detecting Coordinated Cyber and Digital Twin Attacks in Cooperative Smart Farming</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The agriculture sector is increasingly adopting innovative technologies to meet the growing food demands of the global population. To optimize resource utilization and minimize crop losses, farmers are joining cooperatives to share their data and resources among member farms. However, while farmers benefit from this data sharing and interconnection, it exposes them to cybersecurity threats and privacy concerns. A cyberattack on one farm can have widespread consequences, affecting the targeted farm as well as all member farms within a cooperative. In this research, we address existing gaps by proposing a novel and secure architecture for Cooperative Smart Farming (CSF). First, we highlight the role of edge-based DTs in enhancing the efficiency and resilience of agricultural operations. To validate this, we develop a test environment for CSF, implementing various cyberattacks on both the DTs and their physical counterparts using different attack vectors. We collect two smart farming network datasets to identify potential threats. After identifying these threats, we focus on preventing the transmission of malicious data from compromised farms to the central cloud server. To achieve this, we propose a CNN-Transformer-based network anomaly detection model, specifically designed for deployment at the edge. As a proof of concept, we implement this model and evaluate its performance by varying the number of encoder layers. Additionally, we apply Post-Quantization to compress the model and demonstrate the impact of compression on its performance in edge environments. Finally, we compare the model's performance with traditional machine learning approaches to assess its overall effectiveness. </t>
-  </si>
-  <si>
-    <t>Robust Defense Against Extreme Grid Events Using Dual-Policy Reinforcement Learning Agents</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Reinforcement learning (RL) agents are powerful tools for managing power grids. They use large amounts of data to inform their actions and receive rewards or penalties as feedback to learn favorable responses for the system. Once trained, these agents can efficiently make decisions that would be too computationally complex for a human operator. This ability is especially valuable in decarbonizing power networks, where the demand for RL agents is increasing. These agents are well suited to control grid actions since the action space is constantly growing due to uncertainties in renewable generation, microgrid integration, and cybersecurity threats. To assess the efficacy of RL agents in response to an adverse grid event, we use the Grid2Op platform for agent training. We employ a proximal policy optimization (PPO) algorithm in conjunction with graph neural networks (GNNs). By simulating agents' responses to grid events, we assess their performance in avoiding grid failure for as long as possible. The performance of an agent is expressed concisely through its reward function, which helps the agent learn the most optimal ways to reconfigure a grid's topology amidst certain events. To model multi-actor scenarios that threaten modern power networks, particularly those resulting from cyberattacks, we integrate an opponent that acts iteratively against a given agent. This interplay between the RL agent and opponent is utilized in N-k contingency screening, providing a novel alternative to the traditional security assessment</t>
-  </si>
-  <si>
-    <t>SDN-Based Smart Cyber Switching (SCS) for Cyber Restoration of a Digital Substation</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> In recent years, critical infrastructure and power grids have increasingly been targets of cyber-attacks, causing widespread and extended blackouts. Digital substations are particularly vulnerable to such cyber incursions, jeopardizing grid stability. This paper addresses these risks by proposing a cybersecurity framework that leverages software-defined networking (SDN) to bolster the resilience of substations based on the IEC-61850 standard. The research introduces a strategy involving smart cyber switching (SCS) for mitigation and concurrent intelligent electronic device (CIED) for restoration, ensuring ongoing operational integrity and cybersecurity within a substation. The SCS framework improves the physical network's behavior (i.e., leveraging commercial SDN capabilities) by incorporating an adaptive port controller (APC) module for dynamic port management and an intrusion detection system (IDS) to detect and counteract malicious IEC-61850-based sampled value (SV) and generic object-oriented system event (GOOSE) messages within the substation's communication network. The framework's effectiveness is validated through comprehensive simulations and a hardware-in-the-loop (HIL) testbed, demonstrating its ability to sustain substation operations during cyber-attacks and significantly improve the overall resilience of the power grid.</t>
-  </si>
-  <si>
-    <t>Towards Characterizing Cyber Networks with Large Language Models</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Threat hunting analyzes large, noisy, high-dimensional data to find sparse adversarial behavior. We believe adversarial activities, however they are disguised, are extremely difficult to completely obscure in high dimensional space. In this paper, we employ these latent features of cyber data to find anomalies via a prototype tool called Cyber Log Embeddings Model (CLEM). CLEM was trained on Zeek network traffic logs from both a real-world production network and an from Internet of Things (IoT) cybersecurity testbed. The model is deliberately overtrained on a sliding window of data to characterize each window closely. We use the Adjusted Rand Index (ARI) to comparing the k-means clustering of CLEM output to expert labeling of the embeddings. Our approach demonstrates that there is promise in using natural language modeling to understand cyber data. </t>
-  </si>
-  <si>
-    <t>Cybercrime Prediction via Geographically Weighted Learning</t>
-  </si>
-  <si>
-    <t>Inspired by the success of Geographically Weighted Regression and its accounting for spatial variations, we propose GeogGNN -- A graph neural network model that accounts for geographical latitude and longitudinal points. Using a synthetically generated dataset, we apply the algorithm for a 4-class classification problem in cybersecurity with seemingly realistic geographic coordinates centered in the Gulf Cooperation Council region. We demonstrate that it has higher accuracy than standard neural networks and convolutional neural networks that treat the coordinates as features. Encouraged by the speed-up in model accuracy by the GeogGNN model, we provide a general mathematical result that demonstrates that a geometrically weighted neural network will, in principle, always display higher accuracy in the classification of spatially dependent data by making use of spatial continuity and local averaging features.</t>
-  </si>
-  <si>
-    <t>Tactical Edge IoT in Defense and National Security</t>
-  </si>
-  <si>
-    <t>The deployment of Internet of Things (IoT) systems in Defense and National Security faces some limitations that can be addressed with Edge Computing approaches. The Edge Computing and IoT paradigms combined bring potential benefits, since they confront the limitations of traditional centralized cloud computing approaches, which enable easy scalability, real-time applications or mobility support, but whose use poses certain risks in aspects like cybersecurity. This chapter identifies scenarios in which Defense and National Security can leverage Commercial Off-The-Shelf (COTS) Edge IoT capabilities to deliver greater survivability to warfighters or first responders, while lowering costs and increasing operational efficiency and effectiveness. In addition, it presents the general design of a Tactical Edge IoT communications architecture, it identifies the open challenges for a widespread adoption and provides research guidelines and some recommendations for enabling cost-effective Edge IoT for Defense and National Security.</t>
-  </si>
-  <si>
-    <t>Computer Application Research based on Chinese Human Resources and Network Information Security Technology Management and Analysis In Chinese Universities</t>
-  </si>
-  <si>
-    <t>This study investigates the current state of computer network security and human resource management within Chinese universities, emphasizing the growing importance of safeguarding digital infrastructures. To support the analysis, interviews were conducted with managers from two leading Chinese cybersecurity firms and the qualitative data obtained was carefully analyzed to extract key insights and conclusions</t>
-  </si>
-  <si>
-    <t>ADAPT: A Game-Theoretic and Neuro-Symbolic Framework for Automated Distributed Adaptive Penetration Testing</t>
-  </si>
-  <si>
-    <t>The integration of AI into modern critical infrastructure systems, such as healthcare, has introduced new vulnerabilities that can significantly impact workflow, efficiency, and safety. Additionally, the increased connectivity has made traditional human-driven penetration testing insufficient for assessing risks and developing remediation strategies. Consequently, there is a pressing need for a distributed, adaptive, and efficient automated penetration testing framework that not only identifies vulnerabilities but also provides countermeasures to enhance security posture. This work presents ADAPT, a game-theoretic and neuro-symbolic framework for automated distributed adaptive penetration testing, specifically designed to address the unique cybersecurity challenges of AI-enabled healthcare infrastructure networks. We use a healthcare system case study to illustrate the methodologies within ADAPT. The proposed solution enables a learning-based risk assessment. Numerical experiments are used to demonstrate effective countermeasures against various tactical techniques employed by adversarial AI.</t>
-  </si>
-  <si>
-    <t>Securing Healthcare with Deep Learning: A CNN-Based Model for medical IoT Threat Detection</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The increasing integration of the Internet of Medical Things (IoMT) into healthcare systems has significantly enhanced patient care but has also introduced critical cybersecurity challenges. This paper presents a novel approach based on Convolutional Neural Networks (CNNs) for detecting cyberattacks within IoMT environments. Unlike previous studies that predominantly utilized traditional machine learning (ML) models or simpler Deep Neural Networks (DNNs), the proposed model leverages the capabilities of CNNs to effectively analyze the temporal characteristics of network traffic data. Trained and evaluated on the CICIoMT2024 dataset, which comprises 18 distinct types of cyberattacks across a range of IoMT devices, the proposed CNN model demonstrates superior performance compared to previous state-of-the-art methods, achieving a perfect accuracy of 99% in binary, categorical, and multiclass classification tasks. This performance surpasses that of conventional ML models such as Logistic Regression, AdaBoost, DNNs, and Random Forests. These findings highlight the potential of CNNs to substantially improve IoMT cybersecurity, thereby ensuring the protection and integrity of connected healthcare systems.</t>
-  </si>
-  <si>
-    <t>Resilient-By-Design: A Resiliency Framework for Future Wireless Networks</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Our future society will be increasingly digitalised, hyper-connected and globally data driven. The sixth generation (6G) and beyond 6G wireless networks are expected to bridge the digital and physical worlds by providing wireless connectivity as a service to different vertical sectors, including industries, smart cities, eHealth and autonomous transportation. Such far reaching integration will render the society increasingly reliant on wireless networks. While this has the potential to greatly enhance our quality and ease of life, any disruption to these networks would also have significant impact with overreaching consequences. Disruptions can happen due to a variety of reasons, including planned outages, failures due to the nature of wireless propagation, natural disasters, and deliberate cybersecurity attacks. Hence, 6G and beyond 6G networks should not only provide near instant and virtually unlimited connectivity, but also be resilient against internal and external disruptions. This paper proposes a resilient-by-design framework towards this end. First, we provide an overview of the disruption landscape. Thereafter, we comprehensively outline the main features of the proposed concept. Finally, we detail the four key steps of the framework, namely predict, preempt, protect and progress. A simple but illustrative preliminary simulation result is also presented to highlight the potential advantages and efficiency of the proposed approach in addressing outages. </t>
-  </si>
-  <si>
-    <t>Survey of Load-Altering Attacks Against Power Grids: Attack Impact, Detection and Mitigation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">The growing penetration of IoT devices in power grids despite its benefits, raises cybersecurity concerns. In particular, load-altering attacks (LAAs) targeting high-wattage IoT-controllable load devices pose serious risks to grid stability and disrupt electricity markets. This paper provides a comprehensive review of LAAs, highlighting the threat model, analyzing their impact on transmission and distribution networks, and the electricity market dynamics. We also review the detection and localization schemes for LAAs that employ either model-based or data-driven approaches, with some hybrid methods combining the strengths of both. Additionally, mitigation techniques are examined, focusing on both preventive measures, designed to thwart attack execution, and reactive methods, which aim to optimize responses to ongoing attacks. We look into the application of each study and highlight potential streams for future research. </t>
-  </si>
-  <si>
-    <t>Countering Autonomous Cyber Threats</t>
+    <r>
+      <t>Huichun Li</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF1F1F1F"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t>Chengli Zhao</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2649,181 +2757,67 @@
     <r>
       <rPr>
         <b/>
-        <sz val="8"/>
+        <sz val="11"/>
         <color rgb="FF287916"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
       <t>network</t>
     </r>
     <r>
       <rPr>
-        <sz val="8"/>
+        <sz val="11"/>
         <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
       <t> defenses or potential countermeasures unexplored. Critically, understanding the aptitude of downloadable models to function as offensive cyber agents is vital given that they are far more difficult to govern and prevent their misuse. As such, this work evaluates several state-of-the-art FMs on their ability to compromise machines in an isolated </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="8"/>
+        <sz val="11"/>
         <color rgb="FF287916"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
       <t>network</t>
     </r>
     <r>
       <rPr>
-        <sz val="8"/>
+        <sz val="11"/>
         <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
       <t> and investigates defensive mechanisms to defeat such AI-powered attacks. Using target machines from a commercial provider, the most recently released downloadable models are found to be on par with a leading proprietary model at conducting simple cyber attacks with common hacking tools against known vulnerabilities. To mitigate such LLM-powered threats, defensive prompt injection (DPI) payloads for disrupting the malicious cyber agent's workflow are demonstrated to be effective. From these results, the implications for AI safety and governance with respect to </t>
     </r>
     <r>
       <rPr>
         <b/>
-        <sz val="8"/>
+        <sz val="11"/>
         <color rgb="FF287916"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
       <t>cybersecurity</t>
     </r>
     <r>
       <rPr>
-        <sz val="8"/>
+        <sz val="11"/>
         <color rgb="FF333333"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
       </rPr>
       <t> is analyzed.</t>
     </r>
-  </si>
-  <si>
-    <t>Enhancing Enterprise Security with Zero Trust Architecture</t>
-  </si>
-  <si>
-    <t>Zero Trust Architecture (ZTA) represents a transformative approach to modern cybersecurity, directly addressing the shortcomings of traditional perimeter-based security models. With the rise of cloud computing, remote work, and increasingly sophisticated cyber threats, perimeter defenses have proven ineffective at mitigating risks, particularly those involving insider threats and lateral movement within networks. ZTA shifts the security paradigm by assuming that no user, device, or system can be trusted by default, requiring continuous verification and the enforcement of least privilege access for all entities. This paper explores the key components of ZTA, such as identity and access management (IAM), micro-segmentation, continuous monitoring, and behavioral analytics, and evaluates their effectiveness in reducing vulnerabilities across diverse sectors, including finance, healthcare, and technology. Through case studies and industry reports, the advantages of ZTA in mitigating insider threats and minimizing attack surfaces are discussed. Additionally, the paper addresses the challenges faced during ZTA implementation, such as scalability, integration complexity, and costs, while providing best practices for overcoming these obstacles. Lastly, future research directions focusing on emerging technologies like AI, machine learning, blockchain, and their integration into ZTA are examined to enhance its capabilities further.</t>
-  </si>
-  <si>
-    <t>Hierarchical Multi-agent Reinforcement Learning for Cyber Network Defense</t>
-  </si>
-  <si>
-    <t>Recent advances in multi-agent reinforcement learning (MARL) have created opportunities to solve complex real-world tasks. Cybersecurity is a notable application area, where defending networks against sophisticated adversaries remains a challenging task typically performed by teams of security operators. In this work, we explore novel MARL strategies for building autonomous cyber network defenses that address challenges such as large policy spaces, partial observability, and stealthy, deceptive adversarial strategies. To facilitate efficient and generalized learning, we propose a hierarchical Proximal Policy Optimization (PPO) architecture that decomposes the cyber defense task into specific sub-tasks like network investigation and host recovery. Our approach involves training sub-policies for each sub-task using PPO enhanced with domain expertise. These sub-policies are then leveraged by a master defense policy that coordinates their selection to solve complex network defense tasks. Furthermore, the sub-policies can be fine-tuned and transferred with minimal cost to defend against shifts in adversarial behavior or changes in network settings. We conduct extensive experiments using CybORG Cage 4, the state-of-the-art MARL environment for cyber defense. Comparisons with multiple baselines across different adversaries show that our hierarchical learning approach achieves top performance in terms of convergence speed, episodic return, and several interpretable metrics relevant to cybersecurity, including the fraction of clean machines on the network, precision, and false positives on recoveries.</t>
-  </si>
-  <si>
-    <t>Synthetic Network Traffic Data Generation: A Comparative Study</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The generation of synthetic network traffic data is essential for network security testing, machine learning model training, and performance analysis. However, existing methods for synthetic data generation differ significantly in their ability to maintain statistical fidelity, utility for classification tasks, and class balance. This study presents a comparative analysis of twelve synthetic network traffic data generation methods, encompassing non-AI (statistical), classical AI, and generative AI techniques. Using NSL-KDD and CIC-IDS2017 datasets, we evaluate the fidelity, utility, class balance, and scalability of these methods under standardized performance metrics. Results demonstrate that GAN-based models, particularly CTGAN and CopulaGAN, achieve superior fidelity and utility, making them ideal for high-quality synthetic data generation. Statistical methods such as SMOTE and Cluster Centroid effectively maintain class balance but fail to capture complex traffic structures. Meanwhile, diffusion models exhibit computational inefficiencies, limiting their scalability. Our findings provide a structured benchmarking framework for selecting the most suitable synthetic data generation techniques for network traffic analysis and cybersecurity applications.</t>
-  </si>
-  <si>
-    <t>Towards more realistic co-simulation of cyber-physical energy distribution systems</t>
-  </si>
-  <si>
-    <t>The increased integration of information and communications technology at the distribution grid level offers broader opportunities for active operational management concepts. At the same time, requirements for resilience against internal and external threats to the power supply, such as outages or cyberattacks, are increasing. The emerging threat landscape needs to be investigated to ensure the security of supply of future distribution grids. This extended abstract presents a co-simulation environment to study communication infrastructures for the resilient operation of distribution grids. For this purpose, a communication network emulation and a power grid simulation are combined in a common modular environment. This will provide the basis for cybersecurity investigations and testing of new active operation management concepts for smart grids. Exemplary laboratory tests and attack replications will be used to demonstrate the diverse use cases of our co-simulation approach.</t>
-  </si>
-  <si>
-    <t>Cyber Threats to Canadian Federal Election: Emerging Threats, Assessment, and Mitigation Strategies</t>
-  </si>
-  <si>
-    <t>As Canada prepares for the 2025 federal election, ensuring the integrity and security of the electoral process against cyber threats is crucial. Recent foreign interference in elections globally highlight the increasing sophistication of adversaries in exploiting technical and human vulnerabilities. Such vulnerabilities also exist in Canada's electoral system that relies on a complex network of IT systems, vendors, and personnel. To mitigate these vulnerabilities, a threat assessment is crucial to identify emerging threats, develop incident response capabilities, and build public trust and resilience against cyber threats. Therefore, this paper presents a comprehensive national cyber threat assessment, following the NIST Special Publication 800-30 framework, focusing on identifying and mitigating cybersecurity risks to the upcoming 2025 Canadian federal election. The research identifies three major threats: misinformation, disinformation, and malinformation (MDM) campaigns; attacks on critical infrastructure and election support systems; and espionage by malicious actors. Through detailed analysis, the assessment offers insights into the capabilities, intent, and potential impact of these threats. The paper also discusses emerging technologies and their influence on election security and proposes a multi-faceted approach to risk mitigation ahead of the election.</t>
-  </si>
-  <si>
-    <t>Towards the generation of hierarchical attack models from cybersecurity vulnerabilities using language models</t>
-  </si>
-  <si>
-    <t xml:space="preserve">This paper investigates the use of a pre-trained language model and siamese network to discern sibling relationships between text-based cybersecurity vulnerability data. The ultimate purpose of the approach presented in this paper is towards the construction of hierarchical attack models based on a set of text descriptions characterising potential/observed vulnerabilities in a given system. Due to the nature of the data, and the uncertainty sensitive environment in which the problem is presented, a practically oriented soft computing approach is necessary. Therefore, a key focus of this work is to investigate practical questions surrounding the reliability of predicted links towards the construction of such models, to which end conceptual and practical challenges and solutions associated with the proposed approach are outlined, such as dataset complexity and stability of predictions. Accordingly, the contributions of this paper focus on producing neural networks using a pre-trained language model for predicting sibling relationships between cybersecurity vulnerabilities, then outlining how to apply this capability towards the generation of hierarchical attack models. In addition, two data sampling mechanisms for tackling data complexity, and a consensus mechanism for reducing the amount of false positive predictions are outlined. Each of these approaches is compared and contrasted using empirical results from three sets of cybersecurity data to determine their effectiveness. </t>
-  </si>
-  <si>
-    <t>Towards a Self-rescuing System for UAVs Under GNSS Attack</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> There has been substantial growth in the UAV market along with an expansion in their applications. However, the successful execution of a UAV mission is very often dependent on the use of a GNSS. Unfortunately, the vulnerability of GNSS signals, due to their lack of encryption and authentication, poses a significant cybersecurity issue. This vulnerability makes various attacks, particularly the "GNSS spoofing attack," and "GNSS jamming attack" easily executable. Generally speaking, during this attack, the drone is manipulated into altering its path, usually resulting in an immediate forced landing or crash. As far as we know, we are the first to propose a lightweight-solution that enable a drone to autonomously rescue itself, assuming it is under GNSS attack and the GNSS is no longer available, and return safely to its initial takeoff position, thereby preventing any potential crashes. During the flight, wind plays a critical role as it can instantaneously alter the drone's position. To solve this problem, we have devised a highly effective 2-phases solution: (i) Forward Phase, for monitoring and recording the forward journey, and (ii) Backward Phase, that generates a backward route, based on the Forward Phase and wind presence. The final solution ensures strong performance in consistently returning the drone to the original position, even in wind situations, while maintaining a very fast computation time.</t>
-  </si>
-  <si>
-    <t>Adversarial Challenges in Network Intrusion Detection Systems: Research Insights and Future Prospects</t>
-  </si>
-  <si>
-    <t>Machine learning has brought significant advances in cybersecurity, particularly in the development of Intrusion Detection Systems (IDS). These improvements are mainly attributed to the ability of machine learning algorithms to identify complex relationships between features and effectively generalize to unseen data. Deep neural networks, in particular, contributed to this progress by enabling the analysis of large amounts of training data, significantly enhancing detection performance. However, machine learning models remain vulnerable to adversarial attacks, where carefully crafted input data can mislead the model into making incorrect predictions. While adversarial threats in unstructured data, such as images and text, have been extensively studied, their impact on structured data like network traffic is less explored. This survey aims to address this gap by providing a comprehensive review of machine learning-based Network Intrusion Detection Systems (NIDS) and thoroughly analyzing their susceptibility to adversarial attacks. We critically examine existing research in NIDS, highlighting key trends, strengths, and limitations, while identifying areas that require further exploration. Additionally, we discuss emerging challenges in the field and offer insights for the development of more robust and resilient NIDS. In summary, this paper enhances the understanding of adversarial attacks and defenses in NIDS and guide future research in improving the robustness of machine learning models in cybersecurity applications.</t>
-  </si>
-  <si>
-    <t>Comparing Unidirectional, Bidirectional, and Word2vec Models for Discovering Vulnerabilities in Compiled Lifted Code</t>
-  </si>
-  <si>
-    <t>Ransomware and other forms of malware cause significant financial and operational damage to organizations by exploiting long-standing and often difficult-to-detect software vulnerabilities. To detect vulnerabilities such as buffer overflows in compiled code, this research investigates the application of unidirectional transformer-based embeddings, specifically GPT-2. Using a dataset of LLVM functions, we trained a GPT-2 model to generate embeddings, which were subsequently used to build LSTM neural networks to differentiate between vulnerable and non-vulnerable code. Our study reveals that embeddings from the GPT-2 model significantly outperform those from bidirectional models of BERT and RoBERTa, achieving an accuracy of 92.5% and an F1-score of 89.7%. LSTM neural networks were developed with both frozen and unfrozen embedding model layers. The model with the highest performance was achieved when the embedding layers were unfrozen. Further, the research finds that, in exploring the impact of different optimizers within this domain, the SGD optimizer demonstrates superior performance over Adam. Overall, these findings reveal important insights into the potential of unidirectional transformer-based approaches in enhancing cybersecurity defenses.</t>
-  </si>
-  <si>
-    <t>GISExplainer: On Explainability of Graph Neural Networks via Game-theoretic Interaction Subgraphs</t>
-  </si>
-  <si>
-    <t>Explainability is crucial for the application of black-box Graph Neural Networks (GNNs) in critical fields such as healthcare, finance, cybersecurity, and more. Various feature attribution methods, especially the perturbation-based methods, have been proposed to indicate how much each node/edge contributes to the model predictions. However, these methods fail to generate connected explanatory subgraphs that consider the causal interaction between edges within different coalition scales, which will result in unfaithful explanations. In our study, we propose GISExplainer, a novel game-theoretic interaction based explanation method that uncovers what the underlying GNNs have learned for node classification by discovering human-interpretable causal explanatory subgraphs. First, GISExplainer defines a causal attribution mechanism that considers the game-theoretic interaction of multi-granularity coalitions in candidate explanatory subgraph to quantify the causal effect of an edge on the prediction. Second, GISExplainer assumes that the coalitions with negative effects on the predictions are also significant for model interpretation, and the contribution of the computation graph stems from the combined influence of both positive and negative interactions within the coalitions. Then, GISExplainer regards the explanation task as a sequential decision process, in which a salient edges is successively selected and connected to the previously selected subgraph based on its causal effect to form an explanatory subgraph, ultimately striving for better explanations. Additionally, an efficiency optimization scheme is proposed for the causal attribution mechanism through coalition sampling. Extensive experiments demonstrate that GISExplainer achieves better performance than state-of-the-art approaches w.r.t. two quantitative metrics: Fidelity and Sparsity.</t>
-  </si>
-  <si>
-    <t>MEGA-PT: A Meta-Game Framework for Agile Penetration Testing</t>
-  </si>
-  <si>
-    <t>Penetration testing is an essential means of proactive defense in the face of escalating cybersecurity incidents. Traditional manual penetration testing methods are time-consuming, resource-intensive, and prone to human errors. Current trends in automated penetration testing are also impractical, facing significant challenges such as the curse of dimensionality, scalability issues, and lack of adaptability to network changes. To address these issues, we propose MEGA-PT, a meta-game penetration testing framework, featuring micro tactic games for node-level local interactions and a macro strategy process for network-wide attack chains. The micro- and macro-level modeling enables distributed, adaptive, collaborative, and fast penetration testing. MEGA-PT offers agile solutions for various security schemes, including optimal local penetration plans, purple teaming solutions, and risk assessment, providing fundamental principles to guide future automated penetration testing. Our experiments demonstrate the effectiveness and agility of our model by providing improved defense strategies and adaptability to changes at both local and network levels.</t>
-  </si>
-  <si>
-    <t>Cyber-Physical Authentication Scheme for Secure V2G Transactions</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The rapid adoption of electric vehicles (EVs) globally has catalyzed the need for robust cybersecurity measures within vehicle-to-grid (V2G) networks. As these networks are increasingly being integrated into smart charging infrastructures, they also introduce new vulnerabilities that threaten grid stability and user privacy This paper proposes a cyber-physical authentication protocol and trading smart contract tailored to plug and charge (PnC) operations within blockchain-based V2G systems. The protocol leverages advanced cryptographic techniques and blockchain to ensure secure, transparent, and tamper-proof energy transactions between EVs and charging stations. Key contributions include the development of a cyber-physical authentication method, the implementation of a smart contract framework for secure energy trading, and a detailed security and privacy analysis. The proposed protocol effectively mitigates risks such as man-in-the-middle (MitM) attacks and replay attacks while preserving user anonymity and data integrity</t>
-  </si>
-  <si>
-    <t>Maritime Cybersecurity: A Comprehensive Review</t>
-  </si>
-  <si>
-    <t>The maritime industry stands at a critical juncture, where the imperative for technological advancement intersects with the pressing need for robust cybersecurity measures. Maritime cybersecurity refers to the protection of computer systems and digital assests within the maritime industry, as well as the broader network of interconnected components that make up the maritime ecosystem. In this survey, we aim to identify the significant domains of maritime cybersecurity and measure their effectiveness. We have provided an in-depth analysis of threats in key maritime systems, including AIS, GNSS, ECDIS, VDR, RADAR, VSAT, and GMDSS, while exploring real-world cyber incidents that have impacted the sector. A multi-dimensional taxonomy of maritime cyber attacks is presented, offering insights into threat actors, motivations, and impacts. We have also evaluated various security solutions, from integrated solutions to component specific solutions. Finally, we have shared open challenges and future solutions. In the supplementary section, we have presented definitions and vulnerabilities of vessel components that have discussed in this survey. By addressing all these critical issues with key interconnected aspects, this review aims to foster a more resilient maritime ecosystem.</t>
-  </si>
-  <si>
-    <t>CyberNFTs: Conceptualizing a decentralized and reward-driven intrusion detection system with ML</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> The rapid evolution of the Internet, particularly the emergence of Web3, has transformed the ways people interact and share data. Web3, although still not well defined, is thought to be a return to the decentralization of corporations' power over user data. Despite the obsolescence of the idea of building systems to detect and prevent cyber intrusions, this is still a topic of interest. This paper proposes a novel conceptual approach for implementing decentralized collaborative intrusion detection networks (CIDN) through a proof-of-concept. The study employs an analytical and comparative methodology, examining the synergy between cutting-edge Web3 technologies and information security. The proposed model incorporates blockchain concepts, cyber non-fungible token (cyberNFT) rewards, machine learning algorithms, and publish/subscribe architectures. Finally, the paper discusses the strengths and limitations of the proposed system, offering insights into the potential of decentralized cybersecurity models. </t>
-  </si>
-  <si>
-    <t>Hackphyr: A Local Fine-Tuned LLM Agent for Network Security Environments</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> Large Language Models (LLMs) have shown remarkable potential across various domains, including cybersecurity. Using commercial cloud-based LLMs may be undesirable due to privacy concerns, costs, and network connectivity constraints. In this paper, we present Hackphyr, a locally fine-tuned LLM to be used as a red-team agent within network security environments. Our fine-tuned 7 billion parameter model can run on a single GPU card and achieves performance comparable with much larger and more powerful commercial models such as GPT-4. Hackphyr clearly outperforms other models, including GPT-3.5-turbo, and baselines, such as Q-learning agents in complex, previously unseen scenarios. To achieve this performance, we generated a new task-specific cybersecurity dataset to enhance the base model's capabilities. Finally, we conducted a comprehensive analysis of the agents' behaviors that provides insights into the planning abilities and potential shortcomings of such agents, contributing to the broader understanding of LLM-based agents in cybersecurity contexts </t>
-  </si>
-  <si>
-    <t>DrLLM: Prompt-Enhanced Distributed Denial-of-Service Resistance Method with Large Language Models</t>
-  </si>
-  <si>
-    <t>The increasing number of Distributed Denial of Service (DDoS) attacks poses a major threat to the Internet, highlighting the importance of DDoS mitigation. Most existing approaches require complex training methods to learn data features, which increases the complexity and generality of the application. In this paper, we propose DrLLM, which aims to mine anomalous traffic information in zero-shot scenarios through Large Language Models (LLMs). To bridge the gap between DrLLM and existing approaches, we embed the global and local information of the traffic data into the reasoning paradigm and design three modules, namely Knowledge Embedding, Token Embedding, and Progressive Role Reasoning, for data representation and reasoning. In addition we explore the generalization of prompt engineering in the cybersecurity domain to improve the classification capability of DrLLM. Our ablation experiments demonstrate the applicability of DrLLM in zero-shot scenarios and further demonstrate the potential of LLMs in the network domains. DrLLM implementation code has been open-sourced at https://github.com/liuup/DrLLM</t>
-  </si>
-  <si>
-    <t>LSTM Recurrent Neural Networks for Cybersecurity Named Entity Recognition</t>
-  </si>
-  <si>
-    <t>The automated and timely conversion of cybersecurity information from unstructured online sources, such as blogs and articles to more formal representations has become a necessity for many applications in the domain nowadays. Named Entity Recognition (NER) is one of the early phases towards this goal. It involves the detection of the relevant domain entities, such as product, version, attack name, etc. in technical documents. Although generally considered a simple task in the information extraction field, it is quite challenging in some domains like cybersecurity because of the complex structure of its entities. The state of the art methods require time-consuming and labor intensive feature engineering that describes the properties of the entities, their context, domain knowledge, and linguistic characteristics. The model demonstrated in this paper is domain independent and does not rely on any features specific to the entities in the cybersecurity domain, hence does not require expert knowledge to perform feature engineering. The method used relies on a type of recurrent neural networks called Long Short-Term Memory (LSTM) and the Conditional Random Fields (CRFs) method. The results we obtained showed that this method outperforms the state of the art methods given an annotated corpus of a decent size</t>
-  </si>
-  <si>
-    <t>Federated Learning in Adversarial Environments: Testbed Design and Poisoning Resilience in Cybersecurity</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> This paper presents the design and implementation of a Federated Learning (FL) testbed, focusing on its application in cybersecurity and evaluating its resilience against poisoning attacks. Federated Learning allows multiple clients to collaboratively train a global model while keeping their data decentralized, addressing critical needs for data privacy and security, particularly in sensitive fields like cybersecurity. Our testbed, built using Raspberry Pi and Nvidia Jetson hardware by running the Flower framework, facilitates experimentation with various FL frameworks, assessing their performance, scalability, and ease of integration. Through a case study on federated intrusion detection systems, the testbed's capabilities are shown in detecting anomalies and securing critical infrastructure without exposing sensitive network data. Comprehensive poisoning tests, targeting both model and data integrity, evaluate the system's robustness under adversarial conditions. The results show that while federated learning enhances data privacy and distributed learning, it remains vulnerable to poisoning attacks, which must be mitigated to ensure its reliability in real-world applications. </t>
-  </si>
-  <si>
-    <t>Cybersecurity Software Tool Evaluation Using a 'Perfect' Network Model</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cybersecurity software tool evaluation is difficult due to the inherently adversarial nature of the field. A penetration testing (or offensive) tool must be tested against a viable defensive adversary and a defensive tool must, similarly, be tested against a viable offensive adversary. Characterizing the tool's performance inherently depends on the quality of the adversary, which can vary from test to test. This paper proposes the use of a 'perfect' network, representing computing systems, a network and the attack pathways through it as a methodology to use for testing cybersecurity decision-making tools. This facilitates testing by providing a known and consistent standard for comparison. It also allows testing to include researcher-selected levels of error, noise and uncertainty to evaluate cybersecurity tools under these experimental conditions. </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2848,19 +2842,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="8"/>
-      <color rgb="FF333333"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="8"/>
-      <color rgb="FF287916"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
@@ -2875,12 +2856,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF1F1F1F"/>
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
@@ -2905,9 +2880,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF2D2D2D"/>
-      <name val="Arial"/>
-      <family val="2"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2931,20 +2906,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -3260,7 +3232,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45181C84-A38C-4F01-AAA0-AB64EE24D0FC}">
-  <dimension ref="A1:G301"/>
+  <dimension ref="A1:G302"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="5" width="9.33203125" customWidth="1"/>
@@ -5942,7 +5914,7 @@
         <v>478</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>627</v>
+        <v>867</v>
       </c>
       <c r="E128" s="3" t="s">
         <v>479</v>
@@ -6931,10 +6903,10 @@
         <v>180</v>
       </c>
       <c r="B181" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="C181" s="2" t="s">
         <v>628</v>
-      </c>
-      <c r="C181" s="2" t="s">
-        <v>629</v>
       </c>
       <c r="D181" s="2"/>
       <c r="E181" s="2"/>
@@ -6948,10 +6920,10 @@
         <v>181</v>
       </c>
       <c r="B182" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="C182" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="C182" s="2" t="s">
-        <v>631</v>
       </c>
       <c r="D182" s="2"/>
       <c r="E182" s="2"/>
@@ -6965,10 +6937,10 @@
         <v>182</v>
       </c>
       <c r="B183" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C183" s="2" t="s">
         <v>632</v>
-      </c>
-      <c r="C183" s="2" t="s">
-        <v>633</v>
       </c>
       <c r="D183" s="2"/>
       <c r="E183" s="2"/>
@@ -6982,10 +6954,10 @@
         <v>183</v>
       </c>
       <c r="B184" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C184" s="2" t="s">
         <v>634</v>
-      </c>
-      <c r="C184" s="2" t="s">
-        <v>635</v>
       </c>
       <c r="D184" s="2"/>
       <c r="E184" s="2"/>
@@ -6999,10 +6971,10 @@
         <v>184</v>
       </c>
       <c r="B185" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C185" s="2" t="s">
         <v>636</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>637</v>
       </c>
       <c r="D185" s="2"/>
       <c r="E185" s="2"/>
@@ -7016,10 +6988,10 @@
         <v>185</v>
       </c>
       <c r="B186" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C186" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="D186" s="2"/>
       <c r="E186" s="2"/>
@@ -7033,10 +7005,10 @@
         <v>186</v>
       </c>
       <c r="B187" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="C187" s="2" t="s">
         <v>640</v>
-      </c>
-      <c r="C187" s="2" t="s">
-        <v>641</v>
       </c>
       <c r="D187" s="2"/>
       <c r="E187" s="2"/>
@@ -7050,10 +7022,10 @@
         <v>187</v>
       </c>
       <c r="B188" s="2" t="s">
+        <v>641</v>
+      </c>
+      <c r="C188" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="C188" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="D188" s="2"/>
       <c r="E188" s="2"/>
@@ -7067,10 +7039,10 @@
         <v>188</v>
       </c>
       <c r="B189" s="2" t="s">
+        <v>643</v>
+      </c>
+      <c r="C189" s="2" t="s">
         <v>644</v>
-      </c>
-      <c r="C189" s="2" t="s">
-        <v>645</v>
       </c>
       <c r="D189" s="2"/>
       <c r="E189" s="2"/>
@@ -7084,10 +7056,10 @@
         <v>189</v>
       </c>
       <c r="B190" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="C190" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="C190" s="2" t="s">
-        <v>647</v>
       </c>
       <c r="D190" s="2"/>
       <c r="E190" s="2"/>
@@ -7101,10 +7073,10 @@
         <v>190</v>
       </c>
       <c r="B191" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C191" s="2" t="s">
         <v>648</v>
-      </c>
-      <c r="C191" s="2" t="s">
-        <v>649</v>
       </c>
       <c r="D191" s="2"/>
       <c r="E191" s="2"/>
@@ -7118,10 +7090,10 @@
         <v>191</v>
       </c>
       <c r="B192" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="C192" s="2" t="s">
         <v>650</v>
-      </c>
-      <c r="C192" s="2" t="s">
-        <v>651</v>
       </c>
       <c r="D192" s="2"/>
       <c r="E192" s="2"/>
@@ -7135,10 +7107,10 @@
         <v>192</v>
       </c>
       <c r="B193" s="2" t="s">
+        <v>651</v>
+      </c>
+      <c r="C193" s="2" t="s">
         <v>652</v>
-      </c>
-      <c r="C193" s="2" t="s">
-        <v>653</v>
       </c>
       <c r="D193" s="2"/>
       <c r="E193" s="2"/>
@@ -7152,10 +7124,10 @@
         <v>193</v>
       </c>
       <c r="B194" s="2" t="s">
+        <v>653</v>
+      </c>
+      <c r="C194" s="2" t="s">
         <v>654</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>655</v>
       </c>
       <c r="D194" s="2"/>
       <c r="E194" s="2"/>
@@ -7169,10 +7141,10 @@
         <v>194</v>
       </c>
       <c r="B195" s="2" t="s">
+        <v>655</v>
+      </c>
+      <c r="C195" s="2" t="s">
         <v>656</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>657</v>
       </c>
       <c r="D195" s="2"/>
       <c r="E195" s="2"/>
@@ -7186,10 +7158,10 @@
         <v>195</v>
       </c>
       <c r="B196" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="C196" s="2" t="s">
         <v>658</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>659</v>
       </c>
       <c r="D196" s="2"/>
       <c r="E196" s="2"/>
@@ -7203,10 +7175,10 @@
         <v>196</v>
       </c>
       <c r="B197" s="2" t="s">
+        <v>659</v>
+      </c>
+      <c r="C197" s="2" t="s">
         <v>660</v>
-      </c>
-      <c r="C197" s="2" t="s">
-        <v>661</v>
       </c>
       <c r="D197" s="2"/>
       <c r="E197" s="2"/>
@@ -7220,10 +7192,10 @@
         <v>197</v>
       </c>
       <c r="B198" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C198" s="2" t="s">
         <v>662</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>663</v>
       </c>
       <c r="D198" s="2"/>
       <c r="E198" s="2"/>
@@ -7237,10 +7209,10 @@
         <v>198</v>
       </c>
       <c r="B199" s="2" t="s">
+        <v>663</v>
+      </c>
+      <c r="C199" s="2" t="s">
         <v>664</v>
-      </c>
-      <c r="C199" s="2" t="s">
-        <v>665</v>
       </c>
       <c r="D199" s="2"/>
       <c r="E199" s="2"/>
@@ -7254,10 +7226,10 @@
         <v>199</v>
       </c>
       <c r="B200" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="C200" s="2" t="s">
         <v>666</v>
-      </c>
-      <c r="C200" s="2" t="s">
-        <v>667</v>
       </c>
       <c r="D200" s="2"/>
       <c r="E200" s="2"/>
@@ -7271,10 +7243,10 @@
         <v>200</v>
       </c>
       <c r="B201" s="2" t="s">
+        <v>667</v>
+      </c>
+      <c r="C201" s="2" t="s">
         <v>668</v>
-      </c>
-      <c r="C201" s="2" t="s">
-        <v>669</v>
       </c>
       <c r="D201" s="2"/>
       <c r="E201" s="2"/>
@@ -7288,10 +7260,10 @@
         <v>201</v>
       </c>
       <c r="B202" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>670</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>671</v>
       </c>
       <c r="D202" s="2"/>
       <c r="E202" s="2"/>
@@ -7305,10 +7277,10 @@
         <v>202</v>
       </c>
       <c r="B203" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="C203" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>673</v>
       </c>
       <c r="D203" s="2"/>
       <c r="E203" s="2"/>
@@ -7322,10 +7294,10 @@
         <v>203</v>
       </c>
       <c r="B204" s="2" t="s">
+        <v>673</v>
+      </c>
+      <c r="C204" s="2" t="s">
         <v>674</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>675</v>
       </c>
       <c r="D204" s="2"/>
       <c r="E204" s="2"/>
@@ -7339,10 +7311,10 @@
         <v>204</v>
       </c>
       <c r="B205" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="C205" s="2" t="s">
         <v>676</v>
-      </c>
-      <c r="C205" s="2" t="s">
-        <v>677</v>
       </c>
       <c r="D205" s="2"/>
       <c r="E205" s="2"/>
@@ -7356,10 +7328,10 @@
         <v>205</v>
       </c>
       <c r="B206" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="C206" s="2" t="s">
         <v>678</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>679</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" s="2"/>
@@ -7373,10 +7345,10 @@
         <v>206</v>
       </c>
       <c r="B207" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C207" s="2" t="s">
         <v>680</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>681</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" s="2"/>
@@ -7390,10 +7362,10 @@
         <v>207</v>
       </c>
       <c r="B208" s="2" t="s">
+        <v>681</v>
+      </c>
+      <c r="C208" s="2" t="s">
         <v>682</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>683</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" s="2"/>
@@ -7407,10 +7379,10 @@
         <v>208</v>
       </c>
       <c r="B209" s="2" t="s">
+        <v>683</v>
+      </c>
+      <c r="C209" s="2" t="s">
         <v>684</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>685</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" s="2"/>
@@ -7424,10 +7396,10 @@
         <v>209</v>
       </c>
       <c r="B210" s="2" t="s">
+        <v>685</v>
+      </c>
+      <c r="C210" s="2" t="s">
         <v>686</v>
-      </c>
-      <c r="C210" s="2" t="s">
-        <v>687</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" s="2"/>
@@ -7441,10 +7413,10 @@
         <v>210</v>
       </c>
       <c r="B211" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="C211" s="2" t="s">
         <v>688</v>
-      </c>
-      <c r="C211" s="2" t="s">
-        <v>689</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" s="2"/>
@@ -7458,10 +7430,10 @@
         <v>211</v>
       </c>
       <c r="B212" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="C212" s="2" t="s">
         <v>690</v>
-      </c>
-      <c r="C212" s="2" t="s">
-        <v>691</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" s="2"/>
@@ -7475,10 +7447,10 @@
         <v>212</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="C213" s="2" t="s">
         <v>692</v>
-      </c>
-      <c r="C213" s="2" t="s">
-        <v>693</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" s="2"/>
@@ -7492,10 +7464,10 @@
         <v>213</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C214" s="2" t="s">
         <v>694</v>
-      </c>
-      <c r="C214" s="2" t="s">
-        <v>695</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" s="2"/>
@@ -7509,10 +7481,10 @@
         <v>214</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="C215" s="2" t="s">
         <v>696</v>
-      </c>
-      <c r="C215" s="2" t="s">
-        <v>697</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" s="2"/>
@@ -7526,10 +7498,10 @@
         <v>215</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>697</v>
-      </c>
-      <c r="C216" s="9" t="s">
-        <v>700</v>
+        <v>696</v>
+      </c>
+      <c r="C216" s="8" t="s">
+        <v>866</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" s="2"/>
@@ -7543,10 +7515,10 @@
         <v>216</v>
       </c>
       <c r="B217" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="C217" s="2" t="s">
         <v>698</v>
-      </c>
-      <c r="C217" s="2" t="s">
-        <v>699</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" s="2"/>
@@ -7560,10 +7532,10 @@
         <v>217</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" s="2"/>
@@ -7577,10 +7549,10 @@
         <v>218</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" s="2"/>
@@ -7594,10 +7566,10 @@
         <v>219</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" s="2"/>
@@ -7611,10 +7583,10 @@
         <v>220</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" s="2"/>
@@ -7628,10 +7600,10 @@
         <v>221</v>
       </c>
       <c r="B222" s="2" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" s="2"/>
@@ -7645,10 +7617,10 @@
         <v>222</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" s="2"/>
@@ -7662,10 +7634,10 @@
         <v>223</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" s="2"/>
@@ -7679,10 +7651,10 @@
         <v>224</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" s="2"/>
@@ -7696,10 +7668,10 @@
         <v>225</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" s="2"/>
@@ -7713,10 +7685,10 @@
         <v>226</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>719</v>
+        <v>717</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" s="2"/>
@@ -7730,10 +7702,10 @@
         <v>227</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" s="2"/>
@@ -7747,10 +7719,10 @@
         <v>228</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" s="2"/>
@@ -7764,10 +7736,10 @@
         <v>229</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" s="2"/>
@@ -7781,10 +7753,10 @@
         <v>230</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" s="2"/>
@@ -7798,10 +7770,10 @@
         <v>231</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" s="2"/>
@@ -7815,10 +7787,10 @@
         <v>232</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" s="2"/>
@@ -7832,10 +7804,10 @@
         <v>233</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" s="2"/>
@@ -7849,10 +7821,10 @@
         <v>234</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" s="2"/>
@@ -7866,10 +7838,10 @@
         <v>235</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" s="2"/>
@@ -7883,10 +7855,10 @@
         <v>236</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" s="2"/>
@@ -7899,11 +7871,11 @@
       <c r="A238" s="2">
         <v>237</v>
       </c>
-      <c r="B238" s="10" t="s">
-        <v>741</v>
+      <c r="B238" s="2" t="s">
+        <v>739</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" s="2"/>
@@ -7917,10 +7889,10 @@
         <v>238</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" s="2"/>
@@ -7934,10 +7906,10 @@
         <v>239</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" s="2"/>
@@ -7951,10 +7923,10 @@
         <v>240</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="C241" s="11" t="s">
-        <v>748</v>
+        <v>745</v>
+      </c>
+      <c r="C241" s="9" t="s">
+        <v>746</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" s="2"/>
@@ -7968,10 +7940,10 @@
         <v>241</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" s="2"/>
@@ -7985,10 +7957,10 @@
         <v>242</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" s="2"/>
@@ -8002,10 +7974,10 @@
         <v>243</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="D244" s="2"/>
       <c r="E244" s="2"/>
@@ -8019,10 +7991,10 @@
         <v>244</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D245" s="2"/>
       <c r="E245" s="2"/>
@@ -8036,10 +8008,10 @@
         <v>245</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="D246" s="2"/>
       <c r="E246" s="2"/>
@@ -8053,10 +8025,10 @@
         <v>246</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="D247" s="2"/>
       <c r="E247" s="2"/>
@@ -8070,10 +8042,10 @@
         <v>247</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="D248" s="2"/>
       <c r="E248" s="2"/>
@@ -8087,10 +8059,10 @@
         <v>248</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="D249" s="2"/>
       <c r="E249" s="2"/>
@@ -8104,10 +8076,10 @@
         <v>249</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="D250" s="2"/>
       <c r="E250" s="2"/>
@@ -8121,10 +8093,10 @@
         <v>250</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="D251" s="2"/>
       <c r="E251" s="2"/>
@@ -8138,10 +8110,10 @@
         <v>251</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="D252" s="2"/>
       <c r="E252" s="2"/>
@@ -8155,10 +8127,10 @@
         <v>252</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="D253" s="2"/>
       <c r="E253" s="2"/>
@@ -8172,10 +8144,10 @@
         <v>253</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="D254" s="2"/>
       <c r="E254" s="2"/>
@@ -8189,10 +8161,10 @@
         <v>254</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="D255" s="2"/>
       <c r="E255" s="2"/>
@@ -8206,10 +8178,10 @@
         <v>255</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="D256" s="2"/>
       <c r="E256" s="2"/>
@@ -8223,10 +8195,10 @@
         <v>256</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="D257" s="2"/>
       <c r="E257" s="2"/>
@@ -8240,10 +8212,10 @@
         <v>257</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D258" s="2"/>
       <c r="E258" s="2"/>
@@ -8257,10 +8229,10 @@
         <v>258</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="D259" s="2"/>
       <c r="E259" s="2"/>
@@ -8274,10 +8246,10 @@
         <v>259</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="D260" s="2"/>
       <c r="E260" s="2"/>
@@ -8291,10 +8263,10 @@
         <v>260</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="D261" s="2"/>
       <c r="E261" s="2"/>
@@ -8308,10 +8280,10 @@
         <v>261</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="D262" s="2"/>
       <c r="E262" s="2"/>
@@ -8325,10 +8297,10 @@
         <v>262</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="D263" s="2"/>
       <c r="E263" s="2"/>
@@ -8342,10 +8314,10 @@
         <v>263</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="D264" s="2"/>
       <c r="E264" s="2"/>
@@ -8359,10 +8331,10 @@
         <v>264</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="D265" s="2"/>
       <c r="E265" s="2"/>
@@ -8376,10 +8348,10 @@
         <v>265</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="D266" s="2"/>
       <c r="E266" s="2"/>
@@ -8393,10 +8365,10 @@
         <v>266</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="D267" s="2"/>
       <c r="E267" s="2"/>
@@ -8410,10 +8382,10 @@
         <v>267</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="D268" s="2"/>
       <c r="E268" s="2"/>
@@ -8427,10 +8399,10 @@
         <v>268</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D269" s="2"/>
       <c r="E269" s="2"/>
@@ -8443,11 +8415,11 @@
       <c r="A270" s="2">
         <v>269</v>
       </c>
-      <c r="B270" s="12" t="s">
-        <v>805</v>
+      <c r="B270" s="7" t="s">
+        <v>803</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D270" s="2"/>
       <c r="E270" s="2"/>
@@ -8461,10 +8433,10 @@
         <v>270</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D271" s="2"/>
       <c r="E271" s="2"/>
@@ -8478,10 +8450,10 @@
         <v>271</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D272" s="2"/>
       <c r="E272" s="2"/>
@@ -8495,10 +8467,10 @@
         <v>272</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D273" s="2"/>
       <c r="E273" s="2"/>
@@ -8512,10 +8484,10 @@
         <v>273</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D274" s="2"/>
       <c r="E274" s="2"/>
@@ -8529,10 +8501,10 @@
         <v>274</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" s="2"/>
@@ -8546,10 +8518,10 @@
         <v>275</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" s="2"/>
@@ -8563,10 +8535,10 @@
         <v>276</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>819</v>
+        <v>817</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>820</v>
+        <v>818</v>
       </c>
       <c r="D277" s="2"/>
       <c r="E277" s="2"/>
@@ -8580,10 +8552,10 @@
         <v>277</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="D278" s="2"/>
       <c r="E278" s="2"/>
@@ -8597,10 +8569,10 @@
         <v>278</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D279" s="2"/>
       <c r="E279" s="2"/>
@@ -8614,10 +8586,10 @@
         <v>279</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" s="2"/>
@@ -8631,10 +8603,10 @@
         <v>280</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" s="2"/>
@@ -8648,10 +8620,10 @@
         <v>281</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C282" s="8" t="s">
-        <v>830</v>
+        <v>868</v>
       </c>
       <c r="D282" s="2"/>
       <c r="E282" s="2"/>
@@ -8665,10 +8637,10 @@
         <v>282</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="D283" s="2"/>
       <c r="E283" s="2"/>
@@ -8682,10 +8654,10 @@
         <v>283</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="D284" s="2"/>
       <c r="E284" s="2"/>
@@ -8699,10 +8671,10 @@
         <v>284</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="D285" s="2"/>
       <c r="E285" s="2"/>
@@ -8716,10 +8688,10 @@
         <v>285</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" s="2"/>
@@ -8733,10 +8705,10 @@
         <v>286</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" s="2"/>
@@ -8750,10 +8722,10 @@
         <v>287</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" s="2"/>
@@ -8767,10 +8739,10 @@
         <v>288</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" s="2"/>
@@ -8784,10 +8756,10 @@
         <v>289</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D290" s="2"/>
       <c r="E290" s="2"/>
@@ -8801,10 +8773,10 @@
         <v>290</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D291" s="2"/>
       <c r="E291" s="2"/>
@@ -8818,10 +8790,10 @@
         <v>291</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" s="2"/>
@@ -8835,10 +8807,10 @@
         <v>292</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" s="2"/>
@@ -8852,10 +8824,10 @@
         <v>293</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" s="2"/>
@@ -8869,10 +8841,10 @@
         <v>294</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="D295" s="2"/>
       <c r="E295" s="2"/>
@@ -8886,10 +8858,10 @@
         <v>295</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" s="2"/>
@@ -8903,10 +8875,10 @@
         <v>296</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="D297" s="2"/>
       <c r="E297" s="2"/>
@@ -8920,10 +8892,10 @@
         <v>297</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" s="2"/>
@@ -8937,10 +8909,10 @@
         <v>298</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="D299" s="2"/>
       <c r="E299" s="2"/>
@@ -8954,10 +8926,10 @@
         <v>299</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" s="2"/>
@@ -8971,10 +8943,10 @@
         <v>300</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" s="2"/>
@@ -8982,6 +8954,21 @@
         <v>568</v>
       </c>
       <c r="G301" s="2"/>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A302" s="2">
+        <v>301</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>850</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>851</v>
+      </c>
+      <c r="D302" s="2"/>
+      <c r="E302" s="2"/>
+      <c r="F302" s="2"/>
+      <c r="G302" s="2"/>
     </row>
   </sheetData>
   <hyperlinks>
